--- a/COMENTARIOS.xlsx
+++ b/COMENTARIOS.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Por fichero" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comentarios'!$A$1:$G$1613</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por fichero'!$A$1:$D$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comentarios'!$A$1:$G$1626</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por fichero'!$A$1:$D$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1613"/>
+  <dimension ref="A1:G1626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>913</v>
+        <v>918</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1026</v>
+        <v>1037</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>1053</v>
+        <v>1064</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>1067</v>
+        <v>1078</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1074</v>
+        <v>1085</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>1080</v>
+        <v>1091</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>1091</v>
+        <v>1102</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>1130</v>
+        <v>1141</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>1140</v>
+        <v>1151</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>1163</v>
+        <v>1174</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>1234</v>
+        <v>1245</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1268</v>
+        <v>1279</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>1284</v>
+        <v>1295</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1308</v>
+        <v>1319</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>1324</v>
+        <v>1335</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>1340</v>
+        <v>1351</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>1348</v>
+        <v>1359</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>1356</v>
+        <v>1367</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>1387</v>
+        <v>1398</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>1428</v>
+        <v>1439</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>1448</v>
+        <v>1459</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>1466</v>
+        <v>1477</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>1475</v>
+        <v>1486</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>1511</v>
+        <v>1522</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>1532</v>
+        <v>1543</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>1554</v>
+        <v>1565</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>1590</v>
+        <v>1601</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>1630</v>
+        <v>1641</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>1651</v>
+        <v>1662</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>1657</v>
+        <v>1668</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>1677</v>
+        <v>1688</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>1701</v>
+        <v>1712</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>1725</v>
+        <v>1736</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>1751</v>
+        <v>1762</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>1763</v>
+        <v>1774</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>1780</v>
+        <v>1791</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>1794</v>
+        <v>1805</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>1811</v>
+        <v>1822</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>1835</v>
+        <v>1846</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>1860</v>
+        <v>1871</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>1874</v>
+        <v>1885</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>1894</v>
+        <v>1905</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>1909</v>
+        <v>1920</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>1922</v>
+        <v>1933</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>1940</v>
+        <v>1951</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>1955</v>
+        <v>1966</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>1972</v>
+        <v>1983</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>1985</v>
+        <v>1996</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>1997</v>
+        <v>2008</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>2028</v>
+        <v>2039</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>2043</v>
+        <v>2054</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>2064</v>
+        <v>2075</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>2071</v>
+        <v>2082</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>2092</v>
+        <v>2103</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>2123</v>
+        <v>2134</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>2179</v>
+        <v>2190</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>2209</v>
+        <v>2220</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>2225</v>
+        <v>2236</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>2247</v>
+        <v>2258</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>2288</v>
+        <v>2299</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>2303</v>
+        <v>2314</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>2319</v>
+        <v>2330</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>2338</v>
+        <v>2349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>2356</v>
+        <v>2367</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>2368</v>
+        <v>2379</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>2381</v>
+        <v>2392</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>2426</v>
+        <v>2437</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>2445</v>
+        <v>2456</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>2472</v>
+        <v>2483</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>2499</v>
+        <v>2510</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>2526</v>
+        <v>2537</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>2536</v>
+        <v>2547</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>2548</v>
+        <v>2559</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>2559</v>
+        <v>2570</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>2570</v>
+        <v>2581</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>2605</v>
+        <v>2616</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>2632</v>
+        <v>2643</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>2651</v>
+        <v>2662</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>2665</v>
+        <v>2676</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>2689</v>
+        <v>2700</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2707</v>
+        <v>2718</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>2724</v>
+        <v>2735</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>2739</v>
+        <v>2750</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>2765</v>
+        <v>2776</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>2781</v>
+        <v>2792</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>2793</v>
+        <v>2804</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>2811</v>
+        <v>2822</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>2843</v>
+        <v>2854</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>2861</v>
+        <v>2872</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>2889</v>
+        <v>2900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>2945</v>
+        <v>2956</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>2963</v>
+        <v>2974</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>2985</v>
+        <v>2996</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>3002</v>
+        <v>3013</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>3026</v>
+        <v>3037</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>3051</v>
+        <v>3062</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>3063</v>
+        <v>3074</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>3081</v>
+        <v>3092</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>3093</v>
+        <v>3104</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>3108</v>
+        <v>3119</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>3132</v>
+        <v>3143</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>3140</v>
+        <v>3151</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>3158</v>
+        <v>3169</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>3167</v>
+        <v>3178</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>3181</v>
+        <v>3192</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>3196</v>
+        <v>3207</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>3374</v>
+        <v>3385</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>3391</v>
+        <v>3402</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>3404</v>
+        <v>3415</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>3409</v>
+        <v>3420</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>2825</v>
+        <v>2836</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -13594,7 +13594,11 @@
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>[00367] Lo que vale para todo el camión y no se vuelve a teclear pieza a pieza.</t>
+          <t>[00367] Lo que vale para todo el camión y no se vuelve a teclear pieza a pieza.
+Lo que vale para toda la descarga y por eso se queda escrito de una pieza a
+la siguiente. El precio del kilo ya no está: es de cada pieza, y arrastrarlo
+hacía que la segunda bolsa se quedara con el precio de la primera sin que
+nadie lo hubiera dicho. El transporte y la aduana sí, que son del camión.</t>
         </is>
       </c>
     </row>
@@ -13610,7 +13614,7 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -13641,7 +13645,7 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -13674,7 +13678,7 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -13708,7 +13712,7 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>950</v>
+        <v>961</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -13741,7 +13745,7 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>960</v>
+        <v>971</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -13776,7 +13780,7 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -13810,7 +13814,7 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>996</v>
+        <v>1007</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -13844,7 +13848,7 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>1005</v>
+        <v>1016</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -13878,7 +13882,7 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>1010</v>
+        <v>1021</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -13909,7 +13913,7 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>1017</v>
+        <v>1028</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -13944,7 +13948,7 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>1038</v>
+        <v>1049</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -13976,7 +13980,7 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>1103</v>
+        <v>1114</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -14009,7 +14013,7 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>1137</v>
+        <v>1148</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -14042,7 +14046,7 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>1168</v>
+        <v>1179</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -14074,7 +14078,7 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>1179</v>
+        <v>1190</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -14107,7 +14111,7 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>1186</v>
+        <v>1197</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -14142,7 +14146,7 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>1212</v>
+        <v>1223</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -14175,7 +14179,7 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>1218</v>
+        <v>1229</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -14207,7 +14211,7 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>1331</v>
+        <v>1342</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -14243,7 +14247,7 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>1363</v>
+        <v>1374</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -14275,7 +14279,7 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>1395</v>
+        <v>1406</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -14307,7 +14311,7 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>1401</v>
+        <v>1412</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -14339,7 +14343,7 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>1473</v>
+        <v>1484</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -14371,7 +14375,7 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>1484</v>
+        <v>1495</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -14406,7 +14410,7 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>1537</v>
+        <v>1548</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -14438,7 +14442,7 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>1564</v>
+        <v>1575</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -14470,7 +14474,7 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>1734</v>
+        <v>1745</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -14502,7 +14506,7 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>2080</v>
+        <v>2091</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -14534,7 +14538,7 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>2132</v>
+        <v>2143</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -14566,7 +14570,7 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>2148</v>
+        <v>2159</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -14598,7 +14602,7 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>2185</v>
+        <v>2196</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -14629,7 +14633,7 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>2256</v>
+        <v>2267</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -14664,7 +14668,7 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>2263</v>
+        <v>2274</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -14696,7 +14700,7 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>2342</v>
+        <v>2353</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -14728,7 +14732,7 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>2396</v>
+        <v>2407</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -14760,7 +14764,7 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>2403</v>
+        <v>2414</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -14793,7 +14797,7 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>2416</v>
+        <v>2427</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -14825,7 +14829,7 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>2459</v>
+        <v>2470</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -14860,7 +14864,7 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>2712</v>
+        <v>2723</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -14892,7 +14896,7 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>2751</v>
+        <v>2762</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -14925,7 +14929,7 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>2800</v>
+        <v>2811</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -14957,7 +14961,7 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>2841</v>
+        <v>2852</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -14989,7 +14993,7 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>2849</v>
+        <v>2860</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -15021,7 +15025,7 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>2903</v>
+        <v>2914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -15054,7 +15058,7 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>2920</v>
+        <v>2931</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -15088,7 +15092,7 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>2974</v>
+        <v>2985</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -15123,7 +15127,7 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>3007</v>
+        <v>3018</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -15157,7 +15161,7 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>3031</v>
+        <v>3042</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -15191,7 +15195,7 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>3046</v>
+        <v>3057</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -15223,7 +15227,7 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>3206</v>
+        <v>3217</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -17378,7 +17382,7 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>5031</v>
+        <v>5052</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -17630,7 +17634,7 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -17661,7 +17665,7 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -17692,7 +17696,7 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -17723,7 +17727,7 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>1403</v>
+        <v>1409</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -17754,7 +17758,7 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -17785,7 +17789,7 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -17816,7 +17820,7 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>2118</v>
+        <v>2127</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -17847,7 +17851,7 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>2152</v>
+        <v>2161</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -17878,7 +17882,7 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>2169</v>
+        <v>2178</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -17909,7 +17913,7 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>2833</v>
+        <v>2845</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -17940,7 +17944,7 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>2867</v>
+        <v>2879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -17971,7 +17975,7 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>2884</v>
+        <v>2896</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -18002,7 +18006,7 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>3548</v>
+        <v>3563</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -18033,7 +18037,7 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>3582</v>
+        <v>3597</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -18064,7 +18068,7 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>3599</v>
+        <v>3614</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -18095,7 +18099,7 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>4263</v>
+        <v>4281</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -18126,7 +18130,7 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>4297</v>
+        <v>4315</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -18157,7 +18161,7 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>4316</v>
+        <v>4334</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -18188,7 +18192,7 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>4980</v>
+        <v>5001</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -18219,7 +18223,7 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>5014</v>
+        <v>5035</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -20379,7 +20383,7 @@
         </is>
       </c>
       <c r="C564" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -20418,7 +20422,7 @@
         </is>
       </c>
       <c r="C565" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -20457,7 +20461,7 @@
         </is>
       </c>
       <c r="C566" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -20495,7 +20499,7 @@
         </is>
       </c>
       <c r="C567" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -20536,7 +20540,7 @@
         </is>
       </c>
       <c r="C568" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -20577,7 +20581,7 @@
         </is>
       </c>
       <c r="C569" t="n">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -20616,7 +20620,7 @@
         </is>
       </c>
       <c r="C570" t="n">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -20656,7 +20660,7 @@
         </is>
       </c>
       <c r="C571" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -20697,7 +20701,7 @@
         </is>
       </c>
       <c r="C572" t="n">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -20732,7 +20736,7 @@
         </is>
       </c>
       <c r="C573" t="n">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -20771,7 +20775,7 @@
         </is>
       </c>
       <c r="C574" t="n">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -20813,7 +20817,7 @@
         </is>
       </c>
       <c r="C575" t="n">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -20854,7 +20858,7 @@
         </is>
       </c>
       <c r="C576" t="n">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -20893,7 +20897,7 @@
         </is>
       </c>
       <c r="C577" t="n">
-        <v>461</v>
+        <v>494</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -20928,7 +20932,7 @@
         </is>
       </c>
       <c r="C578" t="n">
-        <v>467</v>
+        <v>500</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -20968,7 +20972,7 @@
         </is>
       </c>
       <c r="C579" t="n">
-        <v>500</v>
+        <v>533</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -21003,7 +21007,7 @@
         </is>
       </c>
       <c r="C580" t="n">
-        <v>510</v>
+        <v>543</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -21045,7 +21049,7 @@
         </is>
       </c>
       <c r="C581" t="n">
-        <v>537</v>
+        <v>570</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -21080,7 +21084,7 @@
         </is>
       </c>
       <c r="C582" t="n">
-        <v>549</v>
+        <v>582</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -21115,7 +21119,7 @@
         </is>
       </c>
       <c r="C583" t="n">
-        <v>558</v>
+        <v>591</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -21150,7 +21154,7 @@
         </is>
       </c>
       <c r="C584" t="n">
-        <v>564</v>
+        <v>597</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -21185,7 +21189,7 @@
         </is>
       </c>
       <c r="C585" t="n">
-        <v>569</v>
+        <v>602</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -21220,7 +21224,7 @@
         </is>
       </c>
       <c r="C586" t="n">
-        <v>574</v>
+        <v>607</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -21255,7 +21259,7 @@
         </is>
       </c>
       <c r="C587" t="n">
-        <v>583</v>
+        <v>616</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -21294,7 +21298,7 @@
         </is>
       </c>
       <c r="C588" t="n">
-        <v>612</v>
+        <v>645</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -21329,7 +21333,7 @@
         </is>
       </c>
       <c r="C589" t="n">
-        <v>633</v>
+        <v>666</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -21364,7 +21368,7 @@
         </is>
       </c>
       <c r="C590" t="n">
-        <v>640</v>
+        <v>673</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -21399,7 +21403,7 @@
         </is>
       </c>
       <c r="C591" t="n">
-        <v>645</v>
+        <v>678</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -21434,7 +21438,7 @@
         </is>
       </c>
       <c r="C592" t="n">
-        <v>658</v>
+        <v>691</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -21469,7 +21473,7 @@
         </is>
       </c>
       <c r="C593" t="n">
-        <v>682</v>
+        <v>715</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -21504,7 +21508,7 @@
         </is>
       </c>
       <c r="C594" t="n">
-        <v>772</v>
+        <v>805</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -21539,7 +21543,7 @@
         </is>
       </c>
       <c r="C595" t="n">
-        <v>780</v>
+        <v>813</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -21574,7 +21578,7 @@
         </is>
       </c>
       <c r="C596" t="n">
-        <v>808</v>
+        <v>841</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -21609,7 +21613,7 @@
         </is>
       </c>
       <c r="C597" t="n">
-        <v>814</v>
+        <v>847</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -21644,7 +21648,7 @@
         </is>
       </c>
       <c r="C598" t="n">
-        <v>820</v>
+        <v>853</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -21679,7 +21683,7 @@
         </is>
       </c>
       <c r="C599" t="n">
-        <v>838</v>
+        <v>871</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -21722,7 +21726,7 @@
         </is>
       </c>
       <c r="C600" t="n">
-        <v>901</v>
+        <v>934</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -21757,7 +21761,7 @@
         </is>
       </c>
       <c r="C601" t="n">
-        <v>926</v>
+        <v>959</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -21792,7 +21796,7 @@
         </is>
       </c>
       <c r="C602" t="n">
-        <v>938</v>
+        <v>971</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -21827,7 +21831,7 @@
         </is>
       </c>
       <c r="C603" t="n">
-        <v>959</v>
+        <v>992</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -21862,7 +21866,7 @@
         </is>
       </c>
       <c r="C604" t="n">
-        <v>972</v>
+        <v>1005</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -21897,7 +21901,7 @@
         </is>
       </c>
       <c r="C605" t="n">
-        <v>1023</v>
+        <v>1056</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -21932,7 +21936,7 @@
         </is>
       </c>
       <c r="C606" t="n">
-        <v>1051</v>
+        <v>1084</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -21971,7 +21975,7 @@
         </is>
       </c>
       <c r="C607" t="n">
-        <v>1090</v>
+        <v>1123</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -22006,7 +22010,7 @@
         </is>
       </c>
       <c r="C608" t="n">
-        <v>1130</v>
+        <v>1163</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -22045,7 +22049,7 @@
         </is>
       </c>
       <c r="C609" t="n">
-        <v>1143</v>
+        <v>1176</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -22080,7 +22084,7 @@
         </is>
       </c>
       <c r="C610" t="n">
-        <v>1158</v>
+        <v>1191</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -22115,7 +22119,7 @@
         </is>
       </c>
       <c r="C611" t="n">
-        <v>1182</v>
+        <v>1215</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -22157,7 +22161,7 @@
         </is>
       </c>
       <c r="C612" t="n">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -22195,7 +22199,7 @@
         </is>
       </c>
       <c r="C613" t="n">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -22230,7 +22234,7 @@
         </is>
       </c>
       <c r="C614" t="n">
-        <v>741</v>
+        <v>774</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -22267,7 +22271,7 @@
         </is>
       </c>
       <c r="C615" t="n">
-        <v>752</v>
+        <v>785</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -22302,7 +22306,7 @@
         </is>
       </c>
       <c r="C616" t="n">
-        <v>1013</v>
+        <v>1046</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -22337,7 +22341,7 @@
         </is>
       </c>
       <c r="C617" t="n">
-        <v>1018</v>
+        <v>1051</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -22372,7 +22376,7 @@
         </is>
       </c>
       <c r="C618" t="n">
-        <v>1073</v>
+        <v>1106</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -22407,7 +22411,7 @@
         </is>
       </c>
       <c r="C619" t="n">
-        <v>1078</v>
+        <v>1111</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -22442,7 +22446,7 @@
         </is>
       </c>
       <c r="C620" t="n">
-        <v>1083</v>
+        <v>1116</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -22477,7 +22481,7 @@
         </is>
       </c>
       <c r="C621" t="n">
-        <v>1233</v>
+        <v>1266</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -22547,7 +22551,7 @@
         </is>
       </c>
       <c r="C623" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -22581,7 +22585,7 @@
         </is>
       </c>
       <c r="C624" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -22613,7 +22617,7 @@
         </is>
       </c>
       <c r="C625" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -22645,7 +22649,7 @@
         </is>
       </c>
       <c r="C626" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -22676,7 +22680,7 @@
         </is>
       </c>
       <c r="C627" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -22709,7 +22713,7 @@
         </is>
       </c>
       <c r="C628" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -22743,7 +22747,7 @@
         </is>
       </c>
       <c r="C629" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -22775,7 +22779,7 @@
         </is>
       </c>
       <c r="C630" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -22808,7 +22812,7 @@
         </is>
       </c>
       <c r="C631" t="n">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -22841,7 +22845,7 @@
         </is>
       </c>
       <c r="C632" t="n">
-        <v>436</v>
+        <v>463</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -22874,7 +22878,7 @@
         </is>
       </c>
       <c r="C633" t="n">
-        <v>442</v>
+        <v>475</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -22914,7 +22918,7 @@
         </is>
       </c>
       <c r="C634" t="n">
-        <v>683</v>
+        <v>716</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -22946,7 +22950,7 @@
         </is>
       </c>
       <c r="C635" t="n">
-        <v>694</v>
+        <v>727</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -22978,7 +22982,7 @@
         </is>
       </c>
       <c r="C636" t="n">
-        <v>700</v>
+        <v>733</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -23011,7 +23015,7 @@
         </is>
       </c>
       <c r="C637" t="n">
-        <v>706</v>
+        <v>739</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -23046,7 +23050,7 @@
         </is>
       </c>
       <c r="C638" t="n">
-        <v>728</v>
+        <v>761</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -23081,7 +23085,7 @@
         </is>
       </c>
       <c r="C639" t="n">
-        <v>756</v>
+        <v>789</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -23113,7 +23117,7 @@
         </is>
       </c>
       <c r="C640" t="n">
-        <v>759</v>
+        <v>792</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -23145,7 +23149,7 @@
         </is>
       </c>
       <c r="C641" t="n">
-        <v>763</v>
+        <v>796</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -23177,7 +23181,7 @@
         </is>
       </c>
       <c r="C642" t="n">
-        <v>865</v>
+        <v>898</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -23208,7 +23212,7 @@
         </is>
       </c>
       <c r="C643" t="n">
-        <v>893</v>
+        <v>926</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -23242,7 +23246,7 @@
         </is>
       </c>
       <c r="C644" t="n">
-        <v>947</v>
+        <v>980</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -23274,7 +23278,7 @@
         </is>
       </c>
       <c r="C645" t="n">
-        <v>1094</v>
+        <v>1127</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -23308,7 +23312,7 @@
         </is>
       </c>
       <c r="C646" t="n">
-        <v>1151</v>
+        <v>1184</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -23341,7 +23345,7 @@
         </is>
       </c>
       <c r="C647" t="n">
-        <v>1193</v>
+        <v>1226</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -23372,7 +23376,7 @@
         </is>
       </c>
       <c r="C648" t="n">
-        <v>1204</v>
+        <v>1237</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -23403,7 +23407,7 @@
         </is>
       </c>
       <c r="C649" t="n">
-        <v>1207</v>
+        <v>1240</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -23435,7 +23439,7 @@
         </is>
       </c>
       <c r="C650" t="n">
-        <v>1212</v>
+        <v>1245</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -23467,7 +23471,7 @@
         </is>
       </c>
       <c r="C651" t="n">
-        <v>1223</v>
+        <v>1256</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -23499,7 +23503,7 @@
         </is>
       </c>
       <c r="C652" t="n">
-        <v>1227</v>
+        <v>1260</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -25366,7 +25370,7 @@
         </is>
       </c>
       <c r="C704" t="n">
-        <v>581</v>
+        <v>594</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -25405,7 +25409,7 @@
         </is>
       </c>
       <c r="C705" t="n">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -25445,7 +25449,7 @@
         </is>
       </c>
       <c r="C706" t="n">
-        <v>650</v>
+        <v>663</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -25480,7 +25484,7 @@
         </is>
       </c>
       <c r="C707" t="n">
-        <v>664</v>
+        <v>677</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -25519,7 +25523,7 @@
         </is>
       </c>
       <c r="C708" t="n">
-        <v>804</v>
+        <v>817</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -25559,7 +25563,7 @@
         </is>
       </c>
       <c r="C709" t="n">
-        <v>851</v>
+        <v>864</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -25597,7 +25601,7 @@
         </is>
       </c>
       <c r="C710" t="n">
-        <v>874</v>
+        <v>887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -25635,7 +25639,7 @@
         </is>
       </c>
       <c r="C711" t="n">
-        <v>923</v>
+        <v>936</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -25670,7 +25674,7 @@
         </is>
       </c>
       <c r="C712" t="n">
-        <v>940</v>
+        <v>953</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -25705,7 +25709,7 @@
         </is>
       </c>
       <c r="C713" t="n">
-        <v>968</v>
+        <v>981</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -25740,7 +25744,7 @@
         </is>
       </c>
       <c r="C714" t="n">
-        <v>1006</v>
+        <v>1019</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -25775,7 +25779,7 @@
         </is>
       </c>
       <c r="C715" t="n">
-        <v>1037</v>
+        <v>1050</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -25810,7 +25814,7 @@
         </is>
       </c>
       <c r="C716" t="n">
-        <v>1066</v>
+        <v>1079</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -25845,7 +25849,7 @@
         </is>
       </c>
       <c r="C717" t="n">
-        <v>1084</v>
+        <v>1097</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -25888,7 +25892,7 @@
         </is>
       </c>
       <c r="C718" t="n">
-        <v>1114</v>
+        <v>1127</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -25927,7 +25931,7 @@
         </is>
       </c>
       <c r="C719" t="n">
-        <v>1146</v>
+        <v>1159</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -25967,7 +25971,7 @@
         </is>
       </c>
       <c r="C720" t="n">
-        <v>1165</v>
+        <v>1178</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -26008,7 +26012,7 @@
         </is>
       </c>
       <c r="C721" t="n">
-        <v>1201</v>
+        <v>1214</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -26048,7 +26052,7 @@
         </is>
       </c>
       <c r="C722" t="n">
-        <v>1225</v>
+        <v>1238</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -26088,7 +26092,7 @@
         </is>
       </c>
       <c r="C723" t="n">
-        <v>1251</v>
+        <v>1264</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -26126,7 +26130,7 @@
         </is>
       </c>
       <c r="C724" t="n">
-        <v>1283</v>
+        <v>1296</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -26165,7 +26169,7 @@
         </is>
       </c>
       <c r="C725" t="n">
-        <v>1301</v>
+        <v>1314</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -26208,7 +26212,7 @@
         </is>
       </c>
       <c r="C726" t="n">
-        <v>1324</v>
+        <v>1337</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -26249,7 +26253,7 @@
         </is>
       </c>
       <c r="C727" t="n">
-        <v>1356</v>
+        <v>1369</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -26295,7 +26299,7 @@
         </is>
       </c>
       <c r="C728" t="n">
-        <v>1383</v>
+        <v>1396</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -26338,7 +26342,7 @@
         </is>
       </c>
       <c r="C729" t="n">
-        <v>1411</v>
+        <v>1424</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -27020,7 +27024,7 @@
         </is>
       </c>
       <c r="C749" t="n">
-        <v>532</v>
+        <v>545</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -27056,7 +27060,7 @@
         </is>
       </c>
       <c r="C750" t="n">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -27088,7 +27092,7 @@
         </is>
       </c>
       <c r="C751" t="n">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -27124,7 +27128,7 @@
         </is>
       </c>
       <c r="C752" t="n">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -27155,7 +27159,7 @@
         </is>
       </c>
       <c r="C753" t="n">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -27188,7 +27192,7 @@
         </is>
       </c>
       <c r="C754" t="n">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -27222,7 +27226,7 @@
         </is>
       </c>
       <c r="C755" t="n">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -27254,7 +27258,7 @@
         </is>
       </c>
       <c r="C756" t="n">
-        <v>680</v>
+        <v>693</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -27286,7 +27290,7 @@
         </is>
       </c>
       <c r="C757" t="n">
-        <v>821</v>
+        <v>834</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -27319,7 +27323,7 @@
         </is>
       </c>
       <c r="C758" t="n">
-        <v>825</v>
+        <v>838</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -27352,7 +27356,7 @@
         </is>
       </c>
       <c r="C759" t="n">
-        <v>829</v>
+        <v>842</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -27392,7 +27396,7 @@
         </is>
       </c>
       <c r="C760" t="n">
-        <v>895</v>
+        <v>908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -27423,7 +27427,7 @@
         </is>
       </c>
       <c r="C761" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -27455,7 +27459,7 @@
         </is>
       </c>
       <c r="C762" t="n">
-        <v>903</v>
+        <v>916</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -27487,7 +27491,7 @@
         </is>
       </c>
       <c r="C763" t="n">
-        <v>906</v>
+        <v>919</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -27521,7 +27525,7 @@
         </is>
       </c>
       <c r="C764" t="n">
-        <v>912</v>
+        <v>925</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -27555,7 +27559,7 @@
         </is>
       </c>
       <c r="C765" t="n">
-        <v>954</v>
+        <v>967</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -27587,7 +27591,7 @@
         </is>
       </c>
       <c r="C766" t="n">
-        <v>961</v>
+        <v>974</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -27618,7 +27622,7 @@
         </is>
       </c>
       <c r="C767" t="n">
-        <v>976</v>
+        <v>989</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -27650,7 +27654,7 @@
         </is>
       </c>
       <c r="C768" t="n">
-        <v>1008</v>
+        <v>1021</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -27685,7 +27689,7 @@
         </is>
       </c>
       <c r="C769" t="n">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -27717,7 +27721,7 @@
         </is>
       </c>
       <c r="C770" t="n">
-        <v>1029</v>
+        <v>1042</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -27748,7 +27752,7 @@
         </is>
       </c>
       <c r="C771" t="n">
-        <v>1052</v>
+        <v>1065</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -27781,7 +27785,7 @@
         </is>
       </c>
       <c r="C772" t="n">
-        <v>1057</v>
+        <v>1070</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -27814,7 +27818,7 @@
         </is>
       </c>
       <c r="C773" t="n">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -27848,7 +27852,7 @@
         </is>
       </c>
       <c r="C774" t="n">
-        <v>1181</v>
+        <v>1194</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -27880,7 +27884,7 @@
         </is>
       </c>
       <c r="C775" t="n">
-        <v>1190</v>
+        <v>1203</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -27912,7 +27916,7 @@
         </is>
       </c>
       <c r="C776" t="n">
-        <v>1337</v>
+        <v>1350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -27945,7 +27949,7 @@
         </is>
       </c>
       <c r="C777" t="n">
-        <v>1342</v>
+        <v>1355</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -27977,7 +27981,7 @@
         </is>
       </c>
       <c r="C778" t="n">
-        <v>1348</v>
+        <v>1361</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -28008,7 +28012,7 @@
         </is>
       </c>
       <c r="C779" t="n">
-        <v>1402</v>
+        <v>1415</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -30409,7 +30413,7 @@
         </is>
       </c>
       <c r="C845" t="n">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -30444,7 +30448,7 @@
         </is>
       </c>
       <c r="C846" t="n">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -30479,7 +30483,7 @@
         </is>
       </c>
       <c r="C847" t="n">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -30528,7 +30532,7 @@
         </is>
       </c>
       <c r="C848" t="n">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -30563,7 +30567,7 @@
         </is>
       </c>
       <c r="C849" t="n">
-        <v>679</v>
+        <v>690</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -30601,7 +30605,7 @@
         </is>
       </c>
       <c r="C850" t="n">
-        <v>733</v>
+        <v>757</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -30636,7 +30640,7 @@
         </is>
       </c>
       <c r="C851" t="n">
-        <v>747</v>
+        <v>771</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -30671,7 +30675,7 @@
         </is>
       </c>
       <c r="C852" t="n">
-        <v>782</v>
+        <v>806</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -30713,7 +30717,7 @@
         </is>
       </c>
       <c r="C853" t="n">
-        <v>810</v>
+        <v>834</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -30748,7 +30752,7 @@
         </is>
       </c>
       <c r="C854" t="n">
-        <v>819</v>
+        <v>843</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -30787,7 +30791,7 @@
         </is>
       </c>
       <c r="C855" t="n">
-        <v>862</v>
+        <v>886</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -30825,7 +30829,7 @@
         </is>
       </c>
       <c r="C856" t="n">
-        <v>920</v>
+        <v>944</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -30860,7 +30864,7 @@
         </is>
       </c>
       <c r="C857" t="n">
-        <v>932</v>
+        <v>956</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -30895,7 +30899,7 @@
         </is>
       </c>
       <c r="C858" t="n">
-        <v>940</v>
+        <v>964</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -30934,7 +30938,7 @@
         </is>
       </c>
       <c r="C859" t="n">
-        <v>955</v>
+        <v>979</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -30969,7 +30973,7 @@
         </is>
       </c>
       <c r="C860" t="n">
-        <v>963</v>
+        <v>987</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -31004,7 +31008,7 @@
         </is>
       </c>
       <c r="C861" t="n">
-        <v>974</v>
+        <v>998</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -31039,7 +31043,7 @@
         </is>
       </c>
       <c r="C862" t="n">
-        <v>990</v>
+        <v>1014</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -31078,7 +31082,7 @@
         </is>
       </c>
       <c r="C863" t="n">
-        <v>1019</v>
+        <v>1043</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -31113,7 +31117,7 @@
         </is>
       </c>
       <c r="C864" t="n">
-        <v>1037</v>
+        <v>1061</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -31148,7 +31152,7 @@
         </is>
       </c>
       <c r="C865" t="n">
-        <v>1043</v>
+        <v>1067</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -31183,7 +31187,7 @@
         </is>
       </c>
       <c r="C866" t="n">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -31218,7 +31222,7 @@
         </is>
       </c>
       <c r="C867" t="n">
-        <v>1071</v>
+        <v>1095</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -31260,7 +31264,7 @@
         </is>
       </c>
       <c r="C868" t="n">
-        <v>1131</v>
+        <v>1155</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -31687,7 +31691,7 @@
         </is>
       </c>
       <c r="C880" t="n">
-        <v>761</v>
+        <v>785</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -31722,7 +31726,7 @@
         </is>
       </c>
       <c r="C881" t="n">
-        <v>766</v>
+        <v>790</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -31757,7 +31761,7 @@
         </is>
       </c>
       <c r="C882" t="n">
-        <v>771</v>
+        <v>795</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -31993,7 +31997,7 @@
         </is>
       </c>
       <c r="C889" t="n">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -32029,7 +32033,7 @@
         </is>
       </c>
       <c r="C890" t="n">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -32063,7 +32067,7 @@
         </is>
       </c>
       <c r="C891" t="n">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -32095,7 +32099,7 @@
         </is>
       </c>
       <c r="C892" t="n">
-        <v>692</v>
+        <v>703</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -32127,7 +32131,7 @@
         </is>
       </c>
       <c r="C893" t="n">
-        <v>709</v>
+        <v>720</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -32142,7 +32146,15 @@
       </c>
       <c r="G893" s="2" t="inlineStr">
         <is>
-          <t>[00892] El trozo se lleva su parte: el kilo de lo que queda no se mueve.</t>
+          <t>[00892] El trozo se lleva su parte: el kilo de lo que queda no se mueve.
+Y no se mueve **de verdad**: el kilo manda y de él sale lo que cuesta
+la pieza, no al revés. Restando el trozo de lo que costaba la pieza,
+las dos cifras —lo que cuesta la pieza y lo que cuesta su kilo—
+dejaban de decir lo mismo, porque solo se tocaba una. La siguiente
+pesada las ponía de acuerdo cogiendo la de abajo, y el kilo de la
+pieza bajaba en una pesada que no había cambiado el peso. Nueve
+milésimas cada vez, siempre para abajo, siempre en la carne madurada,
+que es la cara.</t>
         </is>
       </c>
     </row>
@@ -32158,7 +32170,7 @@
         </is>
       </c>
       <c r="C894" t="n">
-        <v>752</v>
+        <v>776</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -32193,7 +32205,7 @@
         </is>
       </c>
       <c r="C895" t="n">
-        <v>843</v>
+        <v>867</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -32225,7 +32237,7 @@
         </is>
       </c>
       <c r="C896" t="n">
-        <v>887</v>
+        <v>911</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -32257,7 +32269,7 @@
         </is>
       </c>
       <c r="C897" t="n">
-        <v>891</v>
+        <v>915</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -32291,7 +32303,7 @@
         </is>
       </c>
       <c r="C898" t="n">
-        <v>1028</v>
+        <v>1052</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -32326,7 +32338,7 @@
         </is>
       </c>
       <c r="C899" t="n">
-        <v>1081</v>
+        <v>1105</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -56647,7 +56659,7 @@
         </is>
       </c>
       <c r="C1581" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="D1581" t="inlineStr">
         <is>
@@ -56680,7 +56692,7 @@
         </is>
       </c>
       <c r="C1582" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D1582" t="inlineStr">
         <is>
@@ -56715,7 +56727,7 @@
         </is>
       </c>
       <c r="C1583" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D1583" t="inlineStr">
         <is>
@@ -56752,7 +56764,7 @@
         </is>
       </c>
       <c r="C1584" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D1584" t="inlineStr">
         <is>
@@ -56784,7 +56796,7 @@
         </is>
       </c>
       <c r="C1585" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="D1585" t="inlineStr">
         <is>
@@ -56817,7 +56829,7 @@
         </is>
       </c>
       <c r="C1586" t="n">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D1586" t="inlineStr">
         <is>
@@ -56849,7 +56861,7 @@
         </is>
       </c>
       <c r="C1587" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="D1587" t="inlineStr">
         <is>
@@ -57729,8 +57741,478 @@
         </is>
       </c>
     </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>01613</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>thegrill/meat/app.py</t>
+        </is>
+      </c>
+      <c r="C1614" t="n">
+        <v>954</v>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1614" t="inlineStr"/>
+      <c r="F1614" s="2" t="inlineStr">
+        <is>
+          <t>El precio del kilo es de cada pieza y de nadie más: dos bolsas del mismo camión no valen lo mismo si una es MB9 y la otra MB6, y un precio de lote que se copia</t>
+        </is>
+      </c>
+      <c r="G1614" s="2" t="inlineStr">
+        <is>
+          <t>El precio del kilo es de cada pieza y de nadie más: dos bolsas del mismo
+camión no valen lo mismo si una es MB9 y la otra MB6, y un precio de lote
+que se copia a todas esconde justo esa diferencia. Del camión entero son
+el transporte y la aduana, que sí se reparten por igual a cada kilo que
+traía, y solo los hay cuando la carne es de importación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>01614</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>thegrill/meat/service.py</t>
+        </is>
+      </c>
+      <c r="C1615" t="n">
+        <v>343</v>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>función</t>
+        </is>
+      </c>
+      <c r="E1615" t="inlineStr">
+        <is>
+          <t>_puesto_en_camara</t>
+        </is>
+      </c>
+      <c r="F1615" s="2" t="inlineStr">
+        <is>
+          <t>Lo que cuesta el kilo de esa pieza puesto en la cámara.</t>
+        </is>
+      </c>
+      <c r="G1615" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lo que cuesta el kilo de esa pieza puesto en la cámara.
+    La carne no cuesta lo que dice la factura del proveedor: cuesta lo que
+    costó ponerla ahí. El precio del kilo es de cada pieza —dos bolsas del
+    mismo camión no valen lo mismo si una es MB9 y la otra MB6—, pero el
+    transporte y la aduana son del camión entero y se reparten por igual a
+    cada kilo que traía.
+    Un lote nacional no lleva ni lo uno ni lo otro y esto devuelve el precio a
+    secas. Una pieza sin precio sigue sin tenerlo: sumarle el flete a lo que no
+    se sabe lo que cuesta sería inventarse un coste, y la pieza tiene que
+    quedarse esperando a que dirección le ponga el suyo.
+    </t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>01615</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>thegrill/meat/service.py</t>
+        </is>
+      </c>
+      <c r="C1616" t="n">
+        <v>56</v>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1616" t="inlineStr"/>
+      <c r="F1616" s="2" t="inlineStr">
+        <is>
+          <t>Lo del camión, repartido a cada kilo de cada pieza: el transporte y la aduana.</t>
+        </is>
+      </c>
+      <c r="G1616" s="2" t="inlineStr">
+        <is>
+          <t>Lo del camión, repartido a cada kilo de cada pieza: el transporte y la
+aduana. Son de importación y casi nunca están, por eso van aparte del
+precio de la carne y no se exigen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>01616</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>thegrill/meat/service.py</t>
+        </is>
+      </c>
+      <c r="C1617" t="n">
+        <v>467</v>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1617" t="inlineStr"/>
+      <c r="F1617" s="2" t="inlineStr">
+        <is>
+          <t>Lo que se teclea aquí es el precio de la carne, que es lo que dice la factura del proveedor.</t>
+        </is>
+      </c>
+      <c r="G1617" s="2" t="inlineStr">
+        <is>
+          <t>Lo que se teclea aquí es el precio de la carne, que es lo que dice la
+factura del proveedor. Lo que costó traerla ya se apuntó en el muelle y
+sigue siendo suyo: el kilo puesto en la cámara es la suma de los tres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>01617</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>thegrill/models.py</t>
+        </is>
+      </c>
+      <c r="C1618" t="n">
+        <v>527</v>
+      </c>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1618" t="inlineStr"/>
+      <c r="F1618" s="2" t="inlineStr">
+        <is>
+          <t>Lo que cuesta el kilo **puesto en la cámara**: lo que se le pagó al proveedor más lo que costó traerlo.</t>
+        </is>
+      </c>
+      <c r="G1618" s="2" t="inlineStr">
+        <is>
+          <t>Lo que cuesta el kilo **puesto en la cámara**: lo que se le pagó al
+proveedor más lo que costó traerlo. Es el número que manda en todo lo que
+viene después —el despiece, el escandallo, el food cost—, porque la carne
+no cuesta lo que dice la factura del proveedor: cuesta lo que costó
+ponerla ahí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>01618</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>thegrill/models.py</t>
+        </is>
+      </c>
+      <c r="C1619" t="n">
+        <v>534</v>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1619" t="inlineStr"/>
+      <c r="F1619" s="2" t="inlineStr">
+        <is>
+          <t>Y de qué está hecho ese número, para poder verlo por separado.</t>
+        </is>
+      </c>
+      <c r="G1619" s="2" t="inlineStr">
+        <is>
+          <t>Y de qué está hecho ese número, para poder verlo por separado. El precio
+del kilo lo pone cada pieza; el transporte y la aduana son del camión
+entero y se reparten a todas por igual. Guardarlos sueltos es lo que
+permite contestar «¿me sale más caro el australiano por la carne o por el
+flete?», que es la pregunta que decide la siguiente compra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>01619</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>thegrill/web/aging.py</t>
+        </is>
+      </c>
+      <c r="C1620" t="n">
+        <v>466</v>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1620" t="inlineStr"/>
+      <c r="F1620" s="2" t="inlineStr">
+        <is>
+          <t>Y una pesada no abarata el kilo.</t>
+        </is>
+      </c>
+      <c r="G1620" s="2" t="inlineStr">
+        <is>
+          <t>Y una pesada no abarata el kilo. Nunca. Aquí solo se pesa lo que se
+evapora: los kilos bajan o se quedan, el coste no se mueve, así que
+la cuenta solo puede salir igual o más alta. Si sale más baja, lo que
+ha pasado no es que la carne valga menos: es que las dos cifras
+—lo que cuesta la pieza y lo que cuesta su kilo— se habían separado
+por el camino, y esta pesada estaba a punto de quedarse con la de
+abajo. Se planta el kilo y se recalcula la pieza desde él.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>01620</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>thegrill/meat/templates/base.html</t>
+        </is>
+      </c>
+      <c r="C1621" t="n">
+        <v>1514</v>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>plantilla</t>
+        </is>
+      </c>
+      <c r="E1621" t="inlineStr"/>
+      <c r="F1621" s="2" t="inlineStr">
+        <is>
+          <t>Cerrar el aviso de cookies sin perder el sitio.</t>
+        </is>
+      </c>
+      <c r="G1621" s="2" t="inlineStr">
+        <is>
+          <t>Cerrar el aviso de cookies sin perder el sitio.
+   El formulario sigue siendo un formulario de verdad: sin guiones se manda,
+   el servidor apunta la cookie y todo funciona como siempre. Es lo que no se
+   puede perder, porque es lo que hace que esto vaya en un teléfono viejo.
+   Pero mandar un formulario recarga, y recargar te sube al principio. Quien
+   iba por la mitad de la portada leyendo, pulsaba «entendido» y aparecía
+   arriba del todo sin saber por qué: se iba el aviso y se iba la página.
+   Con guiones se manda por detrás y la barra se esconde sola.
+   Y lo mismo con la equis de las ventanas: su enlace es `#`, que en un
+   navegador significa «al principio del documento». Cerrar la ventana de las
+   cookies te subía igual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>01621</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>thegrill/meat/templates/login.html</t>
+        </is>
+      </c>
+      <c r="C1622" t="n">
+        <v>33</v>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>plantilla</t>
+        </is>
+      </c>
+      <c r="E1622" t="inlineStr"/>
+      <c r="F1622" s="2" t="inlineStr">
+        <is>
+          <t>Los idiomas, en el pie.</t>
+        </is>
+      </c>
+      <c r="G1622" s="2" t="inlineStr">
+        <is>
+          <t>Los idiomas, en el pie. Aquí estaban repetidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>01622</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>thegrill/meat/templates/public_base.html</t>
+        </is>
+      </c>
+      <c r="C1623" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>plantilla</t>
+        </is>
+      </c>
+      <c r="E1623" t="inlineStr"/>
+      <c r="F1623" s="2" t="inlineStr">
+        <is>
+          <t>Los idiomas van en el pie y en ningún otro sitio: aquí había una tarjeta que los repetía, y en el móvil se veían los dos juegos seguidos.</t>
+        </is>
+      </c>
+      <c r="G1623" s="2" t="inlineStr">
+        <is>
+          <t>Los idiomas van en el pie y en ningún otro sitio: aquí había una tarjeta
+   que los repetía, y en el móvil se veían los dos juegos seguidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>01623</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>thegrill/meat/templates/public_shell.html</t>
+        </is>
+      </c>
+      <c r="C1624" t="n">
+        <v>455</v>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>plantilla</t>
+        </is>
+      </c>
+      <c r="E1624" t="inlineStr"/>
+      <c r="F1624" s="2" t="inlineStr">
+        <is>
+          <t>El único sitio donde se elige idioma en las pantallas públicas.</t>
+        </is>
+      </c>
+      <c r="G1624" s="2" t="inlineStr">
+        <is>
+          <t>El único sitio donde se elige idioma en las pantallas públicas. Lo
+         llevaba el pie desde siempre, y después se le puso además una tarjeta
+         a cada pantalla: desde el móvil salían los dos, uno encima del otro,
+         catorce botones para hacer lo mismo.
+         Y te deja donde estabas. Mandaba siempre a la portada, así que quien
+         comparaba el precio cambiaba a inglés y aparecía en otra pantalla
+         buscando dónde estaba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>01624</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>thegrill/meat/templates/public_shell.html</t>
+        </is>
+      </c>
+      <c r="C1625" t="n">
+        <v>594</v>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>plantilla</t>
+        </is>
+      </c>
+      <c r="E1625" t="inlineStr"/>
+      <c r="F1625" s="2" t="inlineStr">
+        <is>
+          <t>Cerrar el aviso de cookies sin perder el sitio.</t>
+        </is>
+      </c>
+      <c r="G1625" s="2" t="inlineStr">
+        <is>
+          <t>Cerrar el aviso de cookies sin perder el sitio.
+   El formulario sigue siendo un formulario de verdad: sin guiones se manda,
+   el servidor apunta la cookie y todo funciona como siempre. Es lo que no se
+   puede perder, porque es lo que hace que esto vaya en un teléfono viejo.
+   Pero mandar un formulario recarga, y recargar te sube al principio. Quien
+   iba por la mitad de la portada leyendo, pulsaba «entendido» y aparecía
+   arriba del todo sin saber por qué: se iba el aviso y se iba la página.
+   Con guiones se manda por detrás y la barra se esconde sola.
+   Y lo mismo con la equis de las ventanas: su enlace es `#`, que en un
+   navegador significa «al principio del documento». Cerrar la ventana de las
+   cookies te subía igual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>01625</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>thegrill/meat/templates/reception.html</t>
+        </is>
+      </c>
+      <c r="C1626" t="n">
+        <v>39</v>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>plantilla</t>
+        </is>
+      </c>
+      <c r="E1626" t="inlineStr"/>
+      <c r="F1626" s="2" t="inlineStr">
+        <is>
+          <t>El precio del kilo no está aquí a propósito: es de cada pieza.</t>
+        </is>
+      </c>
+      <c r="G1626" s="2" t="inlineStr">
+        <is>
+          <t>El precio del kilo no está aquí a propósito: es de cada pieza. Dos
+         bolsas del mismo camión no valen lo mismo si una es MB9 y la otra
+         MB6, y un precio de lote copiado a todas esconde justo eso. Lo que sí
+         es del camión entero —y solo si viene de fuera— es lo que costó
+         traerlo, que se reparte a cada kilo.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1613"/>
+  <autoFilter ref="A1:G1626"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -57741,7 +58223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -58039,7 +58521,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -58048,7 +58530,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>00417</t>
+          <t>01613</t>
         </is>
       </c>
     </row>
@@ -58239,7 +58721,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -58248,7 +58730,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>00651</t>
+          <t>01616</t>
         </is>
       </c>
     </row>
@@ -58339,7 +58821,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -58348,7 +58830,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>01553</t>
+          <t>01620</t>
         </is>
       </c>
     </row>
@@ -58475,7 +58957,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>thegrill/meat/templates/menu.html</t>
+          <t>thegrill/meat/templates/login.html</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -58483,19 +58965,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>01570</t>
+          <t>01621</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>01570</t>
+          <t>01621</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>thegrill/meat/templates/plate.html</t>
+          <t>thegrill/meat/templates/menu.html</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -58503,19 +58985,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>01571</t>
+          <t>01570</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>01571</t>
+          <t>01570</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>thegrill/meat/templates/prices.html</t>
+          <t>thegrill/meat/templates/plate.html</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -58523,119 +59005,119 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01572</t>
+          <t>01571</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>01572</t>
+          <t>01571</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>thegrill/meat/templates/public_pricing.html</t>
+          <t>thegrill/meat/templates/prices.html</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01573</t>
+          <t>01572</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>01574</t>
+          <t>01572</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>thegrill/meat/templates/public_shell.html</t>
+          <t>thegrill/meat/templates/public_base.html</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01575</t>
+          <t>01622</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>01576</t>
+          <t>01622</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>thegrill/meat/templates/reception.html</t>
+          <t>thegrill/meat/templates/public_pricing.html</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01577</t>
+          <t>01573</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>01586</t>
+          <t>01574</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>thegrill/meat/templates/report.html</t>
+          <t>thegrill/meat/templates/public_shell.html</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>01587</t>
+          <t>01575</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>01587</t>
+          <t>01624</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>thegrill/meat/templates/team.html</t>
+          <t>thegrill/meat/templates/reception.html</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01588</t>
+          <t>01577</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>01588</t>
+          <t>01625</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>thegrill/meat/templates/transfers.html</t>
+          <t>thegrill/meat/templates/report.html</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -58643,877 +59125,917 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01589</t>
+          <t>01587</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>01589</t>
+          <t>01587</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>thegrill/meat/tours.py</t>
+          <t>thegrill/meat/templates/team.html</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>00668</t>
+          <t>01588</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>00680</t>
+          <t>01588</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>thegrill/meat/tutorial.py</t>
+          <t>thegrill/meat/templates/transfers.html</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>00681</t>
+          <t>01589</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>00686</t>
+          <t>01589</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>thegrill/models.py</t>
+          <t>thegrill/meat/tours.py</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>00668</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>00778</t>
+          <t>00680</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>thegrill/orchestrator/chain.py</t>
+          <t>thegrill/meat/tutorial.py</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>00681</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>00801</t>
+          <t>00686</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>thegrill/reports/__init__.py</t>
+          <t>thegrill/models.py</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>00802</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>00802</t>
+          <t>01618</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>thegrill/rules.py</t>
+          <t>thegrill/orchestrator/chain.py</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>00803</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>00823</t>
+          <t>00801</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>thegrill/version.py</t>
+          <t>thegrill/reports/__init__.py</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>00824</t>
+          <t>00802</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>00826</t>
+          <t>00802</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>thegrill/web/__init__.py</t>
+          <t>thegrill/rules.py</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>00827</t>
+          <t>00803</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>00827</t>
+          <t>00823</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>thegrill/web/aging.py</t>
+          <t>thegrill/version.py</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>00828</t>
+          <t>00824</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>00898</t>
+          <t>00826</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>thegrill/web/app.py</t>
+          <t>thegrill/web/__init__.py</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>00899</t>
+          <t>00827</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>00993</t>
+          <t>00827</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>thegrill/web/auth.py</t>
+          <t>thegrill/web/aging.py</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>00994</t>
+          <t>00828</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>01016</t>
+          <t>01619</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>thegrill/web/butchery.py</t>
+          <t>thegrill/web/app.py</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>01017</t>
+          <t>00899</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>01052</t>
+          <t>00993</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>thegrill/web/caducidad.py</t>
+          <t>thegrill/web/auth.py</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>01053</t>
+          <t>00994</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>01058</t>
+          <t>01016</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>thegrill/web/cifras.py</t>
+          <t>thegrill/web/butchery.py</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>01059</t>
+          <t>01017</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>01065</t>
+          <t>01052</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>thegrill/web/costing.py</t>
+          <t>thegrill/web/caducidad.py</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>01066</t>
+          <t>01053</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>01093</t>
+          <t>01058</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>thegrill/web/cuadre.py</t>
+          <t>thegrill/web/cifras.py</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>01094</t>
+          <t>01059</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>01124</t>
+          <t>01065</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>thegrill/web/defrost.py</t>
+          <t>thegrill/web/costing.py</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>01125</t>
+          <t>01066</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>01169</t>
+          <t>01093</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>thegrill/web/exacto.py</t>
+          <t>thegrill/web/cuadre.py</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>01170</t>
+          <t>01094</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>01193</t>
+          <t>01124</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>thegrill/web/fc.py</t>
+          <t>thegrill/web/defrost.py</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>01194</t>
+          <t>01125</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>01209</t>
+          <t>01169</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>thegrill/web/i18n.py</t>
+          <t>thegrill/web/exacto.py</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>01210</t>
+          <t>01170</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>01249</t>
+          <t>01193</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>thegrill/web/inventory.py</t>
+          <t>thegrill/web/fc.py</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>01250</t>
+          <t>01194</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>01286</t>
+          <t>01209</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>thegrill/web/jornada.py</t>
+          <t>thegrill/web/i18n.py</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>01287</t>
+          <t>01210</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>01299</t>
+          <t>01249</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>thegrill/web/locking.py</t>
+          <t>thegrill/web/inventory.py</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>01300</t>
+          <t>01250</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>01305</t>
+          <t>01286</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>thegrill/web/money.py</t>
+          <t>thegrill/web/jornada.py</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>01306</t>
+          <t>01287</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>01309</t>
+          <t>01299</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>thegrill/web/pesos.py</t>
+          <t>thegrill/web/locking.py</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>01310</t>
+          <t>01300</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>01323</t>
+          <t>01305</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>thegrill/web/pos_import.py</t>
+          <t>thegrill/web/money.py</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>01324</t>
+          <t>01306</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>01350</t>
+          <t>01309</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>thegrill/web/rangos.py</t>
+          <t>thegrill/web/pesos.py</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>01351</t>
+          <t>01310</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>01367</t>
+          <t>01323</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>thegrill/web/seed.py</t>
+          <t>thegrill/web/pos_import.py</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>01368</t>
+          <t>01324</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>01370</t>
+          <t>01350</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>thegrill/web/seguridad.py</t>
+          <t>thegrill/web/rangos.py</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>01371</t>
+          <t>01351</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>01376</t>
+          <t>01367</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>thegrill/web/service.py</t>
+          <t>thegrill/web/seed.py</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>01377</t>
+          <t>01368</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>01396</t>
+          <t>01370</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>thegrill/web/sheets.py</t>
+          <t>thegrill/web/seguridad.py</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>01397</t>
+          <t>01371</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>01414</t>
+          <t>01376</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>thegrill/web/sites.py</t>
+          <t>thegrill/web/service.py</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>01415</t>
+          <t>01377</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>01445</t>
+          <t>01396</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>thegrill/web/templates/_peso.html</t>
+          <t>thegrill/web/sheets.py</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>01590</t>
+          <t>01397</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>01590</t>
+          <t>01414</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>thegrill/web/templates/error.html</t>
+          <t>thegrill/web/sites.py</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>01591</t>
+          <t>01415</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>01591</t>
+          <t>01445</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>thegrill/web/templates/ingredient_detail.html</t>
+          <t>thegrill/web/templates/_peso.html</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>01592</t>
+          <t>01590</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>01593</t>
+          <t>01590</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>thegrill/web/templates/inventory.html</t>
+          <t>thegrill/web/templates/error.html</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>01594</t>
+          <t>01591</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>01595</t>
+          <t>01591</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>thegrill/web/templates/recipe_detail.html</t>
+          <t>thegrill/web/templates/ingredient_detail.html</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>01596</t>
+          <t>01592</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>01596</t>
+          <t>01593</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>thegrill/web/templates/settings.html</t>
+          <t>thegrill/web/templates/inventory.html</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>01597</t>
+          <t>01594</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>01601</t>
+          <t>01595</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>thegrill/web/templates/tracing.html</t>
+          <t>thegrill/web/templates/recipe_detail.html</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>01602</t>
+          <t>01596</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>01611</t>
+          <t>01596</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>thegrill/web/templates/waste.html</t>
+          <t>thegrill/web/templates/settings.html</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>01612</t>
+          <t>01597</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>01612</t>
+          <t>01601</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>thegrill/web/tracing.py</t>
+          <t>thegrill/web/templates/tracing.html</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>01446</t>
+          <t>01602</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>01506</t>
+          <t>01611</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>thegrill/web/twofactor.py</t>
+          <t>thegrill/web/templates/waste.html</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>01507</t>
+          <t>01612</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>01516</t>
+          <t>01612</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>thegrill/web/tracing.py</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>61</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>01446</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>01506</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>thegrill/web/twofactor.py</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>10</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>01507</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>01516</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>thegrill/web/waste.py</t>
         </is>
       </c>
-      <c r="B88" t="n">
+      <c r="B90" t="n">
         <v>18</v>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>01517</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>01534</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D88"/>
+  <autoFilter ref="A1:D90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/COMENTARIOS.xlsx
+++ b/COMENTARIOS.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Por fichero" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comentarios'!$A$1:$G$1626</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por fichero'!$A$1:$D$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comentarios'!$A$1:$G$1648</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por fichero'!$A$1:$D$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1626"/>
+  <dimension ref="A1:G1648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>509</v>
+        <v>528</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>553</v>
+        <v>572</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>565</v>
+        <v>584</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>592</v>
+        <v>611</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>613</v>
+        <v>632</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>628</v>
+        <v>647</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>635</v>
+        <v>654</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>643</v>
+        <v>662</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>651</v>
+        <v>670</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>683</v>
+        <v>702</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>697</v>
+        <v>716</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>706</v>
+        <v>725</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>739</v>
+        <v>758</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>749</v>
+        <v>768</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>762</v>
+        <v>781</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>799</v>
+        <v>818</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>808</v>
+        <v>827</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>814</v>
+        <v>833</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>820</v>
+        <v>839</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>826</v>
+        <v>845</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>833</v>
+        <v>852</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>848</v>
+        <v>867</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>895</v>
+        <v>914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>903</v>
+        <v>922</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>918</v>
+        <v>937</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>938</v>
+        <v>957</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1037</v>
+        <v>1056</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>1064</v>
+        <v>1083</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>1078</v>
+        <v>1097</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1085</v>
+        <v>1104</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>1091</v>
+        <v>1110</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>1102</v>
+        <v>1121</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>1141</v>
+        <v>1160</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>1151</v>
+        <v>1170</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>1174</v>
+        <v>1193</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>1245</v>
+        <v>1264</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1279</v>
+        <v>1298</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>1295</v>
+        <v>1314</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1319</v>
+        <v>1338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>1335</v>
+        <v>1354</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>1351</v>
+        <v>1370</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>1359</v>
+        <v>1378</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>1367</v>
+        <v>1386</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>1398</v>
+        <v>1417</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>1439</v>
+        <v>1458</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>1459</v>
+        <v>1478</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>1477</v>
+        <v>1496</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>1486</v>
+        <v>1505</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>1522</v>
+        <v>1541</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>1543</v>
+        <v>1562</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>1565</v>
+        <v>1584</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>1601</v>
+        <v>1620</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>1641</v>
+        <v>1660</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>1662</v>
+        <v>1681</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>1668</v>
+        <v>1687</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>1688</v>
+        <v>1707</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>1712</v>
+        <v>1731</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>1736</v>
+        <v>1755</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>1762</v>
+        <v>1781</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>1774</v>
+        <v>1793</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>1791</v>
+        <v>1810</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>1805</v>
+        <v>1824</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>1822</v>
+        <v>1841</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>1846</v>
+        <v>1865</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>1871</v>
+        <v>1890</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>1885</v>
+        <v>1904</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>1905</v>
+        <v>1924</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>1920</v>
+        <v>1939</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>1933</v>
+        <v>1952</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>1951</v>
+        <v>1970</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>1966</v>
+        <v>1985</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>1983</v>
+        <v>2002</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>1996</v>
+        <v>2015</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>2008</v>
+        <v>2027</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>2023</v>
+        <v>2042</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>2039</v>
+        <v>2058</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>2054</v>
+        <v>2073</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>2075</v>
+        <v>2094</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>2082</v>
+        <v>2101</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>2103</v>
+        <v>2122</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>2134</v>
+        <v>2153</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>2190</v>
+        <v>2209</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>2220</v>
+        <v>2239</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>2236</v>
+        <v>2255</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>2258</v>
+        <v>2277</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>2299</v>
+        <v>2318</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>2314</v>
+        <v>2333</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>2330</v>
+        <v>2349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>2349</v>
+        <v>2368</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>2367</v>
+        <v>2386</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>2379</v>
+        <v>2398</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>2392</v>
+        <v>2411</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>2437</v>
+        <v>2456</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>2456</v>
+        <v>2475</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>2483</v>
+        <v>2502</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>2510</v>
+        <v>2529</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>2537</v>
+        <v>2556</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>2547</v>
+        <v>2566</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>2559</v>
+        <v>2578</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>2570</v>
+        <v>2589</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>2581</v>
+        <v>2600</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>2616</v>
+        <v>2635</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>2643</v>
+        <v>2662</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>2662</v>
+        <v>2681</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>2676</v>
+        <v>2695</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>2700</v>
+        <v>2719</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2718</v>
+        <v>2737</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>2735</v>
+        <v>2754</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>2750</v>
+        <v>2769</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>2776</v>
+        <v>2795</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>2792</v>
+        <v>2811</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>2804</v>
+        <v>2823</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>2822</v>
+        <v>2841</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>2854</v>
+        <v>2873</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>2872</v>
+        <v>2891</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>2900</v>
+        <v>2920</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>2956</v>
+        <v>2989</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>2974</v>
+        <v>3007</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>2996</v>
+        <v>3029</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>3013</v>
+        <v>3046</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>3037</v>
+        <v>3070</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>3062</v>
+        <v>3095</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>3074</v>
+        <v>3107</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>3092</v>
+        <v>3125</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>3104</v>
+        <v>3137</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>3119</v>
+        <v>3152</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>3143</v>
+        <v>3176</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>3151</v>
+        <v>3184</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>3169</v>
+        <v>3202</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>3178</v>
+        <v>3211</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>3192</v>
+        <v>3225</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>3207</v>
+        <v>3240</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>3385</v>
+        <v>3418</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>3402</v>
+        <v>3435</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>3415</v>
+        <v>3448</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>3420</v>
+        <v>3453</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>659</v>
+        <v>678</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>2836</v>
+        <v>2855</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>437</v>
+        <v>456</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>533</v>
+        <v>552</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>712</v>
+        <v>731</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>727</v>
+        <v>746</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>773</v>
+        <v>792</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>867</v>
+        <v>886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>881</v>
+        <v>900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>902</v>
+        <v>921</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>927</v>
+        <v>946</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>949</v>
+        <v>968</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>961</v>
+        <v>980</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>971</v>
+        <v>990</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>982</v>
+        <v>1001</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>1007</v>
+        <v>1026</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>1016</v>
+        <v>1035</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>1021</v>
+        <v>1040</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>1028</v>
+        <v>1047</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>1049</v>
+        <v>1068</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>1114</v>
+        <v>1133</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>1148</v>
+        <v>1167</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>1179</v>
+        <v>1198</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>1190</v>
+        <v>1209</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>1197</v>
+        <v>1216</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>1223</v>
+        <v>1242</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>1229</v>
+        <v>1248</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>1342</v>
+        <v>1361</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>1374</v>
+        <v>1393</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>1406</v>
+        <v>1425</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>1412</v>
+        <v>1431</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>1484</v>
+        <v>1503</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>1495</v>
+        <v>1514</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>1548</v>
+        <v>1567</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>1575</v>
+        <v>1594</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>1745</v>
+        <v>1764</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>2091</v>
+        <v>2110</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>2143</v>
+        <v>2162</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>2159</v>
+        <v>2178</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>2196</v>
+        <v>2215</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>2267</v>
+        <v>2286</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>2274</v>
+        <v>2293</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>2353</v>
+        <v>2372</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>2407</v>
+        <v>2426</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>2414</v>
+        <v>2433</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>2427</v>
+        <v>2446</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>2470</v>
+        <v>2489</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>2723</v>
+        <v>2742</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>2762</v>
+        <v>2781</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>2811</v>
+        <v>2830</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>2852</v>
+        <v>2871</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>2860</v>
+        <v>2879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>2914</v>
+        <v>2947</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>2931</v>
+        <v>2964</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>2985</v>
+        <v>3018</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>3018</v>
+        <v>3051</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>3042</v>
+        <v>3075</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>3057</v>
+        <v>3090</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>3217</v>
+        <v>3250</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>5052</v>
+        <v>5101</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>1409</v>
+        <v>1423</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>1443</v>
+        <v>1457</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>1460</v>
+        <v>1474</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>2127</v>
+        <v>2148</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>2161</v>
+        <v>2182</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>2178</v>
+        <v>2199</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>2845</v>
+        <v>2873</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>2879</v>
+        <v>2907</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>2896</v>
+        <v>2924</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>3563</v>
+        <v>3598</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>3597</v>
+        <v>3632</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>3614</v>
+        <v>3649</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>4281</v>
+        <v>4323</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>4315</v>
+        <v>4357</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>4334</v>
+        <v>4376</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>5001</v>
+        <v>5050</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>5035</v>
+        <v>5084</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         </is>
       </c>
       <c r="C607" t="n">
-        <v>1123</v>
+        <v>1142</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         </is>
       </c>
       <c r="C608" t="n">
-        <v>1163</v>
+        <v>1225</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         </is>
       </c>
       <c r="C609" t="n">
-        <v>1176</v>
+        <v>1238</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         </is>
       </c>
       <c r="C610" t="n">
-        <v>1191</v>
+        <v>1253</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         </is>
       </c>
       <c r="C611" t="n">
-        <v>1215</v>
+        <v>1277</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         </is>
       </c>
       <c r="C618" t="n">
-        <v>1106</v>
+        <v>1125</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="C619" t="n">
-        <v>1111</v>
+        <v>1130</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         </is>
       </c>
       <c r="C620" t="n">
-        <v>1116</v>
+        <v>1135</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         </is>
       </c>
       <c r="C621" t="n">
-        <v>1266</v>
+        <v>1328</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         </is>
       </c>
       <c r="C645" t="n">
-        <v>1127</v>
+        <v>1146</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         </is>
       </c>
       <c r="C646" t="n">
-        <v>1184</v>
+        <v>1246</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         </is>
       </c>
       <c r="C647" t="n">
-        <v>1226</v>
+        <v>1288</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         </is>
       </c>
       <c r="C648" t="n">
-        <v>1237</v>
+        <v>1299</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="C649" t="n">
-        <v>1240</v>
+        <v>1302</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         </is>
       </c>
       <c r="C650" t="n">
-        <v>1245</v>
+        <v>1307</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         </is>
       </c>
       <c r="C651" t="n">
-        <v>1256</v>
+        <v>1318</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         </is>
       </c>
       <c r="C652" t="n">
-        <v>1260</v>
+        <v>1322</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         </is>
       </c>
       <c r="C700" t="n">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         </is>
       </c>
       <c r="C701" t="n">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         </is>
       </c>
       <c r="C702" t="n">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         </is>
       </c>
       <c r="C703" t="n">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         </is>
       </c>
       <c r="C704" t="n">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         </is>
       </c>
       <c r="C705" t="n">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         </is>
       </c>
       <c r="C706" t="n">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         </is>
       </c>
       <c r="C707" t="n">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         </is>
       </c>
       <c r="C708" t="n">
-        <v>817</v>
+        <v>826</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         </is>
       </c>
       <c r="C709" t="n">
-        <v>864</v>
+        <v>873</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         </is>
       </c>
       <c r="C710" t="n">
-        <v>887</v>
+        <v>896</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         </is>
       </c>
       <c r="C711" t="n">
-        <v>936</v>
+        <v>945</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         </is>
       </c>
       <c r="C712" t="n">
-        <v>953</v>
+        <v>962</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         </is>
       </c>
       <c r="C713" t="n">
-        <v>981</v>
+        <v>990</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         </is>
       </c>
       <c r="C714" t="n">
-        <v>1019</v>
+        <v>1028</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         </is>
       </c>
       <c r="C715" t="n">
-        <v>1050</v>
+        <v>1059</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         </is>
       </c>
       <c r="C716" t="n">
-        <v>1079</v>
+        <v>1088</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         </is>
       </c>
       <c r="C717" t="n">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         </is>
       </c>
       <c r="C718" t="n">
-        <v>1127</v>
+        <v>1136</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         </is>
       </c>
       <c r="C719" t="n">
-        <v>1159</v>
+        <v>1168</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         </is>
       </c>
       <c r="C720" t="n">
-        <v>1178</v>
+        <v>1187</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         </is>
       </c>
       <c r="C721" t="n">
-        <v>1214</v>
+        <v>1223</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         </is>
       </c>
       <c r="C722" t="n">
-        <v>1238</v>
+        <v>1247</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         </is>
       </c>
       <c r="C723" t="n">
-        <v>1264</v>
+        <v>1273</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         </is>
       </c>
       <c r="C724" t="n">
-        <v>1296</v>
+        <v>1305</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         </is>
       </c>
       <c r="C725" t="n">
-        <v>1314</v>
+        <v>1323</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         </is>
       </c>
       <c r="C726" t="n">
-        <v>1337</v>
+        <v>1346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         </is>
       </c>
       <c r="C727" t="n">
-        <v>1369</v>
+        <v>1378</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         </is>
       </c>
       <c r="C728" t="n">
-        <v>1396</v>
+        <v>1405</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         </is>
       </c>
       <c r="C729" t="n">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         </is>
       </c>
       <c r="C731" t="n">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         </is>
       </c>
       <c r="C732" t="n">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         </is>
       </c>
       <c r="C733" t="n">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         </is>
       </c>
       <c r="C734" t="n">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -26727,7 +26727,7 @@
         </is>
       </c>
       <c r="C740" t="n">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         </is>
       </c>
       <c r="C741" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         </is>
       </c>
       <c r="C742" t="n">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         </is>
       </c>
       <c r="C743" t="n">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         </is>
       </c>
       <c r="C744" t="n">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         </is>
       </c>
       <c r="C745" t="n">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         </is>
       </c>
       <c r="C746" t="n">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         </is>
       </c>
       <c r="C747" t="n">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         </is>
       </c>
       <c r="C748" t="n">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="C749" t="n">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         </is>
       </c>
       <c r="C750" t="n">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         </is>
       </c>
       <c r="C751" t="n">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         </is>
       </c>
       <c r="C752" t="n">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         </is>
       </c>
       <c r="C753" t="n">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         </is>
       </c>
       <c r="C754" t="n">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="C755" t="n">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         </is>
       </c>
       <c r="C756" t="n">
-        <v>693</v>
+        <v>702</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -27290,7 +27290,7 @@
         </is>
       </c>
       <c r="C757" t="n">
-        <v>834</v>
+        <v>843</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         </is>
       </c>
       <c r="C758" t="n">
-        <v>838</v>
+        <v>847</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         </is>
       </c>
       <c r="C759" t="n">
-        <v>842</v>
+        <v>851</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         </is>
       </c>
       <c r="C760" t="n">
-        <v>908</v>
+        <v>917</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         </is>
       </c>
       <c r="C761" t="n">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         </is>
       </c>
       <c r="C762" t="n">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         </is>
       </c>
       <c r="C763" t="n">
-        <v>919</v>
+        <v>928</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         </is>
       </c>
       <c r="C764" t="n">
-        <v>925</v>
+        <v>934</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         </is>
       </c>
       <c r="C765" t="n">
-        <v>967</v>
+        <v>976</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         </is>
       </c>
       <c r="C766" t="n">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         </is>
       </c>
       <c r="C767" t="n">
-        <v>989</v>
+        <v>998</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         </is>
       </c>
       <c r="C768" t="n">
-        <v>1021</v>
+        <v>1030</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         </is>
       </c>
       <c r="C769" t="n">
-        <v>1039</v>
+        <v>1048</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         </is>
       </c>
       <c r="C770" t="n">
-        <v>1042</v>
+        <v>1051</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         </is>
       </c>
       <c r="C771" t="n">
-        <v>1065</v>
+        <v>1074</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         </is>
       </c>
       <c r="C772" t="n">
-        <v>1070</v>
+        <v>1079</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         </is>
       </c>
       <c r="C773" t="n">
-        <v>1134</v>
+        <v>1143</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         </is>
       </c>
       <c r="C774" t="n">
-        <v>1194</v>
+        <v>1203</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         </is>
       </c>
       <c r="C775" t="n">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -27916,7 +27916,7 @@
         </is>
       </c>
       <c r="C776" t="n">
-        <v>1350</v>
+        <v>1359</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         </is>
       </c>
       <c r="C777" t="n">
-        <v>1355</v>
+        <v>1364</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         </is>
       </c>
       <c r="C778" t="n">
-        <v>1361</v>
+        <v>1370</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         </is>
       </c>
       <c r="C779" t="n">
-        <v>1415</v>
+        <v>1424</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         </is>
       </c>
       <c r="C908" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         </is>
       </c>
       <c r="C909" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         </is>
       </c>
       <c r="C910" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         </is>
       </c>
       <c r="C911" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         </is>
       </c>
       <c r="C912" t="n">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         </is>
       </c>
       <c r="C913" t="n">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         </is>
       </c>
       <c r="C914" t="n">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         </is>
       </c>
       <c r="C915" t="n">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         </is>
       </c>
       <c r="C916" t="n">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         </is>
       </c>
       <c r="C917" t="n">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         </is>
       </c>
       <c r="C918" t="n">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         </is>
       </c>
       <c r="C919" t="n">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         </is>
       </c>
       <c r="C920" t="n">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -33120,7 +33120,7 @@
         </is>
       </c>
       <c r="C921" t="n">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         </is>
       </c>
       <c r="C922" t="n">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         </is>
       </c>
       <c r="C923" t="n">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         </is>
       </c>
       <c r="C924" t="n">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         </is>
       </c>
       <c r="C925" t="n">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         </is>
       </c>
       <c r="C926" t="n">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         </is>
       </c>
       <c r="C927" t="n">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         </is>
       </c>
       <c r="C928" t="n">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         </is>
       </c>
       <c r="C929" t="n">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         </is>
       </c>
       <c r="C930" t="n">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         </is>
       </c>
       <c r="C931" t="n">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         </is>
       </c>
       <c r="C932" t="n">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         </is>
       </c>
       <c r="C933" t="n">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -33576,7 +33576,7 @@
         </is>
       </c>
       <c r="C934" t="n">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         </is>
       </c>
       <c r="C935" t="n">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         </is>
       </c>
       <c r="C936" t="n">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         </is>
       </c>
       <c r="C937" t="n">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         </is>
       </c>
       <c r="C938" t="n">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         </is>
       </c>
       <c r="C939" t="n">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         </is>
       </c>
       <c r="C940" t="n">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         </is>
       </c>
       <c r="C941" t="n">
-        <v>631</v>
+        <v>642</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         </is>
       </c>
       <c r="C942" t="n">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         </is>
       </c>
       <c r="C943" t="n">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="C944" t="n">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         </is>
       </c>
       <c r="C945" t="n">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         </is>
       </c>
       <c r="C946" t="n">
-        <v>729</v>
+        <v>740</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         </is>
       </c>
       <c r="C947" t="n">
-        <v>739</v>
+        <v>750</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         </is>
       </c>
       <c r="C948" t="n">
-        <v>752</v>
+        <v>763</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         </is>
       </c>
       <c r="C949" t="n">
-        <v>763</v>
+        <v>774</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         </is>
       </c>
       <c r="C950" t="n">
-        <v>783</v>
+        <v>794</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         </is>
       </c>
       <c r="C951" t="n">
-        <v>802</v>
+        <v>813</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         </is>
       </c>
       <c r="C952" t="n">
-        <v>823</v>
+        <v>834</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         </is>
       </c>
       <c r="C953" t="n">
-        <v>842</v>
+        <v>853</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         </is>
       </c>
       <c r="C954" t="n">
-        <v>861</v>
+        <v>872</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -34321,7 +34321,7 @@
         </is>
       </c>
       <c r="C955" t="n">
-        <v>879</v>
+        <v>890</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         </is>
       </c>
       <c r="C956" t="n">
-        <v>894</v>
+        <v>905</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         </is>
       </c>
       <c r="C957" t="n">
-        <v>932</v>
+        <v>943</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         </is>
       </c>
       <c r="C958" t="n">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         </is>
       </c>
       <c r="C959" t="n">
-        <v>968</v>
+        <v>979</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         </is>
       </c>
       <c r="C960" t="n">
-        <v>991</v>
+        <v>1002</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         </is>
       </c>
       <c r="C961" t="n">
-        <v>1020</v>
+        <v>1031</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         </is>
       </c>
       <c r="C962" t="n">
-        <v>1051</v>
+        <v>1062</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         </is>
       </c>
       <c r="C963" t="n">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         </is>
       </c>
       <c r="C964" t="n">
-        <v>1080</v>
+        <v>1091</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         </is>
       </c>
       <c r="C965" t="n">
-        <v>1103</v>
+        <v>1114</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         </is>
       </c>
       <c r="C966" t="n">
-        <v>1133</v>
+        <v>1144</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         </is>
       </c>
       <c r="C967" t="n">
-        <v>1142</v>
+        <v>1153</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         </is>
       </c>
       <c r="C968" t="n">
-        <v>1152</v>
+        <v>1163</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
         </is>
       </c>
       <c r="C969" t="n">
-        <v>1165</v>
+        <v>1176</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         </is>
       </c>
       <c r="C970" t="n">
-        <v>1184</v>
+        <v>1195</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         </is>
       </c>
       <c r="C971" t="n">
-        <v>1207</v>
+        <v>1218</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -34920,7 +34920,7 @@
         </is>
       </c>
       <c r="C972" t="n">
-        <v>1263</v>
+        <v>1274</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         </is>
       </c>
       <c r="C973" t="n">
-        <v>1285</v>
+        <v>1296</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         </is>
       </c>
       <c r="C974" t="n">
-        <v>1308</v>
+        <v>1319</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         </is>
       </c>
       <c r="C975" t="n">
-        <v>1321</v>
+        <v>1332</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         </is>
       </c>
       <c r="C976" t="n">
-        <v>1336</v>
+        <v>1347</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         </is>
       </c>
       <c r="C977" t="n">
-        <v>1354</v>
+        <v>1365</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         </is>
       </c>
       <c r="C978" t="n">
-        <v>1359</v>
+        <v>1370</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         </is>
       </c>
       <c r="C987" t="n">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         </is>
       </c>
       <c r="C988" t="n">
-        <v>662</v>
+        <v>673</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         </is>
       </c>
       <c r="C989" t="n">
-        <v>700</v>
+        <v>711</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         </is>
       </c>
       <c r="C990" t="n">
-        <v>846</v>
+        <v>857</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         </is>
       </c>
       <c r="C991" t="n">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         </is>
       </c>
       <c r="C992" t="n">
-        <v>1028</v>
+        <v>1039</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         </is>
       </c>
       <c r="C993" t="n">
-        <v>1036</v>
+        <v>1047</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         </is>
       </c>
       <c r="C994" t="n">
-        <v>1238</v>
+        <v>1249</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -56894,7 +56894,7 @@
         </is>
       </c>
       <c r="C1588" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="D1588" t="inlineStr">
         <is>
@@ -57295,7 +57295,7 @@
         </is>
       </c>
       <c r="C1600" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D1600" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         </is>
       </c>
       <c r="C1601" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D1601" t="inlineStr">
         <is>
@@ -57360,7 +57360,7 @@
         </is>
       </c>
       <c r="C1602" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D1602" t="inlineStr">
         <is>
@@ -57490,7 +57490,7 @@
         </is>
       </c>
       <c r="C1606" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D1606" t="inlineStr">
         <is>
@@ -57525,7 +57525,7 @@
         </is>
       </c>
       <c r="C1607" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D1607" t="inlineStr">
         <is>
@@ -57558,7 +57558,7 @@
         </is>
       </c>
       <c r="C1608" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D1608" t="inlineStr">
         <is>
@@ -57591,7 +57591,7 @@
         </is>
       </c>
       <c r="C1609" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D1609" t="inlineStr">
         <is>
@@ -57622,7 +57622,7 @@
         </is>
       </c>
       <c r="C1610" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D1610" t="inlineStr">
         <is>
@@ -57655,7 +57655,7 @@
         </is>
       </c>
       <c r="C1611" t="n">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="D1611" t="inlineStr">
         <is>
@@ -57688,7 +57688,7 @@
         </is>
       </c>
       <c r="C1612" t="n">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="D1612" t="inlineStr">
         <is>
@@ -57753,7 +57753,7 @@
         </is>
       </c>
       <c r="C1614" t="n">
-        <v>954</v>
+        <v>973</v>
       </c>
       <c r="D1614" t="inlineStr">
         <is>
@@ -57763,12 +57763,12 @@
       <c r="E1614" t="inlineStr"/>
       <c r="F1614" s="2" t="inlineStr">
         <is>
-          <t>El precio del kilo es de cada pieza y de nadie más: dos bolsas del mismo camión no valen lo mismo si una es MB9 y la otra MB6, y un precio de lote que se copia</t>
+          <t>[01613] El precio del kilo es de cada pieza y de nadie más: dos bolsas del mismo camión no valen lo mismo si una es MB9 y la otra MB6, y un precio de lote que s</t>
         </is>
       </c>
       <c r="G1614" s="2" t="inlineStr">
         <is>
-          <t>El precio del kilo es de cada pieza y de nadie más: dos bolsas del mismo
+          <t>[01613] El precio del kilo es de cada pieza y de nadie más: dos bolsas del mismo
 camión no valen lo mismo si una es MB9 y la otra MB6, y un precio de lote
 que se copia a todas esconde justo esa diferencia. Del camión entero son
 el transporte y la aduana, que sí se reparten por igual a cada kilo que
@@ -57802,12 +57802,12 @@
       </c>
       <c r="F1615" s="2" t="inlineStr">
         <is>
-          <t>Lo que cuesta el kilo de esa pieza puesto en la cámara.</t>
+          <t>[01614] Lo que cuesta el kilo de esa pieza puesto en la cámara.</t>
         </is>
       </c>
       <c r="G1615" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lo que cuesta el kilo de esa pieza puesto en la cámara.
+          <t xml:space="preserve">[01614] Lo que cuesta el kilo de esa pieza puesto en la cámara.
     La carne no cuesta lo que dice la factura del proveedor: cuesta lo que
     costó ponerla ahí. El precio del kilo es de cada pieza —dos bolsas del
     mismo camión no valen lo mismo si una es MB9 y la otra MB6—, pero el
@@ -57843,12 +57843,12 @@
       <c r="E1616" t="inlineStr"/>
       <c r="F1616" s="2" t="inlineStr">
         <is>
-          <t>Lo del camión, repartido a cada kilo de cada pieza: el transporte y la aduana.</t>
+          <t>[01615] Lo del camión, repartido a cada kilo de cada pieza: el transporte y la aduana.</t>
         </is>
       </c>
       <c r="G1616" s="2" t="inlineStr">
         <is>
-          <t>Lo del camión, repartido a cada kilo de cada pieza: el transporte y la
+          <t>[01615] Lo del camión, repartido a cada kilo de cada pieza: el transporte y la
 aduana. Son de importación y casi nunca están, por eso van aparte del
 precio de la carne y no se exigen.</t>
         </is>
@@ -57876,12 +57876,12 @@
       <c r="E1617" t="inlineStr"/>
       <c r="F1617" s="2" t="inlineStr">
         <is>
-          <t>Lo que se teclea aquí es el precio de la carne, que es lo que dice la factura del proveedor.</t>
+          <t>[01616] Lo que se teclea aquí es el precio de la carne, que es lo que dice la factura del proveedor.</t>
         </is>
       </c>
       <c r="G1617" s="2" t="inlineStr">
         <is>
-          <t>Lo que se teclea aquí es el precio de la carne, que es lo que dice la
+          <t>[01616] Lo que se teclea aquí es el precio de la carne, que es lo que dice la
 factura del proveedor. Lo que costó traerla ya se apuntó en el muelle y
 sigue siendo suyo: el kilo puesto en la cámara es la suma de los tres.</t>
         </is>
@@ -57899,7 +57899,7 @@
         </is>
       </c>
       <c r="C1618" t="n">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="D1618" t="inlineStr">
         <is>
@@ -57909,12 +57909,12 @@
       <c r="E1618" t="inlineStr"/>
       <c r="F1618" s="2" t="inlineStr">
         <is>
-          <t>Lo que cuesta el kilo **puesto en la cámara**: lo que se le pagó al proveedor más lo que costó traerlo.</t>
+          <t>[01617] Lo que cuesta el kilo **puesto en la cámara**: lo que se le pagó al proveedor más lo que costó traerlo.</t>
         </is>
       </c>
       <c r="G1618" s="2" t="inlineStr">
         <is>
-          <t>Lo que cuesta el kilo **puesto en la cámara**: lo que se le pagó al
+          <t>[01617] Lo que cuesta el kilo **puesto en la cámara**: lo que se le pagó al
 proveedor más lo que costó traerlo. Es el número que manda en todo lo que
 viene después —el despiece, el escandallo, el food cost—, porque la carne
 no cuesta lo que dice la factura del proveedor: cuesta lo que costó
@@ -57934,7 +57934,7 @@
         </is>
       </c>
       <c r="C1619" t="n">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="D1619" t="inlineStr">
         <is>
@@ -57944,12 +57944,12 @@
       <c r="E1619" t="inlineStr"/>
       <c r="F1619" s="2" t="inlineStr">
         <is>
-          <t>Y de qué está hecho ese número, para poder verlo por separado.</t>
+          <t>[01618] Y de qué está hecho ese número, para poder verlo por separado.</t>
         </is>
       </c>
       <c r="G1619" s="2" t="inlineStr">
         <is>
-          <t>Y de qué está hecho ese número, para poder verlo por separado. El precio
+          <t>[01618] Y de qué está hecho ese número, para poder verlo por separado. El precio
 del kilo lo pone cada pieza; el transporte y la aduana son del camión
 entero y se reparten a todas por igual. Guardarlos sueltos es lo que
 permite contestar «¿me sale más caro el australiano por la carne o por el
@@ -57979,12 +57979,12 @@
       <c r="E1620" t="inlineStr"/>
       <c r="F1620" s="2" t="inlineStr">
         <is>
-          <t>Y una pesada no abarata el kilo.</t>
+          <t>[01619] Y una pesada no abarata el kilo.</t>
         </is>
       </c>
       <c r="G1620" s="2" t="inlineStr">
         <is>
-          <t>Y una pesada no abarata el kilo. Nunca. Aquí solo se pesa lo que se
+          <t>[01619] Y una pesada no abarata el kilo. Nunca. Aquí solo se pesa lo que se
 evapora: los kilos bajan o se quedan, el coste no se mueve, así que
 la cuenta solo puede salir igual o más alta. Si sale más baja, lo que
 ha pasado no es que la carne valga menos: es que las dos cifras
@@ -58016,12 +58016,12 @@
       <c r="E1621" t="inlineStr"/>
       <c r="F1621" s="2" t="inlineStr">
         <is>
-          <t>Cerrar el aviso de cookies sin perder el sitio.</t>
+          <t>[01620] Cerrar el aviso de cookies sin perder el sitio.</t>
         </is>
       </c>
       <c r="G1621" s="2" t="inlineStr">
         <is>
-          <t>Cerrar el aviso de cookies sin perder el sitio.
+          <t>[01620] Cerrar el aviso de cookies sin perder el sitio.
    El formulario sigue siendo un formulario de verdad: sin guiones se manda,
    el servidor apunta la cookie y todo funciona como siempre. Es lo que no se
    puede perder, porque es lo que hace que esto vaya en un teléfono viejo.
@@ -58057,12 +58057,12 @@
       <c r="E1622" t="inlineStr"/>
       <c r="F1622" s="2" t="inlineStr">
         <is>
-          <t>Los idiomas, en el pie.</t>
+          <t>[01621] Los idiomas, en el pie.</t>
         </is>
       </c>
       <c r="G1622" s="2" t="inlineStr">
         <is>
-          <t>Los idiomas, en el pie. Aquí estaban repetidos.</t>
+          <t>[01621] Los idiomas, en el pie. Aquí estaban repetidos.</t>
         </is>
       </c>
     </row>
@@ -58088,12 +58088,12 @@
       <c r="E1623" t="inlineStr"/>
       <c r="F1623" s="2" t="inlineStr">
         <is>
-          <t>Los idiomas van en el pie y en ningún otro sitio: aquí había una tarjeta que los repetía, y en el móvil se veían los dos juegos seguidos.</t>
+          <t>[01622] Los idiomas van en el pie y en ningún otro sitio: aquí había una tarjeta que los repetía, y en el móvil se veían los dos juegos seguidos.</t>
         </is>
       </c>
       <c r="G1623" s="2" t="inlineStr">
         <is>
-          <t>Los idiomas van en el pie y en ningún otro sitio: aquí había una tarjeta
+          <t>[01622] Los idiomas van en el pie y en ningún otro sitio: aquí había una tarjeta
    que los repetía, y en el móvil se veían los dos juegos seguidos.</t>
         </is>
       </c>
@@ -58120,12 +58120,12 @@
       <c r="E1624" t="inlineStr"/>
       <c r="F1624" s="2" t="inlineStr">
         <is>
-          <t>El único sitio donde se elige idioma en las pantallas públicas.</t>
+          <t>[01623] El único sitio donde se elige idioma en las pantallas públicas.</t>
         </is>
       </c>
       <c r="G1624" s="2" t="inlineStr">
         <is>
-          <t>El único sitio donde se elige idioma en las pantallas públicas. Lo
+          <t>[01623] El único sitio donde se elige idioma en las pantallas públicas. Lo
          llevaba el pie desde siempre, y después se le puso además una tarjeta
          a cada pantalla: desde el móvil salían los dos, uno encima del otro,
          catorce botones para hacer lo mismo.
@@ -58157,12 +58157,12 @@
       <c r="E1625" t="inlineStr"/>
       <c r="F1625" s="2" t="inlineStr">
         <is>
-          <t>Cerrar el aviso de cookies sin perder el sitio.</t>
+          <t>[01624] Cerrar el aviso de cookies sin perder el sitio.</t>
         </is>
       </c>
       <c r="G1625" s="2" t="inlineStr">
         <is>
-          <t>Cerrar el aviso de cookies sin perder el sitio.
+          <t>[01624] Cerrar el aviso de cookies sin perder el sitio.
    El formulario sigue siendo un formulario de verdad: sin guiones se manda,
    el servidor apunta la cookie y todo funciona como siempre. Es lo que no se
    puede perder, porque es lo que hace que esto vaya en un teléfono viejo.
@@ -58198,12 +58198,12 @@
       <c r="E1626" t="inlineStr"/>
       <c r="F1626" s="2" t="inlineStr">
         <is>
-          <t>El precio del kilo no está aquí a propósito: es de cada pieza.</t>
+          <t>[01625] El precio del kilo no está aquí a propósito: es de cada pieza.</t>
         </is>
       </c>
       <c r="G1626" s="2" t="inlineStr">
         <is>
-          <t>El precio del kilo no está aquí a propósito: es de cada pieza. Dos
+          <t>[01625] El precio del kilo no está aquí a propósito: es de cada pieza. Dos
          bolsas del mismo camión no valen lo mismo si una es MB9 y la otra
          MB6, y un precio de lote copiado a todas esconde justo eso. Lo que sí
          es del camión entero —y solo si viene de fuera— es lo que costó
@@ -58211,8 +58211,805 @@
         </is>
       </c>
     </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>01626</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>thegrill/meat/app.py</t>
+        </is>
+      </c>
+      <c r="C1627" t="n">
+        <v>255</v>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>función</t>
+        </is>
+      </c>
+      <c r="E1627" t="inlineStr">
+        <is>
+          <t>_reparto_de</t>
+        </is>
+      </c>
+      <c r="F1627" s="2" t="inlineStr">
+        <is>
+          <t>Cómo parte esta casa un margen: lo de Hacienda y lo que queda.</t>
+        </is>
+      </c>
+      <c r="G1627" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cómo parte esta casa un margen: lo de Hacienda y lo que queda.
+    Devuelve una función para que cada pantalla la llame con el margen que
+    tenga delante —el de una pieza, el de un corte, el del día— sin volver a
+    preguntar por la casa. Sin casa o sin tipo puesto, el reparto que sale
+    dice que no hay impuesto y las pantallas no pintan nada.
+    </t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>01627</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>thegrill/meat/app.py</t>
+        </is>
+      </c>
+      <c r="C1628" t="n">
+        <v>216</v>
+      </c>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1628" t="inlineStr"/>
+      <c r="F1628" s="2" t="inlineStr">
+        <is>
+          <t>[00351b] Y cómo se parte lo que se gana: lo que hay que apartar para Hacienda y lo que queda limpio.</t>
+        </is>
+      </c>
+      <c r="G1628" s="2" t="inlineStr">
+        <is>
+          <t>[00351b] Y cómo se parte lo que se gana: lo que hay que apartar
+para Hacienda y lo que queda limpio. Va aquí, con la moneda, por
+lo mismo: es cómo habla de dinero esta casa, y así ninguna
+pantalla que enseñe un margen tiene que acordarse de pedirlo.
+Sin tipo puesto, el reparto lo dice y no se pinta nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>01628</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>thegrill/meat/app.py</t>
+        </is>
+      </c>
+      <c r="C1629" t="n">
+        <v>2934</v>
+      </c>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1629" t="inlineStr"/>
+      <c r="F1629" s="2" t="inlineStr">
+        <is>
+          <t>El impuesto sobre lo que se gana.</t>
+        </is>
+      </c>
+      <c r="G1629" s="2" t="inlineStr">
+        <is>
+          <t>El impuesto sobre lo que se gana. Vacío lo borra —«no lo digo»,
+y entonces no se enseña ningún reparto—; un número que no es un
+número deja el que había, que es lo prudente con algo de lo que
+cuelga cuánto dinero se aparta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>01629</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>thegrill/meat/service.py</t>
+        </is>
+      </c>
+      <c r="C1630" t="n">
+        <v>1182</v>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>función</t>
+        </is>
+      </c>
+      <c r="E1630" t="inlineStr">
+        <is>
+          <t>_lo_ganado_hoy</t>
+        </is>
+      </c>
+      <c r="F1630" s="2" t="inlineStr">
+        <is>
+          <t>Lo que se ingresó con la carne del día y lo que costó esa carne.</t>
+        </is>
+      </c>
+      <c r="G1630" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lo que se ingresó con la carne del día y lo que costó esa carne.
+    El coste sale de los apuntes de salida, que es lo que de verdad se
+    descontó de la cámara. El ingreso se reparte igual que en la
+    trazabilidad: cada venta de un plato reparte su precio sin impuestos entre
+    sus ingredientes en proporción a lo que cuesta cada uno dentro de ese
+    plato, y lo que cae sobre la carne es lo que se le atribuye. Sin ese
+    reparto, un entrecot con su guarnición y su salsa se apuntaría el precio
+    entero del plato y el margen del día saldría inflado.
+    Y aparte, lo que se cortó y se cobró al peso, que no pasa por el
+    escandallo: ahí el precio es el precio, sin repartir nada.
+    </t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>01630</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>thegrill/meat/service.py</t>
+        </is>
+      </c>
+      <c r="C1631" t="n">
+        <v>1113</v>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>función</t>
+        </is>
+      </c>
+      <c r="E1631" t="inlineStr">
+        <is>
+          <t>sales_margin</t>
+        </is>
+      </c>
+      <c r="F1631" s="2" t="inlineStr">
+        <is>
+          <t>Lo ganado con la carne que salió hoy: lo cobrado menos lo que costó.</t>
+        </is>
+      </c>
+      <c r="G1631" s="2" t="inlineStr">
+        <is>
+          <t>Lo ganado con la carne que salió hoy: lo cobrado menos lo que costó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>01631</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>thegrill/meat/service.py</t>
+        </is>
+      </c>
+      <c r="C1632" t="n">
+        <v>1118</v>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>función</t>
+        </is>
+      </c>
+      <c r="E1632" t="inlineStr">
+        <is>
+          <t>sales_food_cost_pct</t>
+        </is>
+      </c>
+      <c r="F1632" s="2" t="inlineStr">
+        <is>
+          <t>A qué food cost ha salido el día.</t>
+        </is>
+      </c>
+      <c r="G1632" s="2" t="inlineStr">
+        <is>
+          <t>A qué food cost ha salido el día. Sin ingresos, no hay porcentaje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>01632</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>thegrill/meat/service.py</t>
+        </is>
+      </c>
+      <c r="C1633" t="n">
+        <v>1103</v>
+      </c>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1633" t="inlineStr"/>
+      <c r="F1633" s="2" t="inlineStr">
+        <is>
+          <t>Lo que se ingresó con la carne del día y lo que costó esa carne.</t>
+        </is>
+      </c>
+      <c r="G1633" s="2" t="inlineStr">
+        <is>
+          <t>Lo que se ingresó con la carne del día y lo que costó esa carne. Los dos
+juntos son lo único que contesta «¿cuánto hemos ganado hoy con los kilos
+que han salido?», que es la pregunta del cierre. El parte tenía los
+kilos y las unidades, y con eso se sabe cuánto se ha movido pero no si
+ha valido la pena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>01633</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>thegrill/meat/service.py</t>
+        </is>
+      </c>
+      <c r="C1634" t="n">
+        <v>1207</v>
+      </c>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1634" t="inlineStr"/>
+      <c r="F1634" s="2" t="inlineStr">
+        <is>
+          <t>La venta que no dice el plato —el conteo del descongelado— se valora por la media de los platos que llevan ese ingrediente: es mejor que apuntarle cero ingreso</t>
+        </is>
+      </c>
+      <c r="G1634" s="2" t="inlineStr">
+        <is>
+          <t>La venta que no dice el plato —el conteo del descongelado— se
+valora por la media de los platos que llevan ese ingrediente:
+es mejor que apuntarle cero ingreso a carne que se vendió.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>01634</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>thegrill/models.py</t>
+        </is>
+      </c>
+      <c r="C1635" t="n">
+        <v>238</v>
+      </c>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1635" t="inlineStr"/>
+      <c r="F1635" s="2" t="inlineStr">
+        <is>
+          <t>Lo que se lleva Hacienda de lo que se gana, en tanto por ciento.</t>
+        </is>
+      </c>
+      <c r="G1635" s="2" t="inlineStr">
+        <is>
+          <t>Lo que se lleva Hacienda de lo que se gana, en tanto por ciento. Lo pone
+el manager porque cambia con el país, con el tipo de sociedad y con el
+año, y el programa no tiene por qué saberlo. Sirve para partir el margen
+en dos: lo que hay que apartar y lo que queda limpio.
+No es el IVA. El IVA ya está en cada plato —`vat_pct`— y sale del precio
+antes de calcular el food cost, porque no es dinero de la casa: se cobra
+y se entrega. Esto es lo otro: lo que se paga por haber ganado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>01635</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>thegrill/web/app.py</t>
+        </is>
+      </c>
+      <c r="C1636" t="n">
+        <v>148</v>
+      </c>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>función</t>
+        </is>
+      </c>
+      <c r="E1636" t="inlineStr">
+        <is>
+          <t>_reparto_de</t>
+        </is>
+      </c>
+      <c r="F1636" s="2" t="inlineStr">
+        <is>
+          <t>Cómo parte esta casa un margen.</t>
+        </is>
+      </c>
+      <c r="G1636" s="2" t="inlineStr">
+        <is>
+          <t>Cómo parte esta casa un margen. Sin casa o sin tipo, no parte nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>01636</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>thegrill/web/app.py</t>
+        </is>
+      </c>
+      <c r="C1637" t="n">
+        <v>139</v>
+      </c>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1637" t="inlineStr"/>
+      <c r="F1637" s="2" t="inlineStr">
+        <is>
+          <t>[00985b] Y cómo parte esta casa lo que gana: lo que hay que apartar para Hacienda y lo que queda limpio.</t>
+        </is>
+      </c>
+      <c r="G1637" s="2" t="inlineStr">
+        <is>
+          <t>[00985b] Y cómo parte esta casa lo que gana: lo que hay que
+apartar para Hacienda y lo que queda limpio. Las dos ediciones
+enseñan la misma trazabilidad, así que las dos lo traen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>01637</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>thegrill/web/impuestos.py</t>
+        </is>
+      </c>
+      <c r="C1638" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>módulo</t>
+        </is>
+      </c>
+      <c r="E1638" t="inlineStr">
+        <is>
+          <t>impuestos</t>
+        </is>
+      </c>
+      <c r="F1638" s="2" t="inlineStr">
+        <is>
+          <t>Lo que se gana, lo que hay que apartar y lo que queda limpio.</t>
+        </is>
+      </c>
+      <c r="G1638" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lo que se gana, lo que hay que apartar y lo que queda limpio.
+Un lomo que se compra a 300 € y se vende a 900 deja 600 de margen. Pero de
+esos 600 no se lleva la casa 600: una parte se la lleva Hacienda por haberlos
+ganado, y el día que llega el pago tiene que estar apartada. Un restaurante
+que mira el margen bruto y gasta contra él va bien once meses y mal el
+doceavo, siempre el mismo.
+Así que el margen se parte en dos y las dos partes se enseñan juntas: lo que
+hay que guardar y lo que queda de verdad.
+**Qué no es esto.** No es el IVA: el IVA ya sale del precio de cada plato antes
+de calcular nada, porque no es dinero de la casa —se cobra y se entrega—. Y no
+es la declaración: el impuesto de verdad se paga sobre el beneficio de la
+empresa entera, con el alquiler, las nóminas y la luz descontados, no sobre lo
+que deja la carne. Esto es una reserva, y sirve para lo que sirve una reserva:
+que el dinero esté cuando haya que pagarlo, no para saber cuánto se paga.
+Dicho de otra manera: el número de abajo es **más** de lo que acabará
+quedando, nunca menos. Como reserva, eso es exactamente lo que se quiere.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>01638</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>thegrill/web/impuestos.py</t>
+        </is>
+      </c>
+      <c r="C1639" t="n">
+        <v>34</v>
+      </c>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>clase</t>
+        </is>
+      </c>
+      <c r="E1639" t="inlineStr">
+        <is>
+          <t>Reparto</t>
+        </is>
+      </c>
+      <c r="F1639" s="2" t="inlineStr">
+        <is>
+          <t>El margen partido: lo ganado, lo que se aparta y lo que queda.</t>
+        </is>
+      </c>
+      <c r="G1639" s="2" t="inlineStr">
+        <is>
+          <t>El margen partido: lo ganado, lo que se aparta y lo que queda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>01639</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>thegrill/web/impuestos.py</t>
+        </is>
+      </c>
+      <c r="C1640" t="n">
+        <v>47</v>
+      </c>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>función</t>
+        </is>
+      </c>
+      <c r="E1640" t="inlineStr">
+        <is>
+          <t>tipo_de</t>
+        </is>
+      </c>
+      <c r="F1640" s="2" t="inlineStr">
+        <is>
+          <t>El tanto por ciento que paga esa casa.</t>
+        </is>
+      </c>
+      <c r="G1640" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El tanto por ciento que paga esa casa. Sin poner, cero.
+    Cero quiere decir «no lo he dicho», y entonces no se enseña ningún reparto:
+    inventarse un tipo —el del país, el de la media— sería poner en pantalla un
+    número que parece de la casa y no lo es, y sobre él se toman decisiones.
+    </t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>01640</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>thegrill/web/impuestos.py</t>
+        </is>
+      </c>
+      <c r="C1641" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>función</t>
+        </is>
+      </c>
+      <c r="E1641" t="inlineStr">
+        <is>
+          <t>reparte</t>
+        </is>
+      </c>
+      <c r="F1641" s="2" t="inlineStr">
+        <is>
+          <t>Parte un margen en lo que hay que apartar y lo que queda.</t>
+        </is>
+      </c>
+      <c r="G1641" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parte un margen en lo que hay que apartar y lo que queda.
+    Un margen negativo —se vendió por debajo de lo que costó— no paga
+    impuestos: no se ha ganado nada. Se devuelve entero como pérdida, que es lo
+    que es, en vez de enseñar una devolución que nadie va a recibir por una
+    pieza suelta.
+    </t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>01641</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>thegrill/web/impuestos.py</t>
+        </is>
+      </c>
+      <c r="C1642" t="n">
+        <v>80</v>
+      </c>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>función</t>
+        </is>
+      </c>
+      <c r="E1642" t="inlineStr">
+        <is>
+          <t>de_la_casa</t>
+        </is>
+      </c>
+      <c r="F1642" s="2" t="inlineStr">
+        <is>
+          <t>El reparto de ese margen con el tipo que tenga puesto la casa.</t>
+        </is>
+      </c>
+      <c r="G1642" s="2" t="inlineStr">
+        <is>
+          <t>El reparto de ese margen con el tipo que tenga puesto la casa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>01642</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>thegrill/web/impuestos.py</t>
+        </is>
+      </c>
+      <c r="C1643" t="n">
+        <v>42</v>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>función</t>
+        </is>
+      </c>
+      <c r="E1643" t="inlineStr">
+        <is>
+          <t>hay_impuesto</t>
+        </is>
+      </c>
+      <c r="F1643" s="2" t="inlineStr">
+        <is>
+          <t>Si la casa ha dicho cuánto paga.</t>
+        </is>
+      </c>
+      <c r="G1643" s="2" t="inlineStr">
+        <is>
+          <t>Si la casa ha dicho cuánto paga. Sin decirlo no se enseña nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>01643</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>thegrill/web/impuestos.py</t>
+        </is>
+      </c>
+      <c r="C1644" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1644" t="inlineStr"/>
+      <c r="F1644" s="2" t="inlineStr">
+        <is>
+          <t>Nadie paga el doscientos por cien de lo que gana.</t>
+        </is>
+      </c>
+      <c r="G1644" s="2" t="inlineStr">
+        <is>
+          <t>Nadie paga el doscientos por cien de lo que gana. Un número mayor que esto
+es un dedo, no un tipo impositivo, y se recorta antes de que salga en una
+pantalla como si fuera verdad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>01644</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>thegrill/web/impuestos.py</t>
+        </is>
+      </c>
+      <c r="C1645" t="n">
+        <v>68</v>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1645" t="inlineStr"/>
+      <c r="F1645" s="2" t="inlineStr">
+        <is>
+          <t>El tope también aquí y no solo al leerlo de la casa: esta función la llama cualquiera con el número que tenga a mano, y un tipo del quinientos por ciento dejarí</t>
+        </is>
+      </c>
+      <c r="G1645" s="2" t="inlineStr">
+        <is>
+          <t>El tope también aquí y no solo al leerlo de la casa: esta función la
+llama cualquiera con el número que tenga a mano, y un tipo del quinientos
+por ciento dejaría el limpio en negativo con toda naturalidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>01645</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>thegrill/meat/templates/report.html</t>
+        </is>
+      </c>
+      <c r="C1646" t="n">
+        <v>41</v>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>plantilla</t>
+        </is>
+      </c>
+      <c r="E1646" t="inlineStr"/>
+      <c r="F1646" s="2" t="inlineStr">
+        <is>
+          <t>Lo ganado con los kilos que han salido hoy, y partido: lo que hay que apartar para Hacienda y lo que queda.</t>
+        </is>
+      </c>
+      <c r="G1646" s="2" t="inlineStr">
+        <is>
+          <t>Lo ganado con los kilos que han salido hoy, y partido: lo que hay que
+   apartar para Hacienda y lo que queda. El parte tenía los kilos y las
+   unidades —con eso se sabe cuánto se ha movido, no si ha valido la pena—.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>01646</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>thegrill/web/templates/settings.html</t>
+        </is>
+      </c>
+      <c r="C1647" t="n">
+        <v>52</v>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>plantilla</t>
+        </is>
+      </c>
+      <c r="E1647" t="inlineStr"/>
+      <c r="F1647" s="2" t="inlineStr">
+        <is>
+          <t>Lo que se lleva Hacienda de lo ganado.</t>
+        </is>
+      </c>
+      <c r="G1647" s="2" t="inlineStr">
+        <is>
+          <t>Lo que se lleva Hacienda de lo ganado. Va aquí, con la moneda, porque es
+     lo mismo: cómo habla de dinero esta casa. En blanco no se enseña ningún
+     reparto, que es mejor que enseñar uno inventado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>01647</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>thegrill/web/templates/tracing.html</t>
+        </is>
+      </c>
+      <c r="C1648" t="n">
+        <v>79</v>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>plantilla</t>
+        </is>
+      </c>
+      <c r="E1648" t="inlineStr"/>
+      <c r="F1648" s="2" t="inlineStr">
+        <is>
+          <t>Y el margen partido, si la casa ha dicho cuánto paga: lo que hay que apartar y lo que queda de verdad.</t>
+        </is>
+      </c>
+      <c r="G1648" s="2" t="inlineStr">
+        <is>
+          <t>Y el margen partido, si la casa ha dicho cuánto paga: lo que hay que
+     apartar y lo que queda de verdad. Mirar el margen bruto y gastar contra
+     él sale bien once meses y mal el doceavo, siempre el mismo.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1626"/>
+  <autoFilter ref="A1:G1648"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -58223,7 +59020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -58521,7 +59318,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -58530,7 +59327,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>01613</t>
+          <t>01628</t>
         </is>
       </c>
     </row>
@@ -58721,7 +59518,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -58730,7 +59527,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>01616</t>
+          <t>01633</t>
         </is>
       </c>
     </row>
@@ -59121,7 +59918,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -59130,7 +59927,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>01587</t>
+          <t>01645</t>
         </is>
       </c>
     </row>
@@ -59221,7 +60018,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -59230,7 +60027,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>01618</t>
+          <t>01634</t>
         </is>
       </c>
     </row>
@@ -59361,7 +60158,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -59370,7 +60167,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>00993</t>
+          <t>01636</t>
         </is>
       </c>
     </row>
@@ -59577,267 +60374,267 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>thegrill/web/inventory.py</t>
+          <t>thegrill/web/impuestos.py</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>01250</t>
+          <t>01637</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>01286</t>
+          <t>01644</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>thegrill/web/jornada.py</t>
+          <t>thegrill/web/inventory.py</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>01287</t>
+          <t>01250</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>01299</t>
+          <t>01286</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>thegrill/web/locking.py</t>
+          <t>thegrill/web/jornada.py</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>01300</t>
+          <t>01287</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>01305</t>
+          <t>01299</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>thegrill/web/money.py</t>
+          <t>thegrill/web/locking.py</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>01306</t>
+          <t>01300</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>01309</t>
+          <t>01305</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>thegrill/web/pesos.py</t>
+          <t>thegrill/web/money.py</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>01310</t>
+          <t>01306</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>01323</t>
+          <t>01309</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>thegrill/web/pos_import.py</t>
+          <t>thegrill/web/pesos.py</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>01324</t>
+          <t>01310</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>01350</t>
+          <t>01323</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>thegrill/web/rangos.py</t>
+          <t>thegrill/web/pos_import.py</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>01351</t>
+          <t>01324</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>01367</t>
+          <t>01350</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>thegrill/web/seed.py</t>
+          <t>thegrill/web/rangos.py</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>01368</t>
+          <t>01351</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>01370</t>
+          <t>01367</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>thegrill/web/seguridad.py</t>
+          <t>thegrill/web/seed.py</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>01371</t>
+          <t>01368</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>01376</t>
+          <t>01370</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>thegrill/web/service.py</t>
+          <t>thegrill/web/seguridad.py</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>01377</t>
+          <t>01371</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>01396</t>
+          <t>01376</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>thegrill/web/sheets.py</t>
+          <t>thegrill/web/service.py</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>01397</t>
+          <t>01377</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>01414</t>
+          <t>01396</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>thegrill/web/sites.py</t>
+          <t>thegrill/web/sheets.py</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>01415</t>
+          <t>01397</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>01445</t>
+          <t>01414</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>thegrill/web/templates/_peso.html</t>
+          <t>thegrill/web/sites.py</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>01590</t>
+          <t>01415</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>01590</t>
+          <t>01445</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>thegrill/web/templates/error.html</t>
+          <t>thegrill/web/templates/_peso.html</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -59845,39 +60642,39 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>01591</t>
+          <t>01590</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>01591</t>
+          <t>01590</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>thegrill/web/templates/ingredient_detail.html</t>
+          <t>thegrill/web/templates/error.html</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>01592</t>
+          <t>01591</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>01593</t>
+          <t>01591</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>thegrill/web/templates/inventory.html</t>
+          <t>thegrill/web/templates/ingredient_detail.html</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -59885,157 +60682,177 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>01594</t>
+          <t>01592</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>01595</t>
+          <t>01593</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>thegrill/web/templates/recipe_detail.html</t>
+          <t>thegrill/web/templates/inventory.html</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>01596</t>
+          <t>01594</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>01596</t>
+          <t>01595</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>thegrill/web/templates/settings.html</t>
+          <t>thegrill/web/templates/recipe_detail.html</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>01597</t>
+          <t>01596</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>01601</t>
+          <t>01596</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>thegrill/web/templates/tracing.html</t>
+          <t>thegrill/web/templates/settings.html</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>01602</t>
+          <t>01597</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>01611</t>
+          <t>01646</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>thegrill/web/templates/waste.html</t>
+          <t>thegrill/web/templates/tracing.html</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>01612</t>
+          <t>01602</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>01612</t>
+          <t>01647</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>thegrill/web/tracing.py</t>
+          <t>thegrill/web/templates/waste.html</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>01446</t>
+          <t>01612</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>01506</t>
+          <t>01612</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>thegrill/web/twofactor.py</t>
+          <t>thegrill/web/tracing.py</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>01507</t>
+          <t>01446</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>01516</t>
+          <t>01506</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>thegrill/web/twofactor.py</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>10</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>01507</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>01516</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>thegrill/web/waste.py</t>
         </is>
       </c>
-      <c r="B90" t="n">
+      <c r="B91" t="n">
         <v>18</v>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>01517</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>01534</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D90"/>
+  <autoFilter ref="A1:D91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/COMENTARIOS.xlsx
+++ b/COMENTARIOS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Por fichero" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comentarios'!$A$1:$G$1648</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comentarios'!$A$1:$G$1662</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por fichero'!$A$1:$D$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1648"/>
+  <dimension ref="A1:G1662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>1160</v>
+        <v>1166</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>1170</v>
+        <v>1176</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>1193</v>
+        <v>1199</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1298</v>
+        <v>1304</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>1314</v>
+        <v>1320</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1338</v>
+        <v>1344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>1354</v>
+        <v>1360</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>1370</v>
+        <v>1376</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>1386</v>
+        <v>1392</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>1417</v>
+        <v>1423</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>1496</v>
+        <v>1502</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>1505</v>
+        <v>1511</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>1541</v>
+        <v>1547</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>1562</v>
+        <v>1568</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>1584</v>
+        <v>1590</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>1620</v>
+        <v>1626</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>1660</v>
+        <v>1666</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>1681</v>
+        <v>1687</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>1687</v>
+        <v>1693</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>1707</v>
+        <v>1713</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>1731</v>
+        <v>1737</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>1755</v>
+        <v>1761</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>1781</v>
+        <v>1787</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>1793</v>
+        <v>1799</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>1810</v>
+        <v>1816</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>1824</v>
+        <v>1830</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>1841</v>
+        <v>1847</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>1865</v>
+        <v>1871</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>1890</v>
+        <v>1896</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>1904</v>
+        <v>1910</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>1924</v>
+        <v>1930</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>1939</v>
+        <v>1945</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>1952</v>
+        <v>1958</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>1970</v>
+        <v>1976</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>1985</v>
+        <v>1991</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>2027</v>
+        <v>2033</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>2042</v>
+        <v>2048</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>2058</v>
+        <v>2064</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>2073</v>
+        <v>2079</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>2094</v>
+        <v>2100</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>2101</v>
+        <v>2107</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>2122</v>
+        <v>2128</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>2153</v>
+        <v>2159</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>2209</v>
+        <v>2215</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>2255</v>
+        <v>2261</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>2277</v>
+        <v>2283</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>2318</v>
+        <v>2324</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>2333</v>
+        <v>2339</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>2349</v>
+        <v>2355</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>2368</v>
+        <v>2374</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>2386</v>
+        <v>2392</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>2398</v>
+        <v>2404</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>2411</v>
+        <v>2417</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>2456</v>
+        <v>2462</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>2475</v>
+        <v>2481</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>2502</v>
+        <v>2508</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>2529</v>
+        <v>2535</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>2556</v>
+        <v>2562</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>2566</v>
+        <v>2572</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>2578</v>
+        <v>2584</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>2589</v>
+        <v>2595</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>2600</v>
+        <v>2606</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>2635</v>
+        <v>2641</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>2662</v>
+        <v>2668</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>2681</v>
+        <v>2687</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>2695</v>
+        <v>2701</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>2719</v>
+        <v>2725</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2737</v>
+        <v>2743</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>2754</v>
+        <v>2760</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>2769</v>
+        <v>2775</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>2795</v>
+        <v>2801</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>2811</v>
+        <v>2817</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>2823</v>
+        <v>2829</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>2841</v>
+        <v>2847</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>2873</v>
+        <v>2879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>2891</v>
+        <v>2897</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>2920</v>
+        <v>2926</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>2989</v>
+        <v>2995</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>3007</v>
+        <v>3013</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>3029</v>
+        <v>3035</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>3046</v>
+        <v>3052</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>3070</v>
+        <v>3076</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>3095</v>
+        <v>3101</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>3107</v>
+        <v>3113</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>3125</v>
+        <v>3131</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>3137</v>
+        <v>3143</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>3152</v>
+        <v>3158</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>3176</v>
+        <v>3182</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>3184</v>
+        <v>3190</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>3202</v>
+        <v>3208</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>3211</v>
+        <v>3217</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>3225</v>
+        <v>3231</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>3240</v>
+        <v>3246</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>3418</v>
+        <v>3424</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>3435</v>
+        <v>3441</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>3448</v>
+        <v>3454</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>3453</v>
+        <v>3459</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>2855</v>
+        <v>2861</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>1035</v>
+        <v>1041</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>1040</v>
+        <v>1046</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>1167</v>
+        <v>1173</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>1209</v>
+        <v>1215</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>1248</v>
+        <v>1254</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>1361</v>
+        <v>1367</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>1425</v>
+        <v>1431</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>1503</v>
+        <v>1509</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>1514</v>
+        <v>1520</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>1567</v>
+        <v>1573</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>1594</v>
+        <v>1600</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>1764</v>
+        <v>1770</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>2110</v>
+        <v>2116</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>2162</v>
+        <v>2168</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>2178</v>
+        <v>2184</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>2215</v>
+        <v>2221</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>2286</v>
+        <v>2292</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>2293</v>
+        <v>2299</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>2372</v>
+        <v>2378</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>2426</v>
+        <v>2432</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>2433</v>
+        <v>2439</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>2446</v>
+        <v>2452</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>2489</v>
+        <v>2495</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>2742</v>
+        <v>2748</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>2781</v>
+        <v>2787</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>2830</v>
+        <v>2836</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>2871</v>
+        <v>2877</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>2879</v>
+        <v>2885</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>2947</v>
+        <v>2953</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>2964</v>
+        <v>2970</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>3018</v>
+        <v>3024</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>3051</v>
+        <v>3057</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>3075</v>
+        <v>3081</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>3090</v>
+        <v>3096</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>3250</v>
+        <v>3256</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>5101</v>
+        <v>5150</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>1423</v>
+        <v>1437</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>1457</v>
+        <v>1471</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>1474</v>
+        <v>1488</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>2148</v>
+        <v>2169</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>2182</v>
+        <v>2203</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>2199</v>
+        <v>2220</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>2873</v>
+        <v>2901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>2907</v>
+        <v>2935</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>2924</v>
+        <v>2952</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>3598</v>
+        <v>3633</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>3632</v>
+        <v>3667</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>3649</v>
+        <v>3684</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>4323</v>
+        <v>4365</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>4357</v>
+        <v>4399</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>4376</v>
+        <v>4418</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>5050</v>
+        <v>5099</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>5084</v>
+        <v>5133</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         </is>
       </c>
       <c r="C564" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         </is>
       </c>
       <c r="C565" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         </is>
       </c>
       <c r="C566" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         </is>
       </c>
       <c r="C567" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         </is>
       </c>
       <c r="C568" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="C569" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         </is>
       </c>
       <c r="C570" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         </is>
       </c>
       <c r="C571" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         </is>
       </c>
       <c r="C572" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         </is>
       </c>
       <c r="C573" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         </is>
       </c>
       <c r="C574" t="n">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         </is>
       </c>
       <c r="C575" t="n">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="C576" t="n">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         </is>
       </c>
       <c r="C577" t="n">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         </is>
       </c>
       <c r="C578" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="C579" t="n">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         </is>
       </c>
       <c r="C580" t="n">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         </is>
       </c>
       <c r="C581" t="n">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="C582" t="n">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         </is>
       </c>
       <c r="C583" t="n">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         </is>
       </c>
       <c r="C584" t="n">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         </is>
       </c>
       <c r="C585" t="n">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         </is>
       </c>
       <c r="C586" t="n">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         </is>
       </c>
       <c r="C587" t="n">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         </is>
       </c>
       <c r="C588" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         </is>
       </c>
       <c r="C589" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         </is>
       </c>
       <c r="C590" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         </is>
       </c>
       <c r="C591" t="n">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         </is>
       </c>
       <c r="C592" t="n">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         </is>
       </c>
       <c r="C593" t="n">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         </is>
       </c>
       <c r="C594" t="n">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         </is>
       </c>
       <c r="C595" t="n">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         </is>
       </c>
       <c r="C596" t="n">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         </is>
       </c>
       <c r="C597" t="n">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         </is>
       </c>
       <c r="C598" t="n">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         </is>
       </c>
       <c r="C599" t="n">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         </is>
       </c>
       <c r="C600" t="n">
-        <v>934</v>
+        <v>940</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         </is>
       </c>
       <c r="C601" t="n">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         </is>
       </c>
       <c r="C602" t="n">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         </is>
       </c>
       <c r="C603" t="n">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         </is>
       </c>
       <c r="C604" t="n">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         </is>
       </c>
       <c r="C605" t="n">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         </is>
       </c>
       <c r="C606" t="n">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         </is>
       </c>
       <c r="C607" t="n">
-        <v>1142</v>
+        <v>1152</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         </is>
       </c>
       <c r="C608" t="n">
-        <v>1225</v>
+        <v>1243</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         </is>
       </c>
       <c r="C609" t="n">
-        <v>1238</v>
+        <v>1256</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         </is>
       </c>
       <c r="C610" t="n">
-        <v>1253</v>
+        <v>1271</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         </is>
       </c>
       <c r="C611" t="n">
-        <v>1277</v>
+        <v>1295</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         </is>
       </c>
       <c r="C612" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         </is>
       </c>
       <c r="C613" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         </is>
       </c>
       <c r="C614" t="n">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         </is>
       </c>
       <c r="C615" t="n">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         </is>
       </c>
       <c r="C616" t="n">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         </is>
       </c>
       <c r="C617" t="n">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         </is>
       </c>
       <c r="C618" t="n">
-        <v>1125</v>
+        <v>1135</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="C619" t="n">
-        <v>1130</v>
+        <v>1140</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         </is>
       </c>
       <c r="C620" t="n">
-        <v>1135</v>
+        <v>1145</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         </is>
       </c>
       <c r="C621" t="n">
-        <v>1328</v>
+        <v>1346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         </is>
       </c>
       <c r="C623" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         </is>
       </c>
       <c r="C624" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         </is>
       </c>
       <c r="C625" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         </is>
       </c>
       <c r="C626" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         </is>
       </c>
       <c r="C627" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         </is>
       </c>
       <c r="C628" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         </is>
       </c>
       <c r="C629" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         </is>
       </c>
       <c r="C630" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         </is>
       </c>
       <c r="C631" t="n">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         </is>
       </c>
       <c r="C632" t="n">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         </is>
       </c>
       <c r="C633" t="n">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         </is>
       </c>
       <c r="C634" t="n">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         </is>
       </c>
       <c r="C635" t="n">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         </is>
       </c>
       <c r="C636" t="n">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         </is>
       </c>
       <c r="C637" t="n">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         </is>
       </c>
       <c r="C638" t="n">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         </is>
       </c>
       <c r="C639" t="n">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         </is>
       </c>
       <c r="C640" t="n">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         </is>
       </c>
       <c r="C641" t="n">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         </is>
       </c>
       <c r="C642" t="n">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         </is>
       </c>
       <c r="C643" t="n">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         </is>
       </c>
       <c r="C644" t="n">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         </is>
       </c>
       <c r="C645" t="n">
-        <v>1146</v>
+        <v>1156</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         </is>
       </c>
       <c r="C646" t="n">
-        <v>1246</v>
+        <v>1264</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         </is>
       </c>
       <c r="C647" t="n">
-        <v>1288</v>
+        <v>1306</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         </is>
       </c>
       <c r="C648" t="n">
-        <v>1299</v>
+        <v>1317</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="C649" t="n">
-        <v>1302</v>
+        <v>1320</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         </is>
       </c>
       <c r="C650" t="n">
-        <v>1307</v>
+        <v>1325</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         </is>
       </c>
       <c r="C651" t="n">
-        <v>1318</v>
+        <v>1336</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         </is>
       </c>
       <c r="C652" t="n">
-        <v>1322</v>
+        <v>1340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         </is>
       </c>
       <c r="C704" t="n">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         </is>
       </c>
       <c r="C705" t="n">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         </is>
       </c>
       <c r="C706" t="n">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         </is>
       </c>
       <c r="C707" t="n">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         </is>
       </c>
       <c r="C708" t="n">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         </is>
       </c>
       <c r="C709" t="n">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         </is>
       </c>
       <c r="C710" t="n">
-        <v>896</v>
+        <v>908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         </is>
       </c>
       <c r="C711" t="n">
-        <v>945</v>
+        <v>957</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         </is>
       </c>
       <c r="C712" t="n">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         </is>
       </c>
       <c r="C713" t="n">
-        <v>990</v>
+        <v>1002</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         </is>
       </c>
       <c r="C714" t="n">
-        <v>1028</v>
+        <v>1040</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         </is>
       </c>
       <c r="C715" t="n">
-        <v>1059</v>
+        <v>1071</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         </is>
       </c>
       <c r="C716" t="n">
-        <v>1088</v>
+        <v>1100</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         </is>
       </c>
       <c r="C717" t="n">
-        <v>1106</v>
+        <v>1118</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         </is>
       </c>
       <c r="C718" t="n">
-        <v>1136</v>
+        <v>1148</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         </is>
       </c>
       <c r="C719" t="n">
-        <v>1168</v>
+        <v>1180</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         </is>
       </c>
       <c r="C720" t="n">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         </is>
       </c>
       <c r="C721" t="n">
-        <v>1223</v>
+        <v>1235</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         </is>
       </c>
       <c r="C722" t="n">
-        <v>1247</v>
+        <v>1259</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         </is>
       </c>
       <c r="C723" t="n">
-        <v>1273</v>
+        <v>1285</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         </is>
       </c>
       <c r="C724" t="n">
-        <v>1305</v>
+        <v>1317</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         </is>
       </c>
       <c r="C725" t="n">
-        <v>1323</v>
+        <v>1335</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         </is>
       </c>
       <c r="C726" t="n">
-        <v>1346</v>
+        <v>1358</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         </is>
       </c>
       <c r="C727" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         </is>
       </c>
       <c r="C728" t="n">
-        <v>1405</v>
+        <v>1417</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         </is>
       </c>
       <c r="C729" t="n">
-        <v>1433</v>
+        <v>1445</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="C749" t="n">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         </is>
       </c>
       <c r="C750" t="n">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         </is>
       </c>
       <c r="C751" t="n">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         </is>
       </c>
       <c r="C752" t="n">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         </is>
       </c>
       <c r="C753" t="n">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         </is>
       </c>
       <c r="C754" t="n">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="C755" t="n">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         </is>
       </c>
       <c r="C756" t="n">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -27290,7 +27290,7 @@
         </is>
       </c>
       <c r="C757" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         </is>
       </c>
       <c r="C758" t="n">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         </is>
       </c>
       <c r="C759" t="n">
-        <v>851</v>
+        <v>863</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         </is>
       </c>
       <c r="C760" t="n">
-        <v>917</v>
+        <v>929</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         </is>
       </c>
       <c r="C761" t="n">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         </is>
       </c>
       <c r="C762" t="n">
-        <v>925</v>
+        <v>937</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         </is>
       </c>
       <c r="C763" t="n">
-        <v>928</v>
+        <v>940</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         </is>
       </c>
       <c r="C764" t="n">
-        <v>934</v>
+        <v>946</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         </is>
       </c>
       <c r="C765" t="n">
-        <v>976</v>
+        <v>988</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         </is>
       </c>
       <c r="C766" t="n">
-        <v>983</v>
+        <v>995</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         </is>
       </c>
       <c r="C767" t="n">
-        <v>998</v>
+        <v>1010</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         </is>
       </c>
       <c r="C768" t="n">
-        <v>1030</v>
+        <v>1042</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         </is>
       </c>
       <c r="C769" t="n">
-        <v>1048</v>
+        <v>1060</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         </is>
       </c>
       <c r="C770" t="n">
-        <v>1051</v>
+        <v>1063</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         </is>
       </c>
       <c r="C771" t="n">
-        <v>1074</v>
+        <v>1086</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         </is>
       </c>
       <c r="C772" t="n">
-        <v>1079</v>
+        <v>1091</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         </is>
       </c>
       <c r="C773" t="n">
-        <v>1143</v>
+        <v>1155</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         </is>
       </c>
       <c r="C774" t="n">
-        <v>1203</v>
+        <v>1215</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         </is>
       </c>
       <c r="C775" t="n">
-        <v>1212</v>
+        <v>1224</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -27916,7 +27916,7 @@
         </is>
       </c>
       <c r="C776" t="n">
-        <v>1359</v>
+        <v>1371</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         </is>
       </c>
       <c r="C777" t="n">
-        <v>1364</v>
+        <v>1376</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         </is>
       </c>
       <c r="C778" t="n">
-        <v>1370</v>
+        <v>1382</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         </is>
       </c>
       <c r="C779" t="n">
-        <v>1424</v>
+        <v>1436</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         </is>
       </c>
       <c r="C908" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         </is>
       </c>
       <c r="C909" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         </is>
       </c>
       <c r="C910" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         </is>
       </c>
       <c r="C911" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         </is>
       </c>
       <c r="C912" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         </is>
       </c>
       <c r="C913" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         </is>
       </c>
       <c r="C914" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         </is>
       </c>
       <c r="C915" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         </is>
       </c>
       <c r="C916" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         </is>
       </c>
       <c r="C917" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         </is>
       </c>
       <c r="C918" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         </is>
       </c>
       <c r="C919" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         </is>
       </c>
       <c r="C920" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -33120,7 +33120,7 @@
         </is>
       </c>
       <c r="C921" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         </is>
       </c>
       <c r="C922" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         </is>
       </c>
       <c r="C923" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         </is>
       </c>
       <c r="C924" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         </is>
       </c>
       <c r="C925" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         </is>
       </c>
       <c r="C926" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         </is>
       </c>
       <c r="C927" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         </is>
       </c>
       <c r="C928" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         </is>
       </c>
       <c r="C929" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         </is>
       </c>
       <c r="C930" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         </is>
       </c>
       <c r="C931" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         </is>
       </c>
       <c r="C932" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         </is>
       </c>
       <c r="C933" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -33576,7 +33576,7 @@
         </is>
       </c>
       <c r="C934" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         </is>
       </c>
       <c r="C935" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         </is>
       </c>
       <c r="C936" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         </is>
       </c>
       <c r="C937" t="n">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         </is>
       </c>
       <c r="C938" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         </is>
       </c>
       <c r="C939" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         </is>
       </c>
       <c r="C940" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         </is>
       </c>
       <c r="C941" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         </is>
       </c>
       <c r="C942" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         </is>
       </c>
       <c r="C943" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="C944" t="n">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         </is>
       </c>
       <c r="C945" t="n">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         </is>
       </c>
       <c r="C946" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         </is>
       </c>
       <c r="C947" t="n">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         </is>
       </c>
       <c r="C948" t="n">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         </is>
       </c>
       <c r="C949" t="n">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         </is>
       </c>
       <c r="C950" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         </is>
       </c>
       <c r="C951" t="n">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         </is>
       </c>
       <c r="C952" t="n">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         </is>
       </c>
       <c r="C953" t="n">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         </is>
       </c>
       <c r="C954" t="n">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -34321,7 +34321,7 @@
         </is>
       </c>
       <c r="C955" t="n">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         </is>
       </c>
       <c r="C956" t="n">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         </is>
       </c>
       <c r="C957" t="n">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         </is>
       </c>
       <c r="C958" t="n">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         </is>
       </c>
       <c r="C959" t="n">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         </is>
       </c>
       <c r="C960" t="n">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         </is>
       </c>
       <c r="C961" t="n">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         </is>
       </c>
       <c r="C962" t="n">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         </is>
       </c>
       <c r="C963" t="n">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         </is>
       </c>
       <c r="C964" t="n">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         </is>
       </c>
       <c r="C965" t="n">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         </is>
       </c>
       <c r="C966" t="n">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         </is>
       </c>
       <c r="C967" t="n">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         </is>
       </c>
       <c r="C968" t="n">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
         </is>
       </c>
       <c r="C969" t="n">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         </is>
       </c>
       <c r="C970" t="n">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         </is>
       </c>
       <c r="C971" t="n">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -34920,7 +34920,7 @@
         </is>
       </c>
       <c r="C972" t="n">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         </is>
       </c>
       <c r="C973" t="n">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         </is>
       </c>
       <c r="C974" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         </is>
       </c>
       <c r="C975" t="n">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         </is>
       </c>
       <c r="C976" t="n">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         </is>
       </c>
       <c r="C977" t="n">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         </is>
       </c>
       <c r="C978" t="n">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         </is>
       </c>
       <c r="C987" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         </is>
       </c>
       <c r="C988" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         </is>
       </c>
       <c r="C989" t="n">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         </is>
       </c>
       <c r="C990" t="n">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         </is>
       </c>
       <c r="C991" t="n">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         </is>
       </c>
       <c r="C992" t="n">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         </is>
       </c>
       <c r="C993" t="n">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         </is>
       </c>
       <c r="C994" t="n">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         </is>
       </c>
       <c r="C1581" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D1581" t="inlineStr">
         <is>
@@ -56692,7 +56692,7 @@
         </is>
       </c>
       <c r="C1582" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D1582" t="inlineStr">
         <is>
@@ -56727,7 +56727,7 @@
         </is>
       </c>
       <c r="C1583" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D1583" t="inlineStr">
         <is>
@@ -56764,7 +56764,7 @@
         </is>
       </c>
       <c r="C1584" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="D1584" t="inlineStr">
         <is>
@@ -56796,7 +56796,7 @@
         </is>
       </c>
       <c r="C1585" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D1585" t="inlineStr">
         <is>
@@ -56829,7 +56829,7 @@
         </is>
       </c>
       <c r="C1586" t="n">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="D1586" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         </is>
       </c>
       <c r="C1587" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D1587" t="inlineStr">
         <is>
@@ -56894,7 +56894,7 @@
         </is>
       </c>
       <c r="C1588" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="D1588" t="inlineStr">
         <is>
@@ -57753,7 +57753,7 @@
         </is>
       </c>
       <c r="C1614" t="n">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="D1614" t="inlineStr">
         <is>
@@ -57788,7 +57788,7 @@
         </is>
       </c>
       <c r="C1615" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D1615" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         </is>
       </c>
       <c r="C1617" t="n">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="D1617" t="inlineStr">
         <is>
@@ -58223,7 +58223,7 @@
         </is>
       </c>
       <c r="C1627" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D1627" t="inlineStr">
         <is>
@@ -58237,12 +58237,12 @@
       </c>
       <c r="F1627" s="2" t="inlineStr">
         <is>
-          <t>Cómo parte esta casa un margen: lo de Hacienda y lo que queda.</t>
+          <t>[01626] Cómo parte esta casa un margen: lo de Hacienda y lo que queda.</t>
         </is>
       </c>
       <c r="G1627" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cómo parte esta casa un margen: lo de Hacienda y lo que queda.
+          <t xml:space="preserve">[01626] Cómo parte esta casa un margen: lo de Hacienda y lo que queda.
     Devuelve una función para que cada pantalla la llame con el margen que
     tenga delante —el de una pieza, el de un corte, el del día— sin volver a
     preguntar por la casa. Sin casa o sin tipo puesto, el reparto que sale
@@ -58273,12 +58273,12 @@
       <c r="E1628" t="inlineStr"/>
       <c r="F1628" s="2" t="inlineStr">
         <is>
-          <t>[00351b] Y cómo se parte lo que se gana: lo que hay que apartar para Hacienda y lo que queda limpio.</t>
+          <t>[01627] [00351b] Y cómo se parte lo que se gana: lo que hay que apartar para Hacienda y lo que queda limpio.</t>
         </is>
       </c>
       <c r="G1628" s="2" t="inlineStr">
         <is>
-          <t>[00351b] Y cómo se parte lo que se gana: lo que hay que apartar
+          <t>[01627] [00351b] Y cómo se parte lo que se gana: lo que hay que apartar
 para Hacienda y lo que queda limpio. Va aquí, con la moneda, por
 lo mismo: es cómo habla de dinero esta casa, y así ninguna
 pantalla que enseñe un margen tiene que acordarse de pedirlo.
@@ -58298,7 +58298,7 @@
         </is>
       </c>
       <c r="C1629" t="n">
-        <v>2934</v>
+        <v>2940</v>
       </c>
       <c r="D1629" t="inlineStr">
         <is>
@@ -58308,12 +58308,12 @@
       <c r="E1629" t="inlineStr"/>
       <c r="F1629" s="2" t="inlineStr">
         <is>
-          <t>El impuesto sobre lo que se gana.</t>
+          <t>[01628] El impuesto sobre lo que se gana.</t>
         </is>
       </c>
       <c r="G1629" s="2" t="inlineStr">
         <is>
-          <t>El impuesto sobre lo que se gana. Vacío lo borra —«no lo digo»,
+          <t>[01628] El impuesto sobre lo que se gana. Vacío lo borra —«no lo digo»,
 y entonces no se enseña ningún reparto—; un número que no es un
 número deja el que había, que es lo prudente con algo de lo que
 cuelga cuánto dinero se aparta.</t>
@@ -58332,7 +58332,7 @@
         </is>
       </c>
       <c r="C1630" t="n">
-        <v>1182</v>
+        <v>1200</v>
       </c>
       <c r="D1630" t="inlineStr">
         <is>
@@ -58346,12 +58346,12 @@
       </c>
       <c r="F1630" s="2" t="inlineStr">
         <is>
-          <t>Lo que se ingresó con la carne del día y lo que costó esa carne.</t>
+          <t>[01629] Lo que se ingresó con la carne del día y lo que costó esa carne.</t>
         </is>
       </c>
       <c r="G1630" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lo que se ingresó con la carne del día y lo que costó esa carne.
+          <t xml:space="preserve">[01629] Lo que se ingresó con la carne del día y lo que costó esa carne.
     El coste sale de los apuntes de salida, que es lo que de verdad se
     descontó de la cámara. El ingreso se reparte igual que en la
     trazabilidad: cada venta de un plato reparte su precio sin impuestos entre
@@ -58377,7 +58377,7 @@
         </is>
       </c>
       <c r="C1631" t="n">
-        <v>1113</v>
+        <v>1123</v>
       </c>
       <c r="D1631" t="inlineStr">
         <is>
@@ -58391,12 +58391,12 @@
       </c>
       <c r="F1631" s="2" t="inlineStr">
         <is>
-          <t>Lo ganado con la carne que salió hoy: lo cobrado menos lo que costó.</t>
+          <t>[01630] Lo ganado con la carne que salió hoy: lo cobrado menos lo que costó.</t>
         </is>
       </c>
       <c r="G1631" s="2" t="inlineStr">
         <is>
-          <t>Lo ganado con la carne que salió hoy: lo cobrado menos lo que costó.</t>
+          <t>[01630] Lo ganado con la carne que salió hoy: lo cobrado menos lo que costó.</t>
         </is>
       </c>
     </row>
@@ -58412,7 +58412,7 @@
         </is>
       </c>
       <c r="C1632" t="n">
-        <v>1118</v>
+        <v>1128</v>
       </c>
       <c r="D1632" t="inlineStr">
         <is>
@@ -58426,12 +58426,12 @@
       </c>
       <c r="F1632" s="2" t="inlineStr">
         <is>
-          <t>A qué food cost ha salido el día.</t>
+          <t>[01631] A qué food cost ha salido el día.</t>
         </is>
       </c>
       <c r="G1632" s="2" t="inlineStr">
         <is>
-          <t>A qué food cost ha salido el día. Sin ingresos, no hay porcentaje.</t>
+          <t>[01631] A qué food cost ha salido el día. Sin ingresos, no hay porcentaje.</t>
         </is>
       </c>
     </row>
@@ -58447,7 +58447,7 @@
         </is>
       </c>
       <c r="C1633" t="n">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="D1633" t="inlineStr">
         <is>
@@ -58457,12 +58457,12 @@
       <c r="E1633" t="inlineStr"/>
       <c r="F1633" s="2" t="inlineStr">
         <is>
-          <t>Lo que se ingresó con la carne del día y lo que costó esa carne.</t>
+          <t>[01632] Lo que se ingresó con la carne del día y lo que costó esa carne.</t>
         </is>
       </c>
       <c r="G1633" s="2" t="inlineStr">
         <is>
-          <t>Lo que se ingresó con la carne del día y lo que costó esa carne. Los dos
+          <t>[01632] Lo que se ingresó con la carne del día y lo que costó esa carne. Los dos
 juntos son lo único que contesta «¿cuánto hemos ganado hoy con los kilos
 que han salido?», que es la pregunta del cierre. El parte tenía los
 kilos y las unidades, y con eso se sabe cuánto se ha movido pero no si
@@ -58482,7 +58482,7 @@
         </is>
       </c>
       <c r="C1634" t="n">
-        <v>1207</v>
+        <v>1225</v>
       </c>
       <c r="D1634" t="inlineStr">
         <is>
@@ -58492,12 +58492,12 @@
       <c r="E1634" t="inlineStr"/>
       <c r="F1634" s="2" t="inlineStr">
         <is>
-          <t>La venta que no dice el plato —el conteo del descongelado— se valora por la media de los platos que llevan ese ingrediente: es mejor que apuntarle cero ingreso</t>
+          <t>[01633] La venta que no dice el plato —el conteo del descongelado— se valora por la media de los platos que llevan ese ingrediente: es mejor que apuntarle cero</t>
         </is>
       </c>
       <c r="G1634" s="2" t="inlineStr">
         <is>
-          <t>La venta que no dice el plato —el conteo del descongelado— se
+          <t>[01633] La venta que no dice el plato —el conteo del descongelado— se
 valora por la media de los platos que llevan ese ingrediente:
 es mejor que apuntarle cero ingreso a carne que se vendió.</t>
         </is>
@@ -58525,12 +58525,12 @@
       <c r="E1635" t="inlineStr"/>
       <c r="F1635" s="2" t="inlineStr">
         <is>
-          <t>Lo que se lleva Hacienda de lo que se gana, en tanto por ciento.</t>
+          <t>[01634] Lo que se lleva Hacienda de lo que se gana, en tanto por ciento.</t>
         </is>
       </c>
       <c r="G1635" s="2" t="inlineStr">
         <is>
-          <t>Lo que se lleva Hacienda de lo que se gana, en tanto por ciento. Lo pone
+          <t>[01634] Lo que se lleva Hacienda de lo que se gana, en tanto por ciento. Lo pone
 el manager porque cambia con el país, con el tipo de sociedad y con el
 año, y el programa no tiene por qué saberlo. Sirve para partir el margen
 en dos: lo que hay que apartar y lo que queda limpio.
@@ -58552,7 +58552,7 @@
         </is>
       </c>
       <c r="C1636" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D1636" t="inlineStr">
         <is>
@@ -58566,12 +58566,12 @@
       </c>
       <c r="F1636" s="2" t="inlineStr">
         <is>
-          <t>Cómo parte esta casa un margen.</t>
+          <t>[01635] Cómo parte esta casa un margen.</t>
         </is>
       </c>
       <c r="G1636" s="2" t="inlineStr">
         <is>
-          <t>Cómo parte esta casa un margen. Sin casa o sin tipo, no parte nada.</t>
+          <t>[01635] Cómo parte esta casa un margen. Sin casa o sin tipo, no parte nada.</t>
         </is>
       </c>
     </row>
@@ -58597,12 +58597,12 @@
       <c r="E1637" t="inlineStr"/>
       <c r="F1637" s="2" t="inlineStr">
         <is>
-          <t>[00985b] Y cómo parte esta casa lo que gana: lo que hay que apartar para Hacienda y lo que queda limpio.</t>
+          <t>[01636] [00985b] Y cómo parte esta casa lo que gana: lo que hay que apartar para Hacienda y lo que queda limpio.</t>
         </is>
       </c>
       <c r="G1637" s="2" t="inlineStr">
         <is>
-          <t>[00985b] Y cómo parte esta casa lo que gana: lo que hay que
+          <t>[01636] [00985b] Y cómo parte esta casa lo que gana: lo que hay que
 apartar para Hacienda y lo que queda limpio. Las dos ediciones
 enseñan la misma trazabilidad, así que las dos lo traen.</t>
         </is>
@@ -58634,12 +58634,12 @@
       </c>
       <c r="F1638" s="2" t="inlineStr">
         <is>
-          <t>Lo que se gana, lo que hay que apartar y lo que queda limpio.</t>
+          <t>[01637] Lo que se gana, lo que hay que apartar y lo que queda limpio.</t>
         </is>
       </c>
       <c r="G1638" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lo que se gana, lo que hay que apartar y lo que queda limpio.
+          <t xml:space="preserve">[01637] Lo que se gana, lo que hay que apartar y lo que queda limpio.
 Un lomo que se compra a 300 € y se vende a 900 deja 600 de margen. Pero de
 esos 600 no se lleva la casa 600: una parte se la lleva Hacienda por haberlos
 ganado, y el día que llega el pago tiene que estar apartada. Un restaurante
@@ -58685,12 +58685,12 @@
       </c>
       <c r="F1639" s="2" t="inlineStr">
         <is>
-          <t>El margen partido: lo ganado, lo que se aparta y lo que queda.</t>
+          <t>[01638] El margen partido: lo ganado, lo que se aparta y lo que queda.</t>
         </is>
       </c>
       <c r="G1639" s="2" t="inlineStr">
         <is>
-          <t>El margen partido: lo ganado, lo que se aparta y lo que queda.</t>
+          <t>[01638] El margen partido: lo ganado, lo que se aparta y lo que queda.</t>
         </is>
       </c>
     </row>
@@ -58720,12 +58720,12 @@
       </c>
       <c r="F1640" s="2" t="inlineStr">
         <is>
-          <t>El tanto por ciento que paga esa casa.</t>
+          <t>[01639] El tanto por ciento que paga esa casa.</t>
         </is>
       </c>
       <c r="G1640" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">El tanto por ciento que paga esa casa. Sin poner, cero.
+          <t xml:space="preserve">[01639] El tanto por ciento que paga esa casa. Sin poner, cero.
     Cero quiere decir «no lo he dicho», y entonces no se enseña ningún reparto:
     inventarse un tipo —el del país, el de la media— sería poner en pantalla un
     número que parece de la casa y no lo es, y sobre él se toman decisiones.
@@ -58759,12 +58759,12 @@
       </c>
       <c r="F1641" s="2" t="inlineStr">
         <is>
-          <t>Parte un margen en lo que hay que apartar y lo que queda.</t>
+          <t>[01640] Parte un margen en lo que hay que apartar y lo que queda.</t>
         </is>
       </c>
       <c r="G1641" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parte un margen en lo que hay que apartar y lo que queda.
+          <t xml:space="preserve">[01640] Parte un margen en lo que hay que apartar y lo que queda.
     Un margen negativo —se vendió por debajo de lo que costó— no paga
     impuestos: no se ha ganado nada. Se devuelve entero como pérdida, que es lo
     que es, en vez de enseñar una devolución que nadie va a recibir por una
@@ -58799,12 +58799,12 @@
       </c>
       <c r="F1642" s="2" t="inlineStr">
         <is>
-          <t>El reparto de ese margen con el tipo que tenga puesto la casa.</t>
+          <t>[01641] El reparto de ese margen con el tipo que tenga puesto la casa.</t>
         </is>
       </c>
       <c r="G1642" s="2" t="inlineStr">
         <is>
-          <t>El reparto de ese margen con el tipo que tenga puesto la casa.</t>
+          <t>[01641] El reparto de ese margen con el tipo que tenga puesto la casa.</t>
         </is>
       </c>
     </row>
@@ -58834,12 +58834,12 @@
       </c>
       <c r="F1643" s="2" t="inlineStr">
         <is>
-          <t>Si la casa ha dicho cuánto paga.</t>
+          <t>[01642] Si la casa ha dicho cuánto paga.</t>
         </is>
       </c>
       <c r="G1643" s="2" t="inlineStr">
         <is>
-          <t>Si la casa ha dicho cuánto paga. Sin decirlo no se enseña nada.</t>
+          <t>[01642] Si la casa ha dicho cuánto paga. Sin decirlo no se enseña nada.</t>
         </is>
       </c>
     </row>
@@ -58865,12 +58865,12 @@
       <c r="E1644" t="inlineStr"/>
       <c r="F1644" s="2" t="inlineStr">
         <is>
-          <t>Nadie paga el doscientos por cien de lo que gana.</t>
+          <t>[01643] Nadie paga el doscientos por cien de lo que gana.</t>
         </is>
       </c>
       <c r="G1644" s="2" t="inlineStr">
         <is>
-          <t>Nadie paga el doscientos por cien de lo que gana. Un número mayor que esto
+          <t>[01643] Nadie paga el doscientos por cien de lo que gana. Un número mayor que esto
 es un dedo, no un tipo impositivo, y se recorta antes de que salga en una
 pantalla como si fuera verdad.</t>
         </is>
@@ -58898,12 +58898,12 @@
       <c r="E1645" t="inlineStr"/>
       <c r="F1645" s="2" t="inlineStr">
         <is>
-          <t>El tope también aquí y no solo al leerlo de la casa: esta función la llama cualquiera con el número que tenga a mano, y un tipo del quinientos por ciento dejarí</t>
+          <t>[01644] El tope también aquí y no solo al leerlo de la casa: esta función la llama cualquiera con el número que tenga a mano, y un tipo del quinientos por cient</t>
         </is>
       </c>
       <c r="G1645" s="2" t="inlineStr">
         <is>
-          <t>El tope también aquí y no solo al leerlo de la casa: esta función la
+          <t>[01644] El tope también aquí y no solo al leerlo de la casa: esta función la
 llama cualquiera con el número que tenga a mano, y un tipo del quinientos
 por ciento dejaría el limpio en negativo con toda naturalidad.</t>
         </is>
@@ -58931,12 +58931,12 @@
       <c r="E1646" t="inlineStr"/>
       <c r="F1646" s="2" t="inlineStr">
         <is>
-          <t>Lo ganado con los kilos que han salido hoy, y partido: lo que hay que apartar para Hacienda y lo que queda.</t>
+          <t>[01645] Lo ganado con los kilos que han salido hoy, y partido: lo que hay que apartar para Hacienda y lo que queda.</t>
         </is>
       </c>
       <c r="G1646" s="2" t="inlineStr">
         <is>
-          <t>Lo ganado con los kilos que han salido hoy, y partido: lo que hay que
+          <t>[01645] Lo ganado con los kilos que han salido hoy, y partido: lo que hay que
    apartar para Hacienda y lo que queda. El parte tenía los kilos y las
    unidades —con eso se sabe cuánto se ha movido, no si ha valido la pena—.</t>
         </is>
@@ -58964,12 +58964,12 @@
       <c r="E1647" t="inlineStr"/>
       <c r="F1647" s="2" t="inlineStr">
         <is>
-          <t>Lo que se lleva Hacienda de lo ganado.</t>
+          <t>[01646] Lo que se lleva Hacienda de lo ganado.</t>
         </is>
       </c>
       <c r="G1647" s="2" t="inlineStr">
         <is>
-          <t>Lo que se lleva Hacienda de lo ganado. Va aquí, con la moneda, porque es
+          <t>[01646] Lo que se lleva Hacienda de lo ganado. Va aquí, con la moneda, porque es
      lo mismo: cómo habla de dinero esta casa. En blanco no se enseña ningún
      reparto, que es mejor que enseñar uno inventado.</t>
         </is>
@@ -58997,19 +58997,500 @@
       <c r="E1648" t="inlineStr"/>
       <c r="F1648" s="2" t="inlineStr">
         <is>
-          <t>Y el margen partido, si la casa ha dicho cuánto paga: lo que hay que apartar y lo que queda de verdad.</t>
+          <t>[01647] Y el margen partido, si la casa ha dicho cuánto paga: lo que hay que apartar y lo que queda de verdad.</t>
         </is>
       </c>
       <c r="G1648" s="2" t="inlineStr">
         <is>
-          <t>Y el margen partido, si la casa ha dicho cuánto paga: lo que hay que
+          <t>[01647] Y el margen partido, si la casa ha dicho cuánto paga: lo que hay que
      apartar y lo que queda de verdad. Mirar el margen bruto y gastar contra
      él sale bien once meses y mal el doceavo, siempre el mismo.</t>
         </is>
       </c>
     </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>01648</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>thegrill/meat/app.py</t>
+        </is>
+      </c>
+      <c r="C1649" t="n">
+        <v>222</v>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1649" t="inlineStr"/>
+      <c r="F1649" s="2" t="inlineStr">
+        <is>
+          <t>Y el IVA de las compras, que es el otro: el que se descuenta.</t>
+        </is>
+      </c>
+      <c r="G1649" s="2" t="inlineStr">
+        <is>
+          <t>Y el IVA de las compras, que es el otro: el que se descuenta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>01649</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>thegrill/meat/app.py</t>
+        </is>
+      </c>
+      <c r="C1650" t="n">
+        <v>982</v>
+      </c>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1650" t="inlineStr"/>
+      <c r="F1650" s="2" t="inlineStr">
+        <is>
+          <t>El IVA de la compra es del camión entero y **no se suma al kilo**: se recupera al declarar, así que no es un coste de la casa.</t>
+        </is>
+      </c>
+      <c r="G1650" s="2" t="inlineStr">
+        <is>
+          <t>El IVA de la compra es del camión entero y **no se suma al kilo**: se
+recupera al declarar, así que no es un coste de la casa. Se guarda para
+poder sumar lo que se puede descontar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>01650</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>thegrill/meat/service.py</t>
+        </is>
+      </c>
+      <c r="C1651" t="n">
+        <v>61</v>
+      </c>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1651" t="inlineStr"/>
+      <c r="F1651" s="2" t="inlineStr">
+        <is>
+          <t>El IVA de la compra, en tanto por ciento.</t>
+        </is>
+      </c>
+      <c r="G1651" s="2" t="inlineStr">
+        <is>
+          <t>El IVA de la compra, en tanto por ciento. No es un coste: se recupera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>01651</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>thegrill/meat/service.py</t>
+        </is>
+      </c>
+      <c r="C1652" t="n">
+        <v>382</v>
+      </c>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1652" t="inlineStr"/>
+      <c r="F1652" s="2" t="inlineStr">
+        <is>
+          <t>Aparte del coste a propósito: este IVA se recupera, y meterlo en el kilo inflaría el food cost de todos los platos por un dinero que la casa no ha perdido.</t>
+        </is>
+      </c>
+      <c r="G1652" s="2" t="inlineStr">
+        <is>
+          <t>Aparte del coste a propósito: este IVA se recupera, y meterlo en
+el kilo inflaría el food cost de todos los platos por un dinero
+que la casa no ha perdido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>01652</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>thegrill/meat/service.py</t>
+        </is>
+      </c>
+      <c r="C1653" t="n">
+        <v>1116</v>
+      </c>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1653" t="inlineStr"/>
+      <c r="F1653" s="2" t="inlineStr">
+        <is>
+          <t>Las piezas que entraron hoy, para el IVA que se puede descontar.</t>
+        </is>
+      </c>
+      <c r="G1653" s="2" t="inlineStr">
+        <is>
+          <t>Las piezas que entraron hoy, para el IVA que se puede descontar. Se
+guardan las piezas y no el número ya sumado porque el que suma es
+`impuestos.soportado_de`, que sabe qué base lleva cada una.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>01653</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>thegrill/meat/service.py</t>
+        </is>
+      </c>
+      <c r="C1654" t="n">
+        <v>1187</v>
+      </c>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1654" t="inlineStr"/>
+      <c r="F1654" s="2" t="inlineStr">
+        <is>
+          <t>Lo que entró hoy, para poder sumar el IVA de la compra: lo que se descuenta en la declaración.</t>
+        </is>
+      </c>
+      <c r="G1654" s="2" t="inlineStr">
+        <is>
+          <t>Lo que entró hoy, para poder sumar el IVA de la compra: lo que se
+descuenta en la declaración.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>01654</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>thegrill/models.py</t>
+        </is>
+      </c>
+      <c r="C1655" t="n">
+        <v>551</v>
+      </c>
+      <c r="D1655" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1655" t="inlineStr"/>
+      <c r="F1655" s="2" t="inlineStr">
+        <is>
+          <t>El IVA que se pagó al comprar esta carne, en tanto por ciento.</t>
+        </is>
+      </c>
+      <c r="G1655" s="2" t="inlineStr">
+        <is>
+          <t>El IVA que se pagó al comprar esta carne, en tanto por ciento.
+**No entra en el coste, y es lo que más importa de este campo.** Ese IVA
+se recupera: se descuenta del que se cobra al vender. Meterlo en el kilo
+subiría el coste de la carne un diez por ciento largo, y con él el food
+cost de cada plato, por un dinero que la casa no ha perdido. Se guarda
+aparte para poder sumar lo que se puede descontar en la declaración, que
+es para lo que sirve.
+Es el otro IVA: el de la venta va en cada plato —`Recipe.vat_pct`— y sale
+del precio antes de calcular el food cost. Este es el de la compra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>01655</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>thegrill/web/impuestos.py</t>
+        </is>
+      </c>
+      <c r="C1656" t="n">
+        <v>87</v>
+      </c>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>clase</t>
+        </is>
+      </c>
+      <c r="E1656" t="inlineStr">
+        <is>
+          <t>Soportado</t>
+        </is>
+      </c>
+      <c r="F1656" s="2" t="inlineStr">
+        <is>
+          <t>El IVA pagado en las compras de un periodo: lo que se puede descontar.</t>
+        </is>
+      </c>
+      <c r="G1656" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El IVA pagado en las compras de un periodo: lo que se puede descontar.
+    Se llama soportado porque lo soporta quien compra, no quien vende. Al
+    declarar, se resta del que se ha cobrado en las ventas, así que no es un
+    gasto de la casa: es dinero adelantado a Hacienda que vuelve.
+    </t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>01656</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>thegrill/web/impuestos.py</t>
+        </is>
+      </c>
+      <c r="C1657" t="n">
+        <v>109</v>
+      </c>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>función</t>
+        </is>
+      </c>
+      <c r="E1657" t="inlineStr">
+        <is>
+          <t>soportado_de</t>
+        </is>
+      </c>
+      <c r="F1657" s="2" t="inlineStr">
+        <is>
+          <t>Suma el IVA de la compra de unas piezas.</t>
+        </is>
+      </c>
+      <c r="G1657" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suma el IVA de la compra de unas piezas.
+    La base de cada pieza es lo que costó puesta en la cámara —el género más
+    el transporte y la aduana— porque es sobre eso sobre lo que se paga el IVA
+    de una importación. Una pieza sin IVA apuntado no suma nada: no se supone
+    el tipo del país, que es distinto para la carne, para el pescado y para el
+    vino, y suponerlo aquí acabaría en una declaración.
+    </t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>01657</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>thegrill/web/impuestos.py</t>
+        </is>
+      </c>
+      <c r="C1658" t="n">
+        <v>99</v>
+      </c>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>función</t>
+        </is>
+      </c>
+      <c r="E1658" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="F1658" s="2" t="inlineStr">
+        <is>
+          <t>Lo que se pagó de verdad por esa carne, IVA incluido.</t>
+        </is>
+      </c>
+      <c r="G1658" s="2" t="inlineStr">
+        <is>
+          <t>Lo que se pagó de verdad por esa carne, IVA incluido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>01658</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>thegrill/web/impuestos.py</t>
+        </is>
+      </c>
+      <c r="C1659" t="n">
+        <v>104</v>
+      </c>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>función</t>
+        </is>
+      </c>
+      <c r="E1659" t="inlineStr">
+        <is>
+          <t>hay</t>
+        </is>
+      </c>
+      <c r="F1659" s="2" t="inlineStr">
+        <is>
+          <t>Si hay algo que descontar.</t>
+        </is>
+      </c>
+      <c r="G1659" s="2" t="inlineStr">
+        <is>
+          <t>Si hay algo que descontar. Sin compras con IVA, no se enseña nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>01659</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>thegrill/web/impuestos.py</t>
+        </is>
+      </c>
+      <c r="C1660" t="n">
+        <v>84</v>
+      </c>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1660" t="inlineStr"/>
+      <c r="F1660" s="2" t="inlineStr">
+        <is>
+          <t>el IVA de lo que se compra</t>
+        </is>
+      </c>
+      <c r="G1660" s="2" t="inlineStr">
+        <is>
+          <t>------------------------------------------------- el IVA de lo que se compra</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>01660</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>thegrill/meat/templates/reception.html</t>
+        </is>
+      </c>
+      <c r="C1661" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>plantilla</t>
+        </is>
+      </c>
+      <c r="E1661" t="inlineStr"/>
+      <c r="F1661" s="2" t="inlineStr">
+        <is>
+          <t>El IVA de la compra.</t>
+        </is>
+      </c>
+      <c r="G1661" s="2" t="inlineStr">
+        <is>
+          <t>El IVA de la compra. No se suma al kilo a propósito: se recupera al
+         declarar, y meterlo en el coste inflaría el food cost de todos los
+         platos por un dinero que la casa no ha perdido. Se guarda para poder
+         sumar lo que se puede descontar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>01661</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>thegrill/meat/templates/report.html</t>
+        </is>
+      </c>
+      <c r="C1662" t="n">
+        <v>70</v>
+      </c>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>plantilla</t>
+        </is>
+      </c>
+      <c r="E1662" t="inlineStr"/>
+      <c r="F1662" s="2" t="inlineStr">
+        <is>
+          <t>Y el otro IVA: el que se pagó al comprar.</t>
+        </is>
+      </c>
+      <c r="G1662" s="2" t="inlineStr">
+        <is>
+          <t>Y el otro IVA: el que se pagó al comprar. No es un gasto —se descuenta del
+   que se cobra al vender— y por eso va en su propio bloque y no junto al
+   margen: mezclarlos haría creer que la carne cuesta un diez por ciento más
+   de lo que cuesta.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1648"/>
+  <autoFilter ref="A1:G1662"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -59318,7 +59799,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -59327,7 +59808,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>01628</t>
+          <t>01649</t>
         </is>
       </c>
     </row>
@@ -59518,7 +59999,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -59527,7 +60008,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>01633</t>
+          <t>01653</t>
         </is>
       </c>
     </row>
@@ -59898,7 +60379,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -59907,7 +60388,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>01625</t>
+          <t>01660</t>
         </is>
       </c>
     </row>
@@ -59918,7 +60399,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -59927,7 +60408,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>01645</t>
+          <t>01661</t>
         </is>
       </c>
     </row>
@@ -60018,7 +60499,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -60027,7 +60508,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>01634</t>
+          <t>01654</t>
         </is>
       </c>
     </row>
@@ -60378,7 +60859,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -60387,7 +60868,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>01644</t>
+          <t>01659</t>
         </is>
       </c>
     </row>

--- a/COMENTARIOS.xlsx
+++ b/COMENTARIOS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Por fichero" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comentarios'!$A$1:$G$1662</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comentarios'!$A$1:$G$1667</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por fichero'!$A$1:$D$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1662"/>
+  <dimension ref="A1:G1667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -42050,7 +42050,7 @@
         </is>
       </c>
       <c r="C1172" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D1172" t="inlineStr">
         <is>
@@ -42069,7 +42069,22 @@
       </c>
       <c r="G1172" s="2" t="inlineStr">
         <is>
-          <t>[01171] De euros a céntimos, o de kilos a gramos. Con redondeo al más cercano.</t>
+          <t xml:space="preserve">[01171] De euros a céntimos, o de kilos a gramos. La mitad sube, siempre.
+    La regla escrita, y no la que salga: **al pasar a la unidad pequeña, medio
+    céntimo y medio gramo suben**, y en negativo suben hacia afuera del cero,
+    que es como se devuelve dinero. Es lo que hace una caja registradora, lo
+    que hace Hacienda y lo que va a hacer quien compruebe la cuenta con un
+    lápiz.
+    Antes se hacía con `round()` sobre el número en coma flotante, y ahí la
+    regla no la ponía nadie: la ponía el error de representación. `1,005` no
+    existe en binario —lo que se guarda es 1,00499999999999989…— así que
+    bajaba; `2,675` cae por el otro lado y subía. Dos cifras que una persona
+    escribe igual salían distintas y no había forma de saber cuál sin
+    probarla. De cuarenta mil mitades seguidas, dieciséis mil salían del lado
+    que no era.
+    El paso se hace en decimal, desde el texto más corto que representa ese
+    número —que es el que la persona quiso escribir— y no desde sus bits.
+    </t>
         </is>
       </c>
     </row>
@@ -42085,7 +42100,7 @@
         </is>
       </c>
       <c r="C1173" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="D1173" t="inlineStr">
         <is>
@@ -42120,7 +42135,7 @@
         </is>
       </c>
       <c r="C1174" t="n">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="D1174" t="inlineStr">
         <is>
@@ -42162,7 +42177,7 @@
         </is>
       </c>
       <c r="C1175" t="n">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="D1175" t="inlineStr">
         <is>
@@ -42197,7 +42212,7 @@
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>90</v>
+        <v>151</v>
       </c>
       <c r="D1176" t="inlineStr">
         <is>
@@ -42232,7 +42247,7 @@
         </is>
       </c>
       <c r="C1177" t="n">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="D1177" t="inlineStr">
         <is>
@@ -42267,7 +42282,7 @@
         </is>
       </c>
       <c r="C1178" t="n">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="D1178" t="inlineStr">
         <is>
@@ -42302,7 +42317,7 @@
         </is>
       </c>
       <c r="C1179" t="n">
-        <v>109</v>
+        <v>170</v>
       </c>
       <c r="D1179" t="inlineStr">
         <is>
@@ -42337,7 +42352,7 @@
         </is>
       </c>
       <c r="C1180" t="n">
-        <v>144</v>
+        <v>205</v>
       </c>
       <c r="D1180" t="inlineStr">
         <is>
@@ -42373,7 +42388,7 @@
         </is>
       </c>
       <c r="C1181" t="n">
-        <v>155</v>
+        <v>216</v>
       </c>
       <c r="D1181" t="inlineStr">
         <is>
@@ -42412,7 +42427,7 @@
         </is>
       </c>
       <c r="C1182" t="n">
-        <v>205</v>
+        <v>266</v>
       </c>
       <c r="D1182" t="inlineStr">
         <is>
@@ -42452,7 +42467,7 @@
         </is>
       </c>
       <c r="C1183" t="n">
-        <v>255</v>
+        <v>316</v>
       </c>
       <c r="D1183" t="inlineStr">
         <is>
@@ -42491,7 +42506,7 @@
         </is>
       </c>
       <c r="C1184" t="n">
-        <v>285</v>
+        <v>346</v>
       </c>
       <c r="D1184" t="inlineStr">
         <is>
@@ -42526,7 +42541,7 @@
         </is>
       </c>
       <c r="C1185" t="n">
-        <v>303</v>
+        <v>364</v>
       </c>
       <c r="D1185" t="inlineStr">
         <is>
@@ -42569,7 +42584,7 @@
         </is>
       </c>
       <c r="C1186" t="n">
-        <v>148</v>
+        <v>209</v>
       </c>
       <c r="D1186" t="inlineStr">
         <is>
@@ -42604,7 +42619,7 @@
         </is>
       </c>
       <c r="C1187" t="n">
-        <v>326</v>
+        <v>387</v>
       </c>
       <c r="D1187" t="inlineStr">
         <is>
@@ -42643,7 +42658,7 @@
         </is>
       </c>
       <c r="C1188" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="D1188" t="inlineStr">
         <is>
@@ -42674,7 +42689,7 @@
         </is>
       </c>
       <c r="C1189" t="n">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="D1189" t="inlineStr">
         <is>
@@ -42684,14 +42699,15 @@
       <c r="E1189" t="inlineStr"/>
       <c r="F1189" s="2" t="inlineStr">
         <is>
-          <t>[01188] Quien más parte decimal tiene, primero.</t>
+          <t>[01188] Quien más parte decimal tiene, primero, y en el empate el primero de la lista.</t>
         </is>
       </c>
       <c r="G1189" s="2" t="inlineStr">
         <is>
-          <t>[01188] Quien más parte decimal tiene, primero. El signo importa: repartiendo
-un número negativo —una devolución, un ajuste a la baja— lo que sobra
-también es negativo y va a quien menos le falta.</t>
+          <t>[01188] Quien más parte decimal tiene, primero, y en el empate el primero
+de la lista. El signo importa: repartiendo un número negativo —una
+devolución, un ajuste a la baja— lo que sobra también es negativo y
+va a quien menos le falta.</t>
         </is>
       </c>
     </row>
@@ -42707,7 +42723,7 @@
         </is>
       </c>
       <c r="C1190" t="n">
-        <v>115</v>
+        <v>176</v>
       </c>
       <c r="D1190" t="inlineStr">
         <is>
@@ -42758,7 +42774,7 @@
         </is>
       </c>
       <c r="C1191" t="n">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="D1191" t="inlineStr">
         <is>
@@ -42802,7 +42818,7 @@
         </is>
       </c>
       <c r="C1192" t="n">
-        <v>235</v>
+        <v>296</v>
       </c>
       <c r="D1192" t="inlineStr">
         <is>
@@ -42841,7 +42857,7 @@
         </is>
       </c>
       <c r="C1193" t="n">
-        <v>283</v>
+        <v>344</v>
       </c>
       <c r="D1193" t="inlineStr">
         <is>
@@ -42872,7 +42888,7 @@
         </is>
       </c>
       <c r="C1194" t="n">
-        <v>316</v>
+        <v>377</v>
       </c>
       <c r="D1194" t="inlineStr">
         <is>
@@ -58671,7 +58687,7 @@
         </is>
       </c>
       <c r="C1639" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1639" t="inlineStr">
         <is>
@@ -58706,7 +58722,7 @@
         </is>
       </c>
       <c r="C1640" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D1640" t="inlineStr">
         <is>
@@ -58745,7 +58761,7 @@
         </is>
       </c>
       <c r="C1641" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D1641" t="inlineStr">
         <is>
@@ -58785,7 +58801,7 @@
         </is>
       </c>
       <c r="C1642" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D1642" t="inlineStr">
         <is>
@@ -58820,7 +58836,7 @@
         </is>
       </c>
       <c r="C1643" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D1643" t="inlineStr">
         <is>
@@ -58855,7 +58871,7 @@
         </is>
       </c>
       <c r="C1644" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1644" t="inlineStr">
         <is>
@@ -58888,7 +58904,7 @@
         </is>
       </c>
       <c r="C1645" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D1645" t="inlineStr">
         <is>
@@ -59030,12 +59046,12 @@
       <c r="E1649" t="inlineStr"/>
       <c r="F1649" s="2" t="inlineStr">
         <is>
-          <t>Y el IVA de las compras, que es el otro: el que se descuenta.</t>
+          <t>[01648] Y el IVA de las compras, que es el otro: el que se descuenta.</t>
         </is>
       </c>
       <c r="G1649" s="2" t="inlineStr">
         <is>
-          <t>Y el IVA de las compras, que es el otro: el que se descuenta.</t>
+          <t>[01648] Y el IVA de las compras, que es el otro: el que se descuenta.</t>
         </is>
       </c>
     </row>
@@ -59061,12 +59077,12 @@
       <c r="E1650" t="inlineStr"/>
       <c r="F1650" s="2" t="inlineStr">
         <is>
-          <t>El IVA de la compra es del camión entero y **no se suma al kilo**: se recupera al declarar, así que no es un coste de la casa.</t>
+          <t>[01649] El IVA de la compra es del camión entero y **no se suma al kilo**: se recupera al declarar, así que no es un coste de la casa.</t>
         </is>
       </c>
       <c r="G1650" s="2" t="inlineStr">
         <is>
-          <t>El IVA de la compra es del camión entero y **no se suma al kilo**: se
+          <t>[01649] El IVA de la compra es del camión entero y **no se suma al kilo**: se
 recupera al declarar, así que no es un coste de la casa. Se guarda para
 poder sumar lo que se puede descontar.</t>
         </is>
@@ -59094,12 +59110,12 @@
       <c r="E1651" t="inlineStr"/>
       <c r="F1651" s="2" t="inlineStr">
         <is>
-          <t>El IVA de la compra, en tanto por ciento.</t>
+          <t>[01650] El IVA de la compra, en tanto por ciento.</t>
         </is>
       </c>
       <c r="G1651" s="2" t="inlineStr">
         <is>
-          <t>El IVA de la compra, en tanto por ciento. No es un coste: se recupera.</t>
+          <t>[01650] El IVA de la compra, en tanto por ciento. No es un coste: se recupera.</t>
         </is>
       </c>
     </row>
@@ -59125,12 +59141,12 @@
       <c r="E1652" t="inlineStr"/>
       <c r="F1652" s="2" t="inlineStr">
         <is>
-          <t>Aparte del coste a propósito: este IVA se recupera, y meterlo en el kilo inflaría el food cost de todos los platos por un dinero que la casa no ha perdido.</t>
+          <t>[01651] Aparte del coste a propósito: este IVA se recupera, y meterlo en el kilo inflaría el food cost de todos los platos por un dinero que la casa no ha perdi</t>
         </is>
       </c>
       <c r="G1652" s="2" t="inlineStr">
         <is>
-          <t>Aparte del coste a propósito: este IVA se recupera, y meterlo en
+          <t>[01651] Aparte del coste a propósito: este IVA se recupera, y meterlo en
 el kilo inflaría el food cost de todos los platos por un dinero
 que la casa no ha perdido.</t>
         </is>
@@ -59158,12 +59174,12 @@
       <c r="E1653" t="inlineStr"/>
       <c r="F1653" s="2" t="inlineStr">
         <is>
-          <t>Las piezas que entraron hoy, para el IVA que se puede descontar.</t>
+          <t>[01652] Las piezas que entraron hoy, para el IVA que se puede descontar.</t>
         </is>
       </c>
       <c r="G1653" s="2" t="inlineStr">
         <is>
-          <t>Las piezas que entraron hoy, para el IVA que se puede descontar. Se
+          <t>[01652] Las piezas que entraron hoy, para el IVA que se puede descontar. Se
 guardan las piezas y no el número ya sumado porque el que suma es
 `impuestos.soportado_de`, que sabe qué base lleva cada una.</t>
         </is>
@@ -59191,12 +59207,12 @@
       <c r="E1654" t="inlineStr"/>
       <c r="F1654" s="2" t="inlineStr">
         <is>
-          <t>Lo que entró hoy, para poder sumar el IVA de la compra: lo que se descuenta en la declaración.</t>
+          <t>[01653] Lo que entró hoy, para poder sumar el IVA de la compra: lo que se descuenta en la declaración.</t>
         </is>
       </c>
       <c r="G1654" s="2" t="inlineStr">
         <is>
-          <t>Lo que entró hoy, para poder sumar el IVA de la compra: lo que se
+          <t>[01653] Lo que entró hoy, para poder sumar el IVA de la compra: lo que se
 descuenta en la declaración.</t>
         </is>
       </c>
@@ -59223,12 +59239,12 @@
       <c r="E1655" t="inlineStr"/>
       <c r="F1655" s="2" t="inlineStr">
         <is>
-          <t>El IVA que se pagó al comprar esta carne, en tanto por ciento.</t>
+          <t>[01654] El IVA que se pagó al comprar esta carne, en tanto por ciento.</t>
         </is>
       </c>
       <c r="G1655" s="2" t="inlineStr">
         <is>
-          <t>El IVA que se pagó al comprar esta carne, en tanto por ciento.
+          <t>[01654] El IVA que se pagó al comprar esta carne, en tanto por ciento.
 **No entra en el coste, y es lo que más importa de este campo.** Ese IVA
 se recupera: se descuenta del que se cobra al vender. Meterlo en el kilo
 subiría el coste de la carne un diez por ciento largo, y con él el food
@@ -59252,7 +59268,7 @@
         </is>
       </c>
       <c r="C1656" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D1656" t="inlineStr">
         <is>
@@ -59266,12 +59282,12 @@
       </c>
       <c r="F1656" s="2" t="inlineStr">
         <is>
-          <t>El IVA pagado en las compras de un periodo: lo que se puede descontar.</t>
+          <t>[01655] El IVA pagado en las compras de un periodo: lo que se puede descontar.</t>
         </is>
       </c>
       <c r="G1656" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">El IVA pagado en las compras de un periodo: lo que se puede descontar.
+          <t xml:space="preserve">[01655] El IVA pagado en las compras de un periodo: lo que se puede descontar.
     Se llama soportado porque lo soporta quien compra, no quien vende. Al
     declarar, se resta del que se ha cobrado en las ventas, así que no es un
     gasto de la casa: es dinero adelantado a Hacienda que vuelve.
@@ -59291,7 +59307,7 @@
         </is>
       </c>
       <c r="C1657" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D1657" t="inlineStr">
         <is>
@@ -59305,12 +59321,12 @@
       </c>
       <c r="F1657" s="2" t="inlineStr">
         <is>
-          <t>Suma el IVA de la compra de unas piezas.</t>
+          <t>[01656] Suma el IVA de la compra de unas piezas.</t>
         </is>
       </c>
       <c r="G1657" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suma el IVA de la compra de unas piezas.
+          <t xml:space="preserve">[01656] Suma el IVA de la compra de unas piezas.
     La base de cada pieza es lo que costó puesta en la cámara —el género más
     el transporte y la aduana— porque es sobre eso sobre lo que se paga el IVA
     de una importación. Una pieza sin IVA apuntado no suma nada: no se supone
@@ -59332,7 +59348,7 @@
         </is>
       </c>
       <c r="C1658" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D1658" t="inlineStr">
         <is>
@@ -59346,12 +59362,12 @@
       </c>
       <c r="F1658" s="2" t="inlineStr">
         <is>
-          <t>Lo que se pagó de verdad por esa carne, IVA incluido.</t>
+          <t>[01657] Lo que se pagó de verdad por esa carne, IVA incluido.</t>
         </is>
       </c>
       <c r="G1658" s="2" t="inlineStr">
         <is>
-          <t>Lo que se pagó de verdad por esa carne, IVA incluido.</t>
+          <t>[01657] Lo que se pagó de verdad por esa carne, IVA incluido.</t>
         </is>
       </c>
     </row>
@@ -59367,7 +59383,7 @@
         </is>
       </c>
       <c r="C1659" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D1659" t="inlineStr">
         <is>
@@ -59381,12 +59397,12 @@
       </c>
       <c r="F1659" s="2" t="inlineStr">
         <is>
-          <t>Si hay algo que descontar.</t>
+          <t>[01658] Si hay algo que descontar.</t>
         </is>
       </c>
       <c r="G1659" s="2" t="inlineStr">
         <is>
-          <t>Si hay algo que descontar. Sin compras con IVA, no se enseña nada.</t>
+          <t>[01658] Si hay algo que descontar. Sin compras con IVA, no se enseña nada.</t>
         </is>
       </c>
     </row>
@@ -59402,7 +59418,7 @@
         </is>
       </c>
       <c r="C1660" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D1660" t="inlineStr">
         <is>
@@ -59412,12 +59428,12 @@
       <c r="E1660" t="inlineStr"/>
       <c r="F1660" s="2" t="inlineStr">
         <is>
-          <t>el IVA de lo que se compra</t>
+          <t>[01659] ------------------------------------------------- el IVA de lo que se compra</t>
         </is>
       </c>
       <c r="G1660" s="2" t="inlineStr">
         <is>
-          <t>------------------------------------------------- el IVA de lo que se compra</t>
+          <t>[01659] ------------------------------------------------- el IVA de lo que se compra</t>
         </is>
       </c>
     </row>
@@ -59443,12 +59459,12 @@
       <c r="E1661" t="inlineStr"/>
       <c r="F1661" s="2" t="inlineStr">
         <is>
-          <t>El IVA de la compra.</t>
+          <t>[01660] El IVA de la compra.</t>
         </is>
       </c>
       <c r="G1661" s="2" t="inlineStr">
         <is>
-          <t>El IVA de la compra. No se suma al kilo a propósito: se recupera al
+          <t>[01660] El IVA de la compra. No se suma al kilo a propósito: se recupera al
          declarar, y meterlo en el coste inflaría el food cost de todos los
          platos por un dinero que la casa no ha perdido. Se guarda para poder
          sumar lo que se puede descontar.</t>
@@ -59477,20 +59493,201 @@
       <c r="E1662" t="inlineStr"/>
       <c r="F1662" s="2" t="inlineStr">
         <is>
-          <t>Y el otro IVA: el que se pagó al comprar.</t>
+          <t>[01661] Y el otro IVA: el que se pagó al comprar.</t>
         </is>
       </c>
       <c r="G1662" s="2" t="inlineStr">
         <is>
-          <t>Y el otro IVA: el que se pagó al comprar. No es un gasto —se descuenta del
+          <t>[01661] Y el otro IVA: el que se pagó al comprar. No es un gasto —se descuenta del
    que se cobra al vender— y por eso va en su propio bloque y no junto al
    margen: mezclarlos haría creer que la carne cuesta un diez por ciento más
    de lo que cuesta.</t>
         </is>
       </c>
     </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>01662</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>thegrill/web/exacto.py</t>
+        </is>
+      </c>
+      <c r="C1663" t="n">
+        <v>130</v>
+      </c>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>función</t>
+        </is>
+      </c>
+      <c r="E1663" t="inlineStr">
+        <is>
+          <t>_pesos_enteros</t>
+        </is>
+      </c>
+      <c r="F1663" s="2" t="inlineStr">
+        <is>
+          <t>Los pesos como enteros con denominador común, sin perder nada.</t>
+        </is>
+      </c>
+      <c r="G1663" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Los pesos como enteros con denominador común, sin perder nada.
+    Cada peso se lee por su escritura más corta —la que una persona pondría—
+    y no por sus bits: `0,1` es un décimo, no 0,1000000000000000055…  Con el
+    denominador común, comparar restos es comparar enteros, y ahí no hay
+    empate que se decida por casualidad.
+    </t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>01663</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>thegrill/web/exacto.py</t>
+        </is>
+      </c>
+      <c r="C1664" t="n">
+        <v>89</v>
+      </c>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1664" t="inlineStr"/>
+      <c r="F1664" s="2" t="inlineStr">
+        <is>
+          <t>[01187b] Los pesos, a números enteros y exactos.</t>
+        </is>
+      </c>
+      <c r="G1664" s="2" t="inlineStr">
+        <is>
+          <t>[01187b] Los pesos, a números enteros y exactos. Esto es lo que hace que el
+reparto sea de verdad reproducible.
+Antes la parte de cada uno se calculaba en coma flotante y el orden de
+los restos también. Dos restos que valen lo mismo —o casi— acababan
+ordenados por el error de representación, así que el céntimo que sobra se
+lo llevaba uno u otro según cómo hubieran caído los bits. Dos cosas malas
+salían de ahí: el resultado no era el que da la cuenta exacta (un caso de
+cada cinco mil), y **cambiaba al cambiar la unidad de los pesos**: los
+mismos cortes con el índice de valor puesto en 1,6 o en 16 —que es la
+misma proporción— repartían el céntimo a cortes distintos.
+Los pesos son proporciones: lo único que dicen es cuánto le toca a cada
+uno respecto a los demás. Pasados a enteros con denominador común, la
+división y los restos se hacen con enteros, que no tienen error, y las
+dos cosas se arreglan solas: sale lo que dice la cuenta exacta, y sale lo
+mismo midiendo los pesos en kilos o en gramos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>01664</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>thegrill/web/exacto.py</t>
+        </is>
+      </c>
+      <c r="C1665" t="n">
+        <v>111</v>
+      </c>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1665" t="inlineStr"/>
+      <c r="F1665" s="2" t="inlineStr">
+        <is>
+          <t>Hacia cero, como se ha repartido siempre.</t>
+        </is>
+      </c>
+      <c r="G1665" s="2" t="inlineStr">
+        <is>
+          <t>Hacia cero, como se ha repartido siempre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>01665</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>thegrill/web/impuestos.py</t>
+        </is>
+      </c>
+      <c r="C1666" t="n">
+        <v>69</v>
+      </c>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1666" t="inlineStr"/>
+      <c r="F1666" s="2" t="inlineStr">
+        <is>
+          <t>Al céntimo con la regla de siempre —la mitad sube—, y no con la que le salga a la coma flotante: esto es dinero que alguien va a apartar, y la cuenta tiene que</t>
+        </is>
+      </c>
+      <c r="G1666" s="2" t="inlineStr">
+        <is>
+          <t>Al céntimo con la regla de siempre —la mitad sube—, y no con la que le
+salga a la coma flotante: esto es dinero que alguien va a apartar, y la
+cuenta tiene que dar lo mismo hecha con un lápiz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>01666</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>thegrill/web/impuestos.py</t>
+        </is>
+      </c>
+      <c r="C1667" t="n">
+        <v>80</v>
+      </c>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1667" t="inlineStr"/>
+      <c r="F1667" s="2" t="inlineStr">
+        <is>
+          <t>Lo que queda sale de restar, no de otra cuenta: así las dos partes suman el margen **exacto** y no se pierde el céntimo entre las dos.</t>
+        </is>
+      </c>
+      <c r="G1667" s="2" t="inlineStr">
+        <is>
+          <t>Lo que queda sale de restar, no de otra cuenta: así las dos partes suman
+el margen **exacto** y no se pierde el céntimo entre las dos.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1662"/>
+  <autoFilter ref="A1:G1667"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -60799,7 +60996,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -60808,7 +61005,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>01193</t>
+          <t>01664</t>
         </is>
       </c>
     </row>
@@ -60859,7 +61056,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -60868,7 +61065,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>01659</t>
+          <t>01666</t>
         </is>
       </c>
     </row>

--- a/COMENTARIOS.xlsx
+++ b/COMENTARIOS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Por fichero" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comentarios'!$A$1:$G$1667</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comentarios'!$A$1:$G$1668</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por fichero'!$A$1:$D$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1667"/>
+  <dimension ref="A1:G1668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20348,7 +20348,7 @@
         </is>
       </c>
       <c r="C563" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         </is>
       </c>
       <c r="C564" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         </is>
       </c>
       <c r="C565" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         </is>
       </c>
       <c r="C566" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         </is>
       </c>
       <c r="C567" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         </is>
       </c>
       <c r="C568" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="C569" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         </is>
       </c>
       <c r="C570" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         </is>
       </c>
       <c r="C571" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         </is>
       </c>
       <c r="C572" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         </is>
       </c>
       <c r="C573" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         </is>
       </c>
       <c r="C574" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         </is>
       </c>
       <c r="C575" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="C576" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         </is>
       </c>
       <c r="C577" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         </is>
       </c>
       <c r="C578" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="C579" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         </is>
       </c>
       <c r="C580" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         </is>
       </c>
       <c r="C581" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="C582" t="n">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         </is>
       </c>
       <c r="C583" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         </is>
       </c>
       <c r="C584" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         </is>
       </c>
       <c r="C585" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         </is>
       </c>
       <c r="C586" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         </is>
       </c>
       <c r="C587" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         </is>
       </c>
       <c r="C588" t="n">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         </is>
       </c>
       <c r="C589" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         </is>
       </c>
       <c r="C590" t="n">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         </is>
       </c>
       <c r="C591" t="n">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         </is>
       </c>
       <c r="C592" t="n">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         </is>
       </c>
       <c r="C593" t="n">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         </is>
       </c>
       <c r="C594" t="n">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         </is>
       </c>
       <c r="C595" t="n">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         </is>
       </c>
       <c r="C596" t="n">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         </is>
       </c>
       <c r="C597" t="n">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         </is>
       </c>
       <c r="C598" t="n">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         </is>
       </c>
       <c r="C599" t="n">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         </is>
       </c>
       <c r="C600" t="n">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         </is>
       </c>
       <c r="C601" t="n">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         </is>
       </c>
       <c r="C602" t="n">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         </is>
       </c>
       <c r="C603" t="n">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         </is>
       </c>
       <c r="C604" t="n">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         </is>
       </c>
       <c r="C605" t="n">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         </is>
       </c>
       <c r="C606" t="n">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         </is>
       </c>
       <c r="C607" t="n">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         </is>
       </c>
       <c r="C608" t="n">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         </is>
       </c>
       <c r="C609" t="n">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         </is>
       </c>
       <c r="C610" t="n">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         </is>
       </c>
       <c r="C611" t="n">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         </is>
       </c>
       <c r="C612" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         </is>
       </c>
       <c r="C613" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         </is>
       </c>
       <c r="C614" t="n">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         </is>
       </c>
       <c r="C615" t="n">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         </is>
       </c>
       <c r="C616" t="n">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         </is>
       </c>
       <c r="C617" t="n">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         </is>
       </c>
       <c r="C618" t="n">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="C619" t="n">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         </is>
       </c>
       <c r="C620" t="n">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         </is>
       </c>
       <c r="C621" t="n">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         </is>
       </c>
       <c r="C622" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         </is>
       </c>
       <c r="C623" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         </is>
       </c>
       <c r="C624" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         </is>
       </c>
       <c r="C625" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         </is>
       </c>
       <c r="C626" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         </is>
       </c>
       <c r="C627" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         </is>
       </c>
       <c r="C628" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         </is>
       </c>
       <c r="C629" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         </is>
       </c>
       <c r="C630" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         </is>
       </c>
       <c r="C631" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         </is>
       </c>
       <c r="C632" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         </is>
       </c>
       <c r="C633" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         </is>
       </c>
       <c r="C634" t="n">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         </is>
       </c>
       <c r="C635" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         </is>
       </c>
       <c r="C636" t="n">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         </is>
       </c>
       <c r="C637" t="n">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         </is>
       </c>
       <c r="C638" t="n">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         </is>
       </c>
       <c r="C639" t="n">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         </is>
       </c>
       <c r="C640" t="n">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         </is>
       </c>
       <c r="C641" t="n">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         </is>
       </c>
       <c r="C642" t="n">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         </is>
       </c>
       <c r="C643" t="n">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         </is>
       </c>
       <c r="C644" t="n">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         </is>
       </c>
       <c r="C645" t="n">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         </is>
       </c>
       <c r="C646" t="n">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         </is>
       </c>
       <c r="C647" t="n">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         </is>
       </c>
       <c r="C648" t="n">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="C649" t="n">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         </is>
       </c>
       <c r="C650" t="n">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         </is>
       </c>
       <c r="C651" t="n">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         </is>
       </c>
       <c r="C652" t="n">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42317,7 +42317,7 @@
         </is>
       </c>
       <c r="C1179" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D1179" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         </is>
       </c>
       <c r="C1180" t="n">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D1180" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         </is>
       </c>
       <c r="C1181" t="n">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="D1181" t="inlineStr">
         <is>
@@ -42427,7 +42427,7 @@
         </is>
       </c>
       <c r="C1182" t="n">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="D1182" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         </is>
       </c>
       <c r="C1183" t="n">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D1183" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         </is>
       </c>
       <c r="C1184" t="n">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="D1184" t="inlineStr">
         <is>
@@ -42541,7 +42541,7 @@
         </is>
       </c>
       <c r="C1185" t="n">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="D1185" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         </is>
       </c>
       <c r="C1186" t="n">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="D1186" t="inlineStr">
         <is>
@@ -42619,7 +42619,7 @@
         </is>
       </c>
       <c r="C1187" t="n">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="D1187" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         </is>
       </c>
       <c r="C1190" t="n">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="D1190" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         </is>
       </c>
       <c r="C1191" t="n">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="D1191" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         </is>
       </c>
       <c r="C1192" t="n">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="D1192" t="inlineStr">
         <is>
@@ -42857,7 +42857,7 @@
         </is>
       </c>
       <c r="C1193" t="n">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="D1193" t="inlineStr">
         <is>
@@ -42888,7 +42888,7 @@
         </is>
       </c>
       <c r="C1194" t="n">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="D1194" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         </is>
       </c>
       <c r="C1615" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D1615" t="inlineStr">
         <is>
@@ -57849,7 +57849,7 @@
         </is>
       </c>
       <c r="C1616" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1616" t="inlineStr">
         <is>
@@ -57882,7 +57882,7 @@
         </is>
       </c>
       <c r="C1617" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D1617" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         </is>
       </c>
       <c r="C1630" t="n">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="D1630" t="inlineStr">
         <is>
@@ -58393,7 +58393,7 @@
         </is>
       </c>
       <c r="C1631" t="n">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D1631" t="inlineStr">
         <is>
@@ -58428,7 +58428,7 @@
         </is>
       </c>
       <c r="C1632" t="n">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D1632" t="inlineStr">
         <is>
@@ -58463,7 +58463,7 @@
         </is>
       </c>
       <c r="C1633" t="n">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D1633" t="inlineStr">
         <is>
@@ -58498,7 +58498,7 @@
         </is>
       </c>
       <c r="C1634" t="n">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="D1634" t="inlineStr">
         <is>
@@ -59100,7 +59100,7 @@
         </is>
       </c>
       <c r="C1651" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1651" t="inlineStr">
         <is>
@@ -59131,7 +59131,7 @@
         </is>
       </c>
       <c r="C1652" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D1652" t="inlineStr">
         <is>
@@ -59164,7 +59164,7 @@
         </is>
       </c>
       <c r="C1653" t="n">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D1653" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         </is>
       </c>
       <c r="C1654" t="n">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="D1654" t="inlineStr">
         <is>
@@ -59531,12 +59531,12 @@
       </c>
       <c r="F1663" s="2" t="inlineStr">
         <is>
-          <t>Los pesos como enteros con denominador común, sin perder nada.</t>
+          <t>[01662] Los pesos como enteros con denominador común, sin perder nada.</t>
         </is>
       </c>
       <c r="G1663" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los pesos como enteros con denominador común, sin perder nada.
+          <t xml:space="preserve">[01662] Los pesos como enteros con denominador común, sin perder nada.
     Cada peso se lee por su escritura más corta —la que una persona pondría—
     y no por sus bits: `0,1` es un décimo, no 0,1000000000000000055…  Con el
     denominador común, comparar restos es comparar enteros, y ahí no hay
@@ -59567,12 +59567,12 @@
       <c r="E1664" t="inlineStr"/>
       <c r="F1664" s="2" t="inlineStr">
         <is>
-          <t>[01187b] Los pesos, a números enteros y exactos.</t>
+          <t>[01663] [01187b] Los pesos, a números enteros y exactos.</t>
         </is>
       </c>
       <c r="G1664" s="2" t="inlineStr">
         <is>
-          <t>[01187b] Los pesos, a números enteros y exactos. Esto es lo que hace que el
+          <t>[01663] [01187b] Los pesos, a números enteros y exactos. Esto es lo que hace que el
 reparto sea de verdad reproducible.
 Antes la parte de cada uno se calculaba en coma flotante y el orden de
 los restos también. Dos restos que valen lo mismo —o casi— acababan
@@ -59612,12 +59612,12 @@
       <c r="E1665" t="inlineStr"/>
       <c r="F1665" s="2" t="inlineStr">
         <is>
-          <t>Hacia cero, como se ha repartido siempre.</t>
+          <t>[01664] Hacia cero, como se ha repartido siempre.</t>
         </is>
       </c>
       <c r="G1665" s="2" t="inlineStr">
         <is>
-          <t>Hacia cero, como se ha repartido siempre.</t>
+          <t>[01664] Hacia cero, como se ha repartido siempre.</t>
         </is>
       </c>
     </row>
@@ -59643,12 +59643,12 @@
       <c r="E1666" t="inlineStr"/>
       <c r="F1666" s="2" t="inlineStr">
         <is>
-          <t>Al céntimo con la regla de siempre —la mitad sube—, y no con la que le salga a la coma flotante: esto es dinero que alguien va a apartar, y la cuenta tiene que</t>
+          <t>[01665] Al céntimo con la regla de siempre —la mitad sube—, y no con la que le salga a la coma flotante: esto es dinero que alguien va a apartar, y la cuenta ti</t>
         </is>
       </c>
       <c r="G1666" s="2" t="inlineStr">
         <is>
-          <t>Al céntimo con la regla de siempre —la mitad sube—, y no con la que le
+          <t>[01665] Al céntimo con la regla de siempre —la mitad sube—, y no con la que le
 salga a la coma flotante: esto es dinero que alguien va a apartar, y la
 cuenta tiene que dar lo mismo hecha con un lápiz.</t>
         </is>
@@ -59676,18 +59676,60 @@
       <c r="E1667" t="inlineStr"/>
       <c r="F1667" s="2" t="inlineStr">
         <is>
-          <t>Lo que queda sale de restar, no de otra cuenta: así las dos partes suman el margen **exacto** y no se pierde el céntimo entre las dos.</t>
+          <t>[01666] Lo que queda sale de restar, no de otra cuenta: así las dos partes suman el margen **exacto** y no se pierde el céntimo entre las dos.</t>
         </is>
       </c>
       <c r="G1667" s="2" t="inlineStr">
         <is>
-          <t>Lo que queda sale de restar, no de otra cuenta: así las dos partes suman
+          <t>[01666] Lo que queda sale de restar, no de otra cuenta: así las dos partes suman
 el margen **exacto** y no se pierde el céntimo entre las dos.</t>
         </is>
       </c>
     </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>01667</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>thegrill/web/exacto.py</t>
+        </is>
+      </c>
+      <c r="C1668" t="n">
+        <v>170</v>
+      </c>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>función</t>
+        </is>
+      </c>
+      <c r="E1668" t="inlineStr">
+        <is>
+          <t>eur</t>
+        </is>
+      </c>
+      <c r="F1668" s="2" t="inlineStr">
+        <is>
+          <t>Lo mismo que `euros`, pero nunca devuelve nada: un total se enseña.</t>
+        </is>
+      </c>
+      <c r="G1668" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lo mismo que `euros`, pero nunca devuelve nada: un total se enseña.
+    Es para los números que se pintan en una pantalla —el margen, lo
+    ingresado, lo que costó— y que alguien va a comparar con una factura. Ahí
+    no vale `round(x, 2)`: redondea por donde caiga el binario, y una de cada
+    mil quinientas cifras sale un céntimo por debajo de lo que dice la cuenta
+    hecha a mano. Siempre en las mismas, además: las que caen justo en medio
+    del céntimo, que son las que salen de multiplicar kilos por un precio.
+    </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1667"/>
+  <autoFilter ref="A1:G1668"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -60996,7 +61038,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -61005,7 +61047,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>01664</t>
+          <t>01667</t>
         </is>
       </c>
     </row>

--- a/COMENTARIOS.xlsx
+++ b/COMENTARIOS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Por fichero" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comentarios'!$A$1:$G$1668</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comentarios'!$A$1:$G$1670</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por fichero'!$A$1:$D$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1668"/>
+  <dimension ref="A1:G1670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4246,7 +4246,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -59712,12 +59712,12 @@
       </c>
       <c r="F1668" s="2" t="inlineStr">
         <is>
-          <t>Lo mismo que `euros`, pero nunca devuelve nada: un total se enseña.</t>
+          <t>[01667] Lo mismo que `euros`, pero nunca devuelve nada: un total se enseña.</t>
         </is>
       </c>
       <c r="G1668" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lo mismo que `euros`, pero nunca devuelve nada: un total se enseña.
+          <t xml:space="preserve">[01667] Lo mismo que `euros`, pero nunca devuelve nada: un total se enseña.
     Es para los números que se pintan en una pantalla —el margen, lo
     ingresado, lo que costó— y que alguien va a comparar con una factura. Ahí
     no vale `round(x, 2)`: redondea por donde caiga el binario, y una de cada
@@ -59728,8 +59728,80 @@
         </is>
       </c>
     </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>01668</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>thegrill/engine/fefo.py</t>
+        </is>
+      </c>
+      <c r="C1669" t="n">
+        <v>44</v>
+      </c>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1669" t="inlineStr"/>
+      <c r="F1669" s="2" t="inlineStr">
+        <is>
+          <t>Los dos totales, con los mismos decimales con los que se apunta cada salida.</t>
+        </is>
+      </c>
+      <c r="G1669" s="2" t="inlineStr">
+        <is>
+          <t>Los dos totales, con los mismos decimales con los que se apunta cada
+salida. Iban a cuatro mientras las salidas iban a seis, así que el total
+no era la suma de sus partes: hasta medio decigramo y medio céntimo de
+diferencia entre lo que dice el resumen y lo que dicen las líneas. En un
+módulo cuyo trabajo entero es que las partes sumen el total, ese es el
+sitio donde menos puede pasar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>01669</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>thegrill/engine/fefo.py</t>
+        </is>
+      </c>
+      <c r="C1670" t="n">
+        <v>103</v>
+      </c>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1670" t="inlineStr"/>
+      <c r="F1670" s="2" t="inlineStr">
+        <is>
+          <t>Lo que se apunta es lo que se saca, con los mismos decimales.</t>
+        </is>
+      </c>
+      <c r="G1670" s="2" t="inlineStr">
+        <is>
+          <t>Lo que se apunta es lo que se saca, con los mismos decimales.
+Se apuntaba redondeado a cuatro y se descontaba a seis, así que el
+papel decía una cosa y el lote otra: hasta medio decigramo por lote
+y por salida, siempre en la misma dirección. No llega a la báscula,
+pero es un libro que no cuadra con el almacén, y esa clase de hueco
+es la que se descubre tres meses después sin poder explicarla.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1668"/>
+  <autoFilter ref="A1:G1670"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -59918,7 +59990,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -59927,7 +59999,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00115</t>
+          <t>01669</t>
         </is>
       </c>
     </row>

--- a/COMENTARIOS.xlsx
+++ b/COMENTARIOS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Por fichero" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comentarios'!$A$1:$G$1670</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comentarios'!$A$1:$G$1672</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por fichero'!$A$1:$D$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1670"/>
+  <dimension ref="A1:G1672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         </is>
       </c>
       <c r="C659" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         </is>
       </c>
       <c r="C660" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         </is>
       </c>
       <c r="C661" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         </is>
       </c>
       <c r="C662" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         </is>
       </c>
       <c r="C663" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="C664" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         </is>
       </c>
       <c r="C665" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         </is>
       </c>
       <c r="C666" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         </is>
       </c>
       <c r="C667" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         </is>
       </c>
       <c r="C668" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         </is>
       </c>
       <c r="C1127" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1127" t="inlineStr">
         <is>
@@ -40487,7 +40487,7 @@
         </is>
       </c>
       <c r="C1128" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D1128" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         </is>
       </c>
       <c r="C1129" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D1129" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         </is>
       </c>
       <c r="C1130" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D1130" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         </is>
       </c>
       <c r="C1131" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D1131" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         </is>
       </c>
       <c r="C1132" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D1132" t="inlineStr">
         <is>
@@ -40670,7 +40670,7 @@
         </is>
       </c>
       <c r="C1133" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D1133" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         </is>
       </c>
       <c r="C1134" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D1134" t="inlineStr">
         <is>
@@ -40743,7 +40743,7 @@
         </is>
       </c>
       <c r="C1135" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D1135" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         </is>
       </c>
       <c r="C1136" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D1136" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         </is>
       </c>
       <c r="C1137" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D1137" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         </is>
       </c>
       <c r="C1138" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D1138" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         </is>
       </c>
       <c r="C1139" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D1139" t="inlineStr">
         <is>
@@ -40929,7 +40929,7 @@
         </is>
       </c>
       <c r="C1140" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D1140" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         </is>
       </c>
       <c r="C1141" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D1141" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         </is>
       </c>
       <c r="C1142" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D1142" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         </is>
       </c>
       <c r="C1143" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D1143" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         </is>
       </c>
       <c r="C1144" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D1144" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         </is>
       </c>
       <c r="C1145" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D1145" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         </is>
       </c>
       <c r="C1146" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1146" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         </is>
       </c>
       <c r="C1147" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D1147" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         </is>
       </c>
       <c r="C1148" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D1148" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         </is>
       </c>
       <c r="C1149" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D1149" t="inlineStr">
         <is>
@@ -41301,7 +41301,7 @@
         </is>
       </c>
       <c r="C1150" t="n">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D1150" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         </is>
       </c>
       <c r="C1151" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D1151" t="inlineStr">
         <is>
@@ -41368,7 +41368,7 @@
         </is>
       </c>
       <c r="C1152" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D1152" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         </is>
       </c>
       <c r="C1153" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D1153" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         </is>
       </c>
       <c r="C1154" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D1154" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         </is>
       </c>
       <c r="C1155" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D1155" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         </is>
       </c>
       <c r="C1156" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D1156" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         </is>
       </c>
       <c r="C1157" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D1157" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         </is>
       </c>
       <c r="C1158" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D1158" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         </is>
       </c>
       <c r="C1159" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D1159" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         </is>
       </c>
       <c r="C1160" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D1160" t="inlineStr">
         <is>
@@ -41668,7 +41668,7 @@
         </is>
       </c>
       <c r="C1161" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D1161" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         </is>
       </c>
       <c r="C1162" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D1162" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         </is>
       </c>
       <c r="C1163" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D1163" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         </is>
       </c>
       <c r="C1164" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D1164" t="inlineStr">
         <is>
@@ -41800,7 +41800,7 @@
         </is>
       </c>
       <c r="C1165" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D1165" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         </is>
       </c>
       <c r="C1166" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D1166" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         </is>
       </c>
       <c r="C1167" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D1167" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         </is>
       </c>
       <c r="C1168" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D1168" t="inlineStr">
         <is>
@@ -41930,7 +41930,7 @@
         </is>
       </c>
       <c r="C1169" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D1169" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         </is>
       </c>
       <c r="C1170" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D1170" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         </is>
       </c>
       <c r="C1252" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D1252" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         </is>
       </c>
       <c r="C1253" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1253" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         </is>
       </c>
       <c r="C1254" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D1254" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         </is>
       </c>
       <c r="C1255" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D1255" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         </is>
       </c>
       <c r="C1256" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D1256" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         </is>
       </c>
       <c r="C1257" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D1257" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         </is>
       </c>
       <c r="C1258" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D1258" t="inlineStr">
         <is>
@@ -45121,7 +45121,7 @@
         </is>
       </c>
       <c r="C1259" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D1259" t="inlineStr">
         <is>
@@ -45156,7 +45156,7 @@
         </is>
       </c>
       <c r="C1260" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D1260" t="inlineStr">
         <is>
@@ -45195,7 +45195,7 @@
         </is>
       </c>
       <c r="C1261" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D1261" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         </is>
       </c>
       <c r="C1262" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D1262" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         </is>
       </c>
       <c r="C1263" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D1263" t="inlineStr">
         <is>
@@ -45305,7 +45305,7 @@
         </is>
       </c>
       <c r="C1264" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D1264" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         </is>
       </c>
       <c r="C1265" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D1265" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         </is>
       </c>
       <c r="C1266" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D1266" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         </is>
       </c>
       <c r="C1267" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D1267" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         </is>
       </c>
       <c r="C1268" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D1268" t="inlineStr">
         <is>
@@ -45483,7 +45483,7 @@
         </is>
       </c>
       <c r="C1269" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D1269" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         </is>
       </c>
       <c r="C1270" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D1270" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         </is>
       </c>
       <c r="C1271" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D1271" t="inlineStr">
         <is>
@@ -45601,7 +45601,7 @@
         </is>
       </c>
       <c r="C1272" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D1272" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         </is>
       </c>
       <c r="C1273" t="n">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D1273" t="inlineStr">
         <is>
@@ -45674,7 +45674,7 @@
         </is>
       </c>
       <c r="C1274" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D1274" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         </is>
       </c>
       <c r="C1275" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D1275" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         </is>
       </c>
       <c r="C1276" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D1276" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         </is>
       </c>
       <c r="C1277" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D1277" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         </is>
       </c>
       <c r="C1278" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D1278" t="inlineStr">
         <is>
@@ -45845,7 +45845,7 @@
         </is>
       </c>
       <c r="C1279" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D1279" t="inlineStr">
         <is>
@@ -45877,7 +45877,7 @@
         </is>
       </c>
       <c r="C1280" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D1280" t="inlineStr">
         <is>
@@ -45917,7 +45917,7 @@
         </is>
       </c>
       <c r="C1281" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D1281" t="inlineStr">
         <is>
@@ -45951,7 +45951,7 @@
         </is>
       </c>
       <c r="C1282" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D1282" t="inlineStr">
         <is>
@@ -45985,7 +45985,7 @@
         </is>
       </c>
       <c r="C1283" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D1283" t="inlineStr">
         <is>
@@ -46018,7 +46018,7 @@
         </is>
       </c>
       <c r="C1284" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D1284" t="inlineStr">
         <is>
@@ -46053,7 +46053,7 @@
         </is>
       </c>
       <c r="C1285" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D1285" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         </is>
       </c>
       <c r="C1286" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D1286" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         </is>
       </c>
       <c r="C1287" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D1287" t="inlineStr">
         <is>
@@ -47633,7 +47633,7 @@
         </is>
       </c>
       <c r="C1326" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D1326" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         </is>
       </c>
       <c r="C1327" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D1327" t="inlineStr">
         <is>
@@ -47703,7 +47703,7 @@
         </is>
       </c>
       <c r="C1328" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D1328" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         </is>
       </c>
       <c r="C1329" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D1329" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         </is>
       </c>
       <c r="C1330" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D1330" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         </is>
       </c>
       <c r="C1331" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D1331" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         </is>
       </c>
       <c r="C1332" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D1332" t="inlineStr">
         <is>
@@ -47897,7 +47897,7 @@
         </is>
       </c>
       <c r="C1333" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D1333" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         </is>
       </c>
       <c r="C1334" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D1334" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         </is>
       </c>
       <c r="C1335" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1335" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         </is>
       </c>
       <c r="C1336" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D1336" t="inlineStr">
         <is>
@@ -48046,7 +48046,7 @@
         </is>
       </c>
       <c r="C1337" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D1337" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         </is>
       </c>
       <c r="C1338" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D1338" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         </is>
       </c>
       <c r="C1339" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D1339" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         </is>
       </c>
       <c r="C1340" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D1340" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         </is>
       </c>
       <c r="C1341" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D1341" t="inlineStr">
         <is>
@@ -48230,7 +48230,7 @@
         </is>
       </c>
       <c r="C1342" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D1342" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         </is>
       </c>
       <c r="C1343" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D1343" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         </is>
       </c>
       <c r="C1344" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D1344" t="inlineStr">
         <is>
@@ -48335,7 +48335,7 @@
         </is>
       </c>
       <c r="C1345" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D1345" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         </is>
       </c>
       <c r="C1346" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D1346" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         </is>
       </c>
       <c r="C1347" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D1347" t="inlineStr">
         <is>
@@ -48437,7 +48437,7 @@
         </is>
       </c>
       <c r="C1348" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D1348" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         </is>
       </c>
       <c r="C1349" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D1349" t="inlineStr">
         <is>
@@ -48501,7 +48501,7 @@
         </is>
       </c>
       <c r="C1350" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D1350" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         </is>
       </c>
       <c r="C1351" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D1351" t="inlineStr">
         <is>
@@ -59750,12 +59750,12 @@
       <c r="E1669" t="inlineStr"/>
       <c r="F1669" s="2" t="inlineStr">
         <is>
-          <t>Los dos totales, con los mismos decimales con los que se apunta cada salida.</t>
+          <t>[01668] Los dos totales, con los mismos decimales con los que se apunta cada salida.</t>
         </is>
       </c>
       <c r="G1669" s="2" t="inlineStr">
         <is>
-          <t>Los dos totales, con los mismos decimales con los que se apunta cada
+          <t>[01668] Los dos totales, con los mismos decimales con los que se apunta cada
 salida. Iban a cuatro mientras las salidas iban a seis, así que el total
 no era la suma de sus partes: hasta medio decigramo y medio céntimo de
 diferencia entre lo que dice el resumen y lo que dicen las líneas. En un
@@ -59786,12 +59786,12 @@
       <c r="E1670" t="inlineStr"/>
       <c r="F1670" s="2" t="inlineStr">
         <is>
-          <t>Lo que se apunta es lo que se saca, con los mismos decimales.</t>
+          <t>[01669] Lo que se apunta es lo que se saca, con los mismos decimales.</t>
         </is>
       </c>
       <c r="G1670" s="2" t="inlineStr">
         <is>
-          <t>Lo que se apunta es lo que se saca, con los mismos decimales.
+          <t>[01669] Lo que se apunta es lo que se saca, con los mismos decimales.
 Se apuntaba redondeado a cuatro y se descontaba a seis, así que el
 papel decía una cosa y el lote otra: hasta medio decigramo por lote
 y por salida, siempre en la misma dirección. No llega a la báscula,
@@ -59800,8 +59800,71 @@
         </is>
       </c>
     </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>01670</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>thegrill/engine/cost.py</t>
+        </is>
+      </c>
+      <c r="C1671" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1671" t="inlineStr"/>
+      <c r="F1671" s="2" t="inlineStr">
+        <is>
+          <t>`exacto` no es «web»: es la aritmética del dinero y del peso, sin ninguna dependencia del proyecto.</t>
+        </is>
+      </c>
+      <c r="G1671" s="2" t="inlineStr">
+        <is>
+          <t>`exacto` no es «web»: es la aritmética del dinero y del peso, sin ninguna
+dependencia del proyecto. Duplicar aquí la regla del redondeo sería peor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>01671</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>thegrill/engine/inventory.py</t>
+        </is>
+      </c>
+      <c r="C1672" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1672" t="inlineStr"/>
+      <c r="F1672" s="2" t="inlineStr">
+        <is>
+          <t>Ver la nota de `engine/cost.py`: `exacto` es aritmética, no una capa de arriba.</t>
+        </is>
+      </c>
+      <c r="G1672" s="2" t="inlineStr">
+        <is>
+          <t>Ver la nota de `engine/cost.py`: `exacto` es aritmética, no una capa de arriba.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1670"/>
+  <autoFilter ref="A1:G1672"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -59950,7 +60013,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -59959,7 +60022,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00090</t>
+          <t>01670</t>
         </is>
       </c>
     </row>
@@ -60010,7 +60073,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -60019,7 +60082,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00130</t>
+          <t>01671</t>
         </is>
       </c>
     </row>

--- a/COMENTARIOS.xlsx
+++ b/COMENTARIOS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Por fichero" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comentarios'!$A$1:$G$1672</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comentarios'!$A$1:$G$1677</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por fichero'!$A$1:$D$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1672"/>
+  <dimension ref="A1:G1677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>2508</v>
+        <v>2511</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>2535</v>
+        <v>2538</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>2562</v>
+        <v>2565</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>2572</v>
+        <v>2575</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>2584</v>
+        <v>2587</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>2595</v>
+        <v>2598</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>2606</v>
+        <v>2609</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>2641</v>
+        <v>2644</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>2687</v>
+        <v>2690</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>2701</v>
+        <v>2704</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>2725</v>
+        <v>2728</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2743</v>
+        <v>2746</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>2760</v>
+        <v>2763</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>2775</v>
+        <v>2778</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>2801</v>
+        <v>2804</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>2817</v>
+        <v>2820</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>2829</v>
+        <v>2832</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>2847</v>
+        <v>2850</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>2879</v>
+        <v>2882</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>2897</v>
+        <v>2900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>2926</v>
+        <v>2929</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>2995</v>
+        <v>2998</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>3013</v>
+        <v>3016</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>3035</v>
+        <v>3038</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>3052</v>
+        <v>3055</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>3076</v>
+        <v>3079</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>3101</v>
+        <v>3104</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>3113</v>
+        <v>3116</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>3131</v>
+        <v>3134</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>3143</v>
+        <v>3146</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>3158</v>
+        <v>3161</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>3182</v>
+        <v>3185</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>3190</v>
+        <v>3193</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>3208</v>
+        <v>3211</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>3217</v>
+        <v>3220</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>3231</v>
+        <v>3234</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>3246</v>
+        <v>3249</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>3424</v>
+        <v>3427</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>3441</v>
+        <v>3444</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>3454</v>
+        <v>3457</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>3459</v>
+        <v>3462</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>2861</v>
+        <v>2864</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>2748</v>
+        <v>2751</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>2787</v>
+        <v>2790</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>2836</v>
+        <v>2839</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>2877</v>
+        <v>2880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>2885</v>
+        <v>2888</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>2953</v>
+        <v>2956</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>3024</v>
+        <v>3027</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>3057</v>
+        <v>3060</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>3081</v>
+        <v>3084</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>3096</v>
+        <v>3099</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>3256</v>
+        <v>3259</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>5150</v>
+        <v>5185</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>1437</v>
+        <v>1447</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>1471</v>
+        <v>1481</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>1488</v>
+        <v>1498</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>2169</v>
+        <v>2184</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>2203</v>
+        <v>2218</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>2220</v>
+        <v>2235</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>2901</v>
+        <v>2921</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>2935</v>
+        <v>2955</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>2952</v>
+        <v>2972</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>3633</v>
+        <v>3658</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>3667</v>
+        <v>3692</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>3684</v>
+        <v>3709</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>4365</v>
+        <v>4395</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>4399</v>
+        <v>4429</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>4418</v>
+        <v>4448</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>5099</v>
+        <v>5134</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>5133</v>
+        <v>5168</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -55225,7 +55225,7 @@
         </is>
       </c>
       <c r="C1537" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="D1537" t="inlineStr">
         <is>
@@ -58314,7 +58314,7 @@
         </is>
       </c>
       <c r="C1629" t="n">
-        <v>2940</v>
+        <v>2943</v>
       </c>
       <c r="D1629" t="inlineStr">
         <is>
@@ -59822,12 +59822,12 @@
       <c r="E1671" t="inlineStr"/>
       <c r="F1671" s="2" t="inlineStr">
         <is>
-          <t>`exacto` no es «web»: es la aritmética del dinero y del peso, sin ninguna dependencia del proyecto.</t>
+          <t>[01670] `exacto` no es «web»: es la aritmética del dinero y del peso, sin ninguna dependencia del proyecto.</t>
         </is>
       </c>
       <c r="G1671" s="2" t="inlineStr">
         <is>
-          <t>`exacto` no es «web»: es la aritmética del dinero y del peso, sin ninguna
+          <t>[01670] `exacto` no es «web»: es la aritmética del dinero y del peso, sin ninguna
 dependencia del proyecto. Duplicar aquí la regla del redondeo sería peor.</t>
         </is>
       </c>
@@ -59854,17 +59854,187 @@
       <c r="E1672" t="inlineStr"/>
       <c r="F1672" s="2" t="inlineStr">
         <is>
-          <t>Ver la nota de `engine/cost.py`: `exacto` es aritmética, no una capa de arriba.</t>
+          <t>[01671] Ver la nota de `engine/cost.py`: `exacto` es aritmética, no una capa de arriba.</t>
         </is>
       </c>
       <c r="G1672" s="2" t="inlineStr">
         <is>
-          <t>Ver la nota de `engine/cost.py`: `exacto` es aritmética, no una capa de arriba.</t>
+          <t>[01671] Ver la nota de `engine/cost.py`: `exacto` es aritmética, no una capa de arriba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>01672</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>thegrill/config.py</t>
+        </is>
+      </c>
+      <c r="C1673" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1673" t="inlineStr"/>
+      <c r="F1673" s="2" t="inlineStr">
+        <is>
+          <t>la página que lo explica El recorrido de una pieza del muelle al plato, dibujado, para mandárselo a quien pregunte cómo funciona esto.</t>
+        </is>
+      </c>
+      <c r="G1673" s="2" t="inlineStr">
+        <is>
+          <t>--------------------------------------------------- la página que lo explica
+El recorrido de una pieza del muelle al plato, dibujado, para mandárselo a
+quien pregunte cómo funciona esto. Sale en la consola del dueño, con su botón
+de copiar.
+Va en una variable de entorno y no escrito en la plantilla porque cambiar a
+dónde apunta —una versión nueva, la página en otro sitio— es una decisión de
+un martes cualquiera y no puede depender de un despliegue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>01673</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>thegrill/meat/app.py</t>
+        </is>
+      </c>
+      <c r="C1674" t="n">
+        <v>2495</v>
+      </c>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>bloque</t>
+        </is>
+      </c>
+      <c r="E1674" t="inlineStr"/>
+      <c r="F1674" s="2" t="inlineStr">
+        <is>
+          <t>La página que explica el recorrido de una pieza, para mandársela a quien pregunte cómo funciona esto.</t>
+        </is>
+      </c>
+      <c r="G1674" s="2" t="inlineStr">
+        <is>
+          <t>La página que explica el recorrido de una pieza, para
+mandársela a quien pregunte cómo funciona esto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>01674</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>thegrill/meat/templates/admin.html</t>
+        </is>
+      </c>
+      <c r="C1675" t="n">
+        <v>27</v>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>plantilla</t>
+        </is>
+      </c>
+      <c r="E1675" t="inlineStr"/>
+      <c r="F1675" s="2" t="inlineStr">
+        <is>
+          <t>La página que explica el recorrido de una pieza, dibujado.</t>
+        </is>
+      </c>
+      <c r="G1675" s="2" t="inlineStr">
+        <is>
+          <t>La página que explica el recorrido de una pieza, dibujado. Va aquí arriba
+   porque su trabajo es que esté a mano el día que alguien pregunta «¿y esto
+   cómo funciona?»: se copia el enlace y se manda, sin buscarlo en ningún
+   sitio. La dirección sale de `GRILL_PAGINA_RECORRIDO`, no está escrita en la
+   plantilla: cambiar a dónde apunta es cosa de un martes, no de un
+   despliegue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>01675</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>thegrill/meat/templates/admin.html</t>
+        </is>
+      </c>
+      <c r="C1676" t="n">
+        <v>44</v>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>plantilla</t>
+        </is>
+      </c>
+      <c r="E1676" t="inlineStr"/>
+      <c r="F1676" s="2" t="inlineStr">
+        <is>
+          <t>El enlace, escrito y seleccionable: si copiar falla —un navegador viejo, un permiso— sigue estando para cogerlo a mano.</t>
+        </is>
+      </c>
+      <c r="G1676" s="2" t="inlineStr">
+        <is>
+          <t>El enlace, escrito y seleccionable: si copiar falla —un navegador viejo,
+     un permiso— sigue estando para cogerlo a mano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>01676</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>thegrill/meat/templates/admin.html</t>
+        </is>
+      </c>
+      <c r="C1677" t="n">
+        <v>276</v>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>plantilla</t>
+        </is>
+      </c>
+      <c r="E1677" t="inlineStr"/>
+      <c r="F1677" s="2" t="inlineStr">
+        <is>
+          <t>Copiar el enlace sin salir de la pantalla.</t>
+        </is>
+      </c>
+      <c r="G1677" s="2" t="inlineStr">
+        <is>
+          <t>Copiar el enlace sin salir de la pantalla. Si el navegador no deja —los
+   viejos y algunos permisos—, se selecciona el texto para cogerlo a mano: lo
+   que no puede pasar es que el botón no haga nada y no lo diga.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1672"/>
+  <autoFilter ref="A1:G1677"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -59973,7 +60143,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -59982,7 +60152,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00066</t>
+          <t>01672</t>
         </is>
       </c>
     </row>
@@ -60173,7 +60343,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -60182,7 +60352,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>01649</t>
+          <t>01673</t>
         </is>
       </c>
     </row>
@@ -60433,7 +60603,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -60442,7 +60612,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>01536</t>
+          <t>01676</t>
         </is>
       </c>
     </row>
